--- a/docs/pcb-preparation/power-budget/MIRA_Power_Budget_Day2.xlsx
+++ b/docs/pcb-preparation/power-budget/MIRA_Power_Budget_Day2.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="1" r:id="R93990ade9f764ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шины" sheetId="2" r:id="R1e3e30b011ed43c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пуск" sheetId="3" r:id="Rf7d0b7d0ccc84b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Контакты" sheetId="4" r:id="Raf56503058f9438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузки" sheetId="5" r:id="R57ee232ec5b14687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вход" sheetId="6" r:id="Rc72af9767b2d4765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="1" r:id="R7b685b285528471d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шины" sheetId="2" r:id="Rfc9f5733c5ac4ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пуск" sheetId="3" r:id="R35ec77e0246b4fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Контакты" sheetId="4" r:id="R665859b3078b4ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нагрузки" sheetId="5" r:id="R3c03f413e94d4549"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вход" sheetId="6" r:id="R8fd8275618294460"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -80,6 +80,21 @@
         <x:fgColor rgb="FFEAF2FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF24364B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0CB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -93,7 +108,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -175,18 +190,49 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="5">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF9B2424"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE4E4"/>
         </x:patternFill>
       </x:fill>
@@ -197,7 +243,7 @@
         <x:color rgb="FF9B2424"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFBE4E4"/>
         </x:patternFill>
       </x:fill>
@@ -208,7 +254,18 @@
         <x:color rgb="FF9B2424"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFFBE4E4"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9B2424"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFFBE4E4"/>
         </x:patternFill>
       </x:fill>
@@ -463,7 +520,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="str">
-        <x:v>28.10.2026. Предварительный расчёт по 24b4428. Неизвестные нагрузки явно заданы допущениями.</x:v>
+        <x:v>28.10.2026. Схема 52f4386: восемь пар разъёмов. Пик нагрузок включает +30% к предварительным допущениям.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -490,7 +547,7 @@
         <x:v>Шина</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>Номинал, В</x:v>
+        <x:v>Vraw модели, В</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
         <x:v>Источник: ср., А</x:v>
@@ -505,10 +562,10 @@
         <x:v>Пик Control, А</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
-        <x:v>Контактов питания</x:v>
+        <x:v>Силовых контактов всего</x:v>
       </x:c>
       <x:c r="H5" s="8" t="str">
-        <x:v>Запас падения, мВ</x:v>
+        <x:v>CORE: запас, мВ</x:v>
       </x:c>
       <x:c r="I5" s="8" t="str">
         <x:v>Статус</x:v>
@@ -528,26 +585,24 @@
       </x:c>
       <x:c r="D6" s="16" t="n">
         <x:f>'Шины'!O6</x:f>
-        <x:v>0.20600000000000002</x:v>
+        <x:v>0.26780000000000004</x:v>
       </x:c>
       <x:c r="E6" s="16" t="n">
         <x:f>'Пуск'!J6</x:f>
-        <x:v>0.16635604</x:v>
+        <x:v>0.16651348</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
-        <x:f>'Контакты'!E6</x:f>
-        <x:v>0.005</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"AON",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="G6" s="9" t="n">
-        <x:f>'Контакты'!C6</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="n">
-        <x:f>'Контакты'!M6</x:f>
-        <x:v>33.67500000000001</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
@@ -564,26 +619,24 @@
       </x:c>
       <x:c r="D7" s="17" t="n">
         <x:f>'Шины'!O7</x:f>
-        <x:v>0.9000000000000001</x:v>
+        <x:v>1.1700000000000002</x:v>
       </x:c>
       <x:c r="E7" s="17" t="n">
         <x:f>'Пуск'!J7</x:f>
         <x:v>0.40361111111111114</x:v>
       </x:c>
       <x:c r="F7" s="17" t="n">
-        <x:f>'Контакты'!E7</x:f>
-        <x:v>0.8800000000000001</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"SYS3V3",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>1.1440000000000001</x:v>
       </x:c>
       <x:c r="G7" s="2" t="n">
-        <x:f>'Контакты'!C7</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H7" s="17" t="n">
-        <x:f>'Контакты'!M7</x:f>
-        <x:v>216.31851851851857</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H7" s="17" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I7" s="13" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="38" customHeight="1">
@@ -600,26 +653,24 @@
       </x:c>
       <x:c r="D8" s="16" t="n">
         <x:f>'Шины'!O8</x:f>
-        <x:v>0.05</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="E8" s="16" t="n">
         <x:f>'Пуск'!J8</x:f>
         <x:v>0.13291999999999998</x:v>
       </x:c>
       <x:c r="F8" s="16" t="n">
-        <x:f>'Контакты'!E8</x:f>
-        <x:v>0.05</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"USB5",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="G8" s="9" t="n">
-        <x:f>'Контакты'!C8</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="16" t="n">
-        <x:f>'Контакты'!M8</x:f>
-        <x:v>136.25000000000034</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H8" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
@@ -628,7 +679,7 @@
       </x:c>
       <x:c r="B9" s="17" t="n">
         <x:f>'Шины'!D10</x:f>
-        <x:v>1.008</x:v>
+        <x:v>1.0440769847634321</x:v>
       </x:c>
       <x:c r="C9" s="17" t="n">
         <x:f>'Шины'!N10</x:f>
@@ -636,26 +687,25 @@
       </x:c>
       <x:c r="D9" s="17" t="n">
         <x:f>'Шины'!O10</x:f>
-        <x:v>4</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="E9" s="17" t="n">
         <x:f>'Пуск'!J10</x:f>
-        <x:v>1.6193097018181817</x:v>
+        <x:v>1.6414752044732812</x:v>
       </x:c>
       <x:c r="F9" s="17" t="n">
-        <x:f>'Контакты'!E9</x:f>
-        <x:v>4</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"CORE1V0",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="G9" s="2" t="n">
-        <x:f>'Контакты'!C9</x:f>
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H9" s="17" t="n">
-        <x:f>'Контакты'!M9</x:f>
-        <x:v>-20.160000000000018</x:v>
+        <x:f>'Контакты'!D64</x:f>
+        <x:v>9.189230152365724</x:v>
       </x:c>
       <x:c r="I9" s="13" t="str">
-        <x:v>Нужны XPE и проверка сопротивления пути</x:v>
+        <x:v>Условная DC-оценка; нужны XPE и PCB</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
@@ -672,26 +722,24 @@
       </x:c>
       <x:c r="D10" s="16" t="n">
         <x:f>'Шины'!O11</x:f>
-        <x:v>0.3</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="E10" s="16" t="n">
         <x:f>'Пуск'!J11</x:f>
         <x:v>0.19771439999999998</x:v>
       </x:c>
       <x:c r="F10" s="16" t="n">
-        <x:f>'Контакты'!E10</x:f>
-        <x:v>0.3</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"AUX1V8",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="G10" s="9" t="n">
-        <x:f>'Контакты'!C10</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="n">
-        <x:f>'Контакты'!M10</x:f>
-        <x:v>33.50000000000005</x:v>
+      <x:c r="H10" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="38" customHeight="1">
@@ -708,26 +756,24 @@
       </x:c>
       <x:c r="D11" s="17" t="n">
         <x:f>'Шины'!O13</x:f>
-        <x:v>1.19003</x:v>
+        <x:v>1.5470300000000001</x:v>
       </x:c>
       <x:c r="E11" s="17" t="n">
         <x:f>'Пуск'!J13</x:f>
         <x:v>0.912907788</x:v>
       </x:c>
       <x:c r="F11" s="17" t="n">
-        <x:f>'Контакты'!E11</x:f>
-        <x:v>1.19003</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
       </x:c>
       <x:c r="G11" s="2" t="n">
-        <x:f>'Контакты'!C11</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="n">
-        <x:f>'Контакты'!M11</x:f>
-        <x:v>31.415716666666622</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H11" s="17" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I11" s="13" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="38" customHeight="1">
@@ -744,26 +790,24 @@
       </x:c>
       <x:c r="D12" s="16" t="n">
         <x:f>'Шины'!O14</x:f>
-        <x:v>1.111122244488978</x:v>
+        <x:v>1.4444589178356715</x:v>
       </x:c>
       <x:c r="E12" s="16" t="n">
         <x:f>'Пуск'!J14</x:f>
         <x:v>0.23898608</x:v>
       </x:c>
       <x:c r="F12" s="16" t="n">
-        <x:f>'Контакты'!E12</x:f>
-        <x:v>0.8</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"DDR1V35",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="G12" s="9" t="n">
-        <x:f>'Контакты'!C12</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="n">
-        <x:f>'Контакты'!M12</x:f>
-        <x:v>10.055444221776861</x:v>
+      <x:c r="H12" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I12" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
@@ -780,26 +824,24 @@
       </x:c>
       <x:c r="D13" s="17" t="n">
         <x:f>'Шины'!O15</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="E13" s="17" t="n">
         <x:f>'Пуск'!J15</x:f>
         <x:v>0.12213046799999999</x:v>
       </x:c>
       <x:c r="F13" s="17" t="n">
-        <x:f>'Контакты'!E13</x:f>
-        <x:v>0.2</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"PHY1V05",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="G13" s="2" t="n">
-        <x:f>'Контакты'!C13</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="17" t="n">
-        <x:f>'Контакты'!M13</x:f>
-        <x:v>59.510000000000076</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H13" s="17" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I13" s="13" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
@@ -816,26 +858,24 @@
       </x:c>
       <x:c r="D14" s="16" t="n">
         <x:f>'Шины'!O16</x:f>
-        <x:v>0.31112224448897796</x:v>
+        <x:v>0.40445891783567134</x:v>
       </x:c>
       <x:c r="E14" s="16" t="n">
         <x:f>'Пуск'!J16</x:f>
         <x:v>0.02486</x:v>
       </x:c>
       <x:c r="F14" s="16" t="n">
-        <x:f>'Контакты'!E14</x:f>
-        <x:v>0.31112224448897796</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"VTT",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.40445891783567134</x:v>
       </x:c>
       <x:c r="G14" s="9" t="n">
-        <x:f>'Контакты'!C14</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str">
-        <x:f>'Контакты'!M14</x:f>
-        <x:v>проверить отдельно</x:v>
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
-        <x:v>Проверить tracking и межплатный возврат</x:v>
+        <x:v>Проверить source/sink, tracking и возврат</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="38" customHeight="1">
@@ -852,26 +892,24 @@
       </x:c>
       <x:c r="D15" s="17" t="n">
         <x:f>'Шины'!O17</x:f>
-        <x:v>0.001</x:v>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="E15" s="17" t="n">
         <x:f>'Пуск'!J17</x:f>
         <x:v>0.000181</x:v>
       </x:c>
       <x:c r="F15" s="17" t="n">
-        <x:f>'Контакты'!E15</x:f>
-        <x:v>0.001</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"DDR_VREF",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="G15" s="2" t="n">
-        <x:f>'Контакты'!C15</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
-        <x:f>'Контакты'!M15</x:f>
-        <x:v>проверить отдельно</x:v>
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I15" s="13" t="str">
-        <x:v>Проверить tracking и межплатный возврат</x:v>
+        <x:v>Проверить source/sink, tracking и возврат</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="38" customHeight="1">
@@ -888,26 +926,24 @@
       </x:c>
       <x:c r="D16" s="16" t="n">
         <x:f>'Шины'!O19</x:f>
-        <x:v>0.20643</x:v>
+        <x:v>0.26703</x:v>
       </x:c>
       <x:c r="E16" s="16" t="n">
         <x:f>'Пуск'!J19</x:f>
         <x:v>0.13775073846153846</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
-        <x:f>'Контакты'!E16</x:f>
-        <x:v>0.15</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"ANA5",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.195</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:f>'Контакты'!C16</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="16" t="n">
-        <x:f>'Контакты'!M16</x:f>
-        <x:v>125.92850000000033</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I16" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="38" customHeight="1">
@@ -924,26 +960,24 @@
       </x:c>
       <x:c r="D17" s="17" t="n">
         <x:f>'Шины'!O20</x:f>
-        <x:v>0.05203000000000001</x:v>
+        <x:v>0.06763000000000001</x:v>
       </x:c>
       <x:c r="E17" s="17" t="n">
         <x:f>'Пуск'!J20</x:f>
         <x:v>0.02610458461538461</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
-        <x:f>'Контакты'!E17</x:f>
-        <x:v>0.050030000000000005</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"ANA3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q26</x:f>
+        <x:v>0.06503</x:v>
       </x:c>
       <x:c r="G17" s="2" t="n">
-        <x:f>'Контакты'!C17</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="17" t="n">
-        <x:f>'Контакты'!M17</x:f>
-        <x:v>80.24775000000007</x:v>
+      <x:c r="H17" s="17" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I17" s="13" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="38" customHeight="1">
@@ -960,26 +994,24 @@
       </x:c>
       <x:c r="D18" s="16" t="n">
         <x:f>'Шины'!O21</x:f>
-        <x:v>0.36810000000000004</x:v>
+        <x:v>0.47850000000000004</x:v>
       </x:c>
       <x:c r="E18" s="16" t="n">
         <x:f>'Пуск'!J21</x:f>
         <x:v>0.5894901972850679</x:v>
       </x:c>
       <x:c r="F18" s="16" t="n">
-        <x:f>'Контакты'!E18</x:f>
-        <x:v>0.30810000000000004</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"P15",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q27</x:f>
+        <x:v>0.4005</x:v>
       </x:c>
       <x:c r="G18" s="9" t="n">
-        <x:f>'Контакты'!C18</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="16" t="n">
-        <x:f>'Контакты'!M18</x:f>
-        <x:v>385.73184389140056</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I18" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="38" customHeight="1">
@@ -988,7 +1020,7 @@
       </x:c>
       <x:c r="B19" s="17" t="n">
         <x:f>'Шины'!D22</x:f>
-        <x:v>-14.990045248868777</x:v>
+        <x:v>-15</x:v>
       </x:c>
       <x:c r="C19" s="17" t="n">
         <x:f>'Шины'!N22</x:f>
@@ -996,26 +1028,24 @@
       </x:c>
       <x:c r="D19" s="17" t="n">
         <x:f>'Шины'!O22</x:f>
-        <x:v>0.36000000000000004</x:v>
+        <x:v>0.468</x:v>
       </x:c>
       <x:c r="E19" s="17" t="n">
         <x:f>'Пуск'!J22</x:f>
-        <x:v>0.6351778751131222</x:v>
+        <x:v>0.61788</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
-        <x:f>'Контакты'!E19</x:f>
-        <x:v>0.30000000000000004</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"N15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="G19" s="2" t="n">
-        <x:f>'Контакты'!C19</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="17" t="n">
-        <x:f>'Контакты'!M19</x:f>
-        <x:v>386.7443438914005</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="17" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I19" s="13" t="str">
-        <x:v>Проверить пуск, рампу и sequencing</x:v>
+        <x:v>Модуль 2 А; проверить пуск относительно OCP</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="38" customHeight="1">
@@ -1032,26 +1062,24 @@
       </x:c>
       <x:c r="D20" s="16" t="n">
         <x:f>'Шины'!O23</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="E20" s="16" t="n">
         <x:f>'Пуск'!J23</x:f>
         <x:v>0.06644583529411763</x:v>
       </x:c>
       <x:c r="F20" s="16" t="n">
-        <x:f>'Контакты'!E20</x:f>
-        <x:v>0.06</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"PROG_P15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="G20" s="9" t="n">
-        <x:f>'Контакты'!C20</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H20" s="16" t="n">
-        <x:f>'Контакты'!M20</x:f>
-        <x:v>391.93434389140054</x:v>
+      <x:c r="H20" s="16" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I20" s="12" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="38" customHeight="1">
@@ -1060,7 +1088,7 @@
       </x:c>
       <x:c r="B21" s="17" t="n">
         <x:f>'Шины'!D24</x:f>
-        <x:v>-14.990045248868777</x:v>
+        <x:v>-15</x:v>
       </x:c>
       <x:c r="C21" s="17" t="n">
         <x:f>'Шины'!N24</x:f>
@@ -1068,26 +1096,24 @@
       </x:c>
       <x:c r="D21" s="17" t="n">
         <x:f>'Шины'!O24</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="E21" s="17" t="n">
         <x:f>'Пуск'!J24</x:f>
-        <x:v>0.06644583529411763</x:v>
+        <x:v>0.06648</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:f>'Контакты'!E21</x:f>
-        <x:v>0.06</x:v>
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"PROG_N15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="G21" s="2" t="n">
-        <x:f>'Контакты'!C21</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H21" s="17" t="n">
-        <x:f>'Контакты'!M21</x:f>
-        <x:v>392.7443438914005</x:v>
+      <x:c r="H21" s="17" t="str">
+        <x:v>Требуется PCB</x:v>
       </x:c>
       <x:c r="I21" s="13" t="str">
-        <x:v>Значения предварительные; MPN разъёма не выбран</x:v>
+        <x:v>MPN выбраны; ветви и нагрев ещё проверить</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1120,7 +1146,7 @@
       <x:c r="C24" s="2"/>
       <x:c r="D24" s="17" t="n">
         <x:f>'Вход'!C29</x:f>
-        <x:v>0.6080574097421761</x:v>
+        <x:v>0.6421060300578763</x:v>
       </x:c>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2"/>
@@ -1136,7 +1162,7 @@
       <x:c r="C25" s="2"/>
       <x:c r="D25" s="17" t="n">
         <x:f>'Вход'!C30</x:f>
-        <x:v>1.3541294952707617</x:v>
+        <x:v>1.7993227645216456</x:v>
       </x:c>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2"/>
@@ -1152,7 +1178,7 @@
       <x:c r="C26" s="2"/>
       <x:c r="D26" s="17" t="n">
         <x:f>'Вход'!C31</x:f>
-        <x:v>1.8152490771758512</x:v>
+        <x:v>2.416441190124911</x:v>
       </x:c>
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2"/>
@@ -1162,13 +1188,13 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="1" t="str">
-        <x:v>Мощность внешнего БП с запасом, Вт</x:v>
+        <x:v>Входная мощность расчётного пика, Вт</x:v>
       </x:c>
       <x:c r="B27" s="1"/>
       <x:c r="C27" s="1"/>
       <x:c r="D27" s="29" t="n">
         <x:f>'Вход'!C37</x:f>
-        <x:v>40.62388485812285</x:v>
+        <x:v>43.18374634851949</x:v>
       </x:c>
       <x:c r="E27" s="1"/>
       <x:c r="F27" s="1"/>
@@ -1240,7 +1266,7 @@
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
       <x:c r="A33" s="30" t="str">
-        <x:v>1. Уточнить ток FPGA в XPE и сценарий матрицы; согласовать расчётные допущения.</x:v>
+        <x:v>1. Уточнить XPE FPGA и предельную нагрузку матрицы. Запас 30% задан над предварительными токами.</x:v>
       </x:c>
       <x:c r="B33" s="30"/>
       <x:c r="C33" s="30"/>
@@ -1264,7 +1290,7 @@
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
       <x:c r="A35" s="30" t="str">
-        <x:v>2. Подтвердить фактические рампы, EN и пуск −15 В при минимальном входе.</x:v>
+        <x:v>2. Подтвердить запуск N15/PROG_N15 при минимальном входе, с учётом порога OCP платы.</x:v>
       </x:c>
       <x:c r="B35" s="30"/>
       <x:c r="C35" s="30"/>
@@ -1288,7 +1314,7 @@
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
       <x:c r="A37" s="30" t="str">
-        <x:v>3. Выбрать пару разъёмов и проверить ток при одновременной нагрузке контактов и реальную петлю GND.</x:v>
+        <x:v>3. Восемь пар разъёмов выбраны. Проверить токи местных ветвей, возврат GND, геометрию и температуру.</x:v>
       </x:c>
       <x:c r="B37" s="30"/>
       <x:c r="C37" s="30"/>
@@ -1312,7 +1338,7 @@
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
       <x:c r="A39" s="30" t="str">
-        <x:v>4. Уточнить допуски напряжений, входную защиту, тепловые ограничения и реальные сопротивления.</x:v>
+        <x:v>4. Подтвердить потери и окна напряжений на PCB, динамику sense CORE, VTT и DDR_VREF.</x:v>
       </x:c>
       <x:c r="B39" s="30"/>
       <x:c r="C39" s="30"/>
@@ -1336,7 +1362,7 @@
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
       <x:c r="A41" s="30" t="str">
-        <x:v>Расчёт не изменяет схемы. FT1V0 / FT_PLL1V0 учтены в потреблении FT601 от IO3V3; фильтрованные ветви не добавляют второй источник мощности.</x:v>
+        <x:v>ERC обеих схем: 0 ошибок, 0 предупреждений, 0 исключений. Два прежних правила оформления отключены.</x:v>
       </x:c>
       <x:c r="B41" s="30"/>
       <x:c r="C41" s="30"/>
@@ -1360,7 +1386,7 @@
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
       <x:c r="A43" s="30" t="str">
-        <x:v>Модель предполагает штатную работу узлов. Вопросы ERC остаются открытыми. Мелкие фильтрованные ёмкости и токи пуска ИС ещё уточнить.</x:v>
+        <x:v>Формулы описывают условные режимы. Ни разводка PCB, ни испытания прототипа ещё не подтверждены.</x:v>
       </x:c>
       <x:c r="B43" s="30"/>
       <x:c r="C43" s="30"/>
@@ -1484,7 +1510,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="str">
-        <x:v>Номиналы до шунта. Для отрицательных шин мощность и ток рассчитаны по модулю. Паспортный ток ИС не подтверждает тепловой запас платы.</x:v>
+        <x:v>Пик нагрузок включает запас. CORE Vraw учитывает положительный sense при расчётном пике. Ток ИС не равен пределу платы.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -1547,7 +1573,7 @@
         <x:v>Источник</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
-        <x:v>Vraw, В</x:v>
+        <x:v>Vraw в модели, В</x:v>
       </x:c>
       <x:c r="E5" s="8" t="str">
         <x:v>Ток ИС / оценка, А</x:v>
@@ -1647,7 +1673,7 @@
       </x:c>
       <x:c r="K6" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A6)</x:f>
-        <x:v>0.20500000000000002</x:v>
+        <x:v>0.2665</x:v>
       </x:c>
       <x:c r="L6" s="16" t="n">
         <x:f>P17</x:f>
@@ -1655,7 +1681,7 @@
       </x:c>
       <x:c r="M6" s="16" t="n">
         <x:f>Q17</x:f>
-        <x:v>0.001</x:v>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="N6" s="16" t="n">
         <x:f>J6+L6</x:f>
@@ -1663,7 +1689,7 @@
       </x:c>
       <x:c r="O6" s="16" t="n">
         <x:f>K6+M6</x:f>
-        <x:v>0.20600000000000002</x:v>
+        <x:v>0.26780000000000004</x:v>
       </x:c>
       <x:c r="P6" s="16" t="n">
         <x:f>ABS(D6)*N6/('Вход'!$C$6*H6)+I6</x:f>
@@ -1671,15 +1697,15 @@
       </x:c>
       <x:c r="Q6" s="16" t="n">
         <x:f>ABS(D6)*O6/('Вход'!$C$6*H6)+I6</x:f>
-        <x:v>0.03314656862745098</x:v>
+        <x:v>0.04308303921568628</x:v>
       </x:c>
       <x:c r="R6" s="16" t="n">
         <x:f>ABS(D6)*O6</x:f>
-        <x:v>0.6756800000000001</x:v>
+        <x:v>0.878384</x:v>
       </x:c>
       <x:c r="S6" s="16" t="n">
         <x:f>E6-O6</x:f>
-        <x:v>0.794</x:v>
+        <x:v>0.7322</x:v>
       </x:c>
       <x:c r="T6" s="16" t="n">
         <x:v>3.15</x:v>
@@ -1698,7 +1724,7 @@
       </x:c>
       <x:c r="Y6" s="23" t="n">
         <x:f>'Вход'!$C$6*Q6-R6</x:f>
-        <x:v>0.1198376470588235</x:v>
+        <x:v>0.1556089411764705</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="47" customHeight="1">
@@ -1735,7 +1761,7 @@
       </x:c>
       <x:c r="K7" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A7)</x:f>
-        <x:v>0.9000000000000001</x:v>
+        <x:v>1.1700000000000002</x:v>
       </x:c>
       <x:c r="L7" s="17" t="n">
         <x:f>0</x:f>
@@ -1751,7 +1777,7 @@
       </x:c>
       <x:c r="O7" s="17" t="n">
         <x:f>K7+M7</x:f>
-        <x:v>0.9000000000000001</x:v>
+        <x:v>1.1700000000000002</x:v>
       </x:c>
       <x:c r="P7" s="17" t="n">
         <x:f>ABS(D7)*N7/('Вход'!$C$6*H7)+I7</x:f>
@@ -1759,15 +1785,15 @@
       </x:c>
       <x:c r="Q7" s="17" t="n">
         <x:f>ABS(D7)*O7/('Вход'!$C$6*H7)+I7</x:f>
-        <x:v>0.13813228395061727</x:v>
+        <x:v>0.17956746913580246</x:v>
       </x:c>
       <x:c r="R7" s="17" t="n">
         <x:f>ABS(D7)*O7</x:f>
-        <x:v>2.983333333333334</x:v>
+        <x:v>3.878333333333334</x:v>
       </x:c>
       <x:c r="S7" s="17" t="n">
         <x:f>E7-O7</x:f>
-        <x:v>4.1</x:v>
+        <x:v>3.83</x:v>
       </x:c>
       <x:c r="T7" s="17" t="n">
         <x:v>3</x:v>
@@ -1786,7 +1812,7 @@
       </x:c>
       <x:c r="Y7" s="23" t="n">
         <x:f>'Вход'!$C$6*Q7-R7</x:f>
-        <x:v>0.33184148148148074</x:v>
+        <x:v>0.4312859259259252</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="47" customHeight="1">
@@ -1823,7 +1849,7 @@
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A8)</x:f>
-        <x:v>0.05</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="L8" s="16" t="n">
         <x:f>0</x:f>
@@ -1839,7 +1865,7 @@
       </x:c>
       <x:c r="O8" s="16" t="n">
         <x:f>K8+M8</x:f>
-        <x:v>0.05</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="P8" s="16" t="n">
         <x:f>ABS(D8)*N8/('Вход'!$C$6*H8)+I8</x:f>
@@ -1847,15 +1873,15 @@
       </x:c>
       <x:c r="Q8" s="16" t="n">
         <x:f>ABS(D8)*O8/('Вход'!$C$6*H8)+I8</x:f>
-        <x:v>0.012279901960784316</x:v>
+        <x:v>0.01595637254901961</x:v>
       </x:c>
       <x:c r="R8" s="16" t="n">
         <x:f>ABS(D8)*O8</x:f>
-        <x:v>0.25</x:v>
+        <x:v>0.325</x:v>
       </x:c>
       <x:c r="S8" s="16" t="n">
         <x:f>E8-O8</x:f>
-        <x:v>0.95</x:v>
+        <x:v>0.935</x:v>
       </x:c>
       <x:c r="T8" s="16" t="n">
         <x:v>4.75</x:v>
@@ -1874,7 +1900,7 @@
       </x:c>
       <x:c r="Y8" s="23" t="n">
         <x:f>'Вход'!$C$6*Q8-R8</x:f>
-        <x:v>0.044717647058823584</x:v>
+        <x:v>0.05795294117647065</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="47" customHeight="1">
@@ -1915,35 +1941,35 @@
       </x:c>
       <x:c r="L9" s="17" t="n">
         <x:f>P10+P11+P12+P13+P14+P15</x:f>
-        <x:v>1.0780293201543267</x:v>
+        <x:v>1.092870012643193</x:v>
       </x:c>
       <x:c r="M9" s="17" t="n">
         <x:f>Q10+Q11+Q12+Q13+Q14+Q15</x:f>
-        <x:v>2.0828616247931384</x:v>
+        <x:v>2.746094448779118</x:v>
       </x:c>
       <x:c r="N9" s="17" t="n">
         <x:f>J9+L9</x:f>
-        <x:v>1.0780293201543267</x:v>
+        <x:v>1.092870012643193</x:v>
       </x:c>
       <x:c r="O9" s="17" t="n">
         <x:f>K9+M9</x:f>
-        <x:v>2.0828616247931384</x:v>
+        <x:v>2.746094448779118</x:v>
       </x:c>
       <x:c r="P9" s="17" t="n">
         <x:f>ABS(D9)*N9/('Вход'!$C$6*H9)+I9</x:f>
-        <x:v>0.2757552798534508</x:v>
+        <x:v>0.2795512588900072</x:v>
       </x:c>
       <x:c r="Q9" s="17" t="n">
         <x:f>ABS(D9)*O9/('Вход'!$C$6*H9)+I9</x:f>
-        <x:v>0.5327730953310754</x:v>
+        <x:v>0.7024159808026025</x:v>
       </x:c>
       <x:c r="R9" s="17" t="n">
         <x:f>ABS(D9)*O9</x:f>
-        <x:v>11.50757485915123</x:v>
+        <x:v>15.171861185336214</x:v>
       </x:c>
       <x:c r="S9" s="17" t="n">
         <x:f>E9-O9</x:f>
-        <x:v>2.9171383752068616</x:v>
+        <x:v>2.253905551220882</x:v>
       </x:c>
       <x:c r="T9" s="17" t="n">
         <x:v>4.5</x:v>
@@ -1962,7 +1988,7 @@
       </x:c>
       <x:c r="Y9" s="23" t="n">
         <x:f>'Вход'!$C$6*Q9-R9</x:f>
-        <x:v>1.27897942879458</x:v>
+        <x:v>1.6861223539262458</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="47" customHeight="1">
@@ -1976,7 +2002,8 @@
         <x:v>U1201 TPS568215</x:v>
       </x:c>
       <x:c r="D10" s="16" t="n">
-        <x:v>1.008</x:v>
+        <x:f>'Контакты'!D61</x:f>
+        <x:v>1.0440769847634321</x:v>
       </x:c>
       <x:c r="E10" s="16" t="n">
         <x:v>8</x:v>
@@ -1999,7 +2026,7 @@
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A10)</x:f>
-        <x:v>4</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="L10" s="16" t="n">
         <x:f>0</x:f>
@@ -2015,23 +2042,23 @@
       </x:c>
       <x:c r="O10" s="16" t="n">
         <x:f>K10+M10</x:f>
-        <x:v>4</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="P10" s="16" t="n">
         <x:f>ABS(D10)*N10/(ABS(D9)*H10)+I10</x:f>
-        <x:v>0.41525266919812376</x:v>
+        <x:v>0.43009336168699</x:v>
       </x:c>
       <x:c r="Q10" s="16" t="n">
         <x:f>ABS(D10)*O10/(ABS(D9)*H10)+I10</x:f>
-        <x:v>0.8299053383962476</x:v>
+        <x:v>1.1172827403861738</x:v>
       </x:c>
       <x:c r="R10" s="16" t="n">
         <x:f>ABS(D10)*O10</x:f>
-        <x:v>4.032</x:v>
+        <x:v>5.429200320769847</x:v>
       </x:c>
       <x:c r="S10" s="16" t="n">
         <x:f>E10-O10</x:f>
-        <x:v>4</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="T10" s="16" t="n">
         <x:v>0.95</x:v>
@@ -2050,7 +2077,7 @@
       </x:c>
       <x:c r="Y10" s="23" t="n">
         <x:f>ABS(D9)*Q10-R10</x:f>
-        <x:v>0.5531331139448792</x:v>
+        <x:v>0.7436604304134935</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="47" customHeight="1">
@@ -2087,7 +2114,7 @@
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A11)</x:f>
-        <x:v>0.3</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="L11" s="17" t="n">
         <x:f>0</x:f>
@@ -2103,7 +2130,7 @@
       </x:c>
       <x:c r="O11" s="17" t="n">
         <x:f>K11+M11</x:f>
-        <x:v>0.3</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="P11" s="17" t="n">
         <x:f>ABS(D11)*N11/(ABS(D9)*H11)+I11</x:f>
@@ -2111,15 +2138,15 @@
       </x:c>
       <x:c r="Q11" s="17" t="n">
         <x:f>ABS(D11)*O11/(ABS(D9)*H11)+I11</x:f>
-        <x:v>0.11108467924949744</x:v>
+        <x:v>0.14440498302434668</x:v>
       </x:c>
       <x:c r="R11" s="17" t="n">
         <x:f>ABS(D11)*O11</x:f>
-        <x:v>0.54</x:v>
+        <x:v>0.7020000000000001</x:v>
       </x:c>
       <x:c r="S11" s="17" t="n">
         <x:f>E11-O11</x:f>
-        <x:v>2.7</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="T11" s="17" t="n">
         <x:v>1.71</x:v>
@@ -2138,7 +2165,7 @@
       </x:c>
       <x:c r="Y11" s="23" t="n">
         <x:f>ABS(D9)*Q11-R11</x:f>
-        <x:v>0.07373028671328674</x:v>
+        <x:v>0.09582119580419579</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="47" customHeight="1">
@@ -2263,7 +2290,7 @@
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A13)</x:f>
-        <x:v>0.9899999999999999</x:v>
+        <x:v>1.2870000000000001</x:v>
       </x:c>
       <x:c r="L13" s="17" t="n">
         <x:f>P25</x:f>
@@ -2271,7 +2298,7 @@
       </x:c>
       <x:c r="M13" s="17" t="n">
         <x:f>Q25</x:f>
-        <x:v>0.20003</x:v>
+        <x:v>0.26003</x:v>
       </x:c>
       <x:c r="N13" s="17" t="n">
         <x:f>J13+L13</x:f>
@@ -2279,7 +2306,7 @@
       </x:c>
       <x:c r="O13" s="17" t="n">
         <x:f>K13+M13</x:f>
-        <x:v>1.19003</x:v>
+        <x:v>1.5470300000000001</x:v>
       </x:c>
       <x:c r="P13" s="17" t="n">
         <x:f>ABS(D13)*N13/(ABS(D9)*H13)+I13</x:f>
@@ -2287,15 +2314,15 @@
       </x:c>
       <x:c r="Q13" s="17" t="n">
         <x:f>ABS(D13)*O13/(ABS(D9)*H13)+I13</x:f>
-        <x:v>0.7886000338065338</x:v>
+        <x:v>1.02516898002548</x:v>
       </x:c>
       <x:c r="R13" s="17" t="n">
         <x:f>ABS(D13)*O13</x:f>
-        <x:v>3.92114885</x:v>
+        <x:v>5.0974638500000005</x:v>
       </x:c>
       <x:c r="S13" s="17" t="n">
         <x:f>E13-O13</x:f>
-        <x:v>1.80997</x:v>
+        <x:v>1.4529699999999999</x:v>
       </x:c>
       <x:c r="T13" s="17" t="n">
         <x:v>3.15</x:v>
@@ -2314,7 +2341,7 @@
       </x:c>
       <x:c r="Y13" s="23" t="n">
         <x:f>ABS(D9)*Q13-R13</x:f>
-        <x:v>0.43577712863247875</x:v>
+        <x:v>0.5664787952991448</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="47" customHeight="1">
@@ -2351,7 +2378,7 @@
       </x:c>
       <x:c r="K14" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A14)</x:f>
-        <x:v>0.8</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="L14" s="16" t="n">
         <x:f>P16</x:f>
@@ -2359,7 +2386,7 @@
       </x:c>
       <x:c r="M14" s="16" t="n">
         <x:f>Q16</x:f>
-        <x:v>0.31112224448897796</x:v>
+        <x:v>0.40445891783567134</x:v>
       </x:c>
       <x:c r="N14" s="16" t="n">
         <x:f>J14+L14</x:f>
@@ -2367,7 +2394,7 @@
       </x:c>
       <x:c r="O14" s="16" t="n">
         <x:f>K14+M14</x:f>
-        <x:v>1.111122244488978</x:v>
+        <x:v>1.4444589178356715</x:v>
       </x:c>
       <x:c r="P14" s="16" t="n">
         <x:f>ABS(D14)*N14/(ABS(D9)*H14)+I14</x:f>
@@ -2375,15 +2402,15 @@
       </x:c>
       <x:c r="Q14" s="16" t="n">
         <x:f>ABS(D14)*O14/(ABS(D9)*H14)+I14</x:f>
-        <x:v>0.3085414226447087</x:v>
+        <x:v>0.40109874943812135</x:v>
       </x:c>
       <x:c r="R14" s="16" t="n">
         <x:f>ABS(D14)*O14</x:f>
-        <x:v>1.5000150300601203</x:v>
+        <x:v>1.9500195390781567</x:v>
       </x:c>
       <x:c r="S14" s="16" t="n">
         <x:f>E14-O14</x:f>
-        <x:v>1.888877755511022</x:v>
+        <x:v>1.5555410821643285</x:v>
       </x:c>
       <x:c r="T14" s="16" t="n">
         <x:v>1.2825</x:v>
@@ -2402,7 +2429,7 @@
       </x:c>
       <x:c r="Y14" s="23" t="n">
         <x:f>ABS(D9)*Q14-R14</x:f>
-        <x:v>0.2046414271760304</x:v>
+        <x:v>0.2660056784057627</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="47" customHeight="1">
@@ -2439,7 +2466,7 @@
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A15)</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="L15" s="17" t="n">
         <x:f>0</x:f>
@@ -2455,7 +2482,7 @@
       </x:c>
       <x:c r="O15" s="17" t="n">
         <x:f>K15+M15</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="P15" s="17" t="n">
         <x:f>ABS(D15)*N15/(ABS(D9)*H15)+I15</x:f>
@@ -2463,15 +2490,15 @@
       </x:c>
       <x:c r="Q15" s="17" t="n">
         <x:f>ABS(D15)*O15/(ABS(D9)*H15)+I15</x:f>
-        <x:v>0.04471315069615071</x:v>
+        <x:v>0.05812199590499592</x:v>
       </x:c>
       <x:c r="R15" s="17" t="n">
         <x:f>ABS(D15)*O15</x:f>
-        <x:v>0.20990000000000003</x:v>
+        <x:v>0.27287000000000006</x:v>
       </x:c>
       <x:c r="S15" s="17" t="n">
         <x:f>E15-O15</x:f>
-        <x:v>2.8</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="T15" s="17" t="n">
         <x:v>0.95</x:v>
@@ -2490,7 +2517,7 @@
       </x:c>
       <x:c r="Y15" s="23" t="n">
         <x:f>ABS(D9)*Q15-R15</x:f>
-        <x:v>0.03713509954751135</x:v>
+        <x:v>0.048247452488687836</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="47" customHeight="1">
@@ -2527,7 +2554,7 @@
       </x:c>
       <x:c r="K16" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A16)</x:f>
-        <x:v>0.31112224448897796</x:v>
+        <x:v>0.40445891783567134</x:v>
       </x:c>
       <x:c r="L16" s="16" t="n">
         <x:f>0</x:f>
@@ -2543,7 +2570,7 @@
       </x:c>
       <x:c r="O16" s="16" t="n">
         <x:f>K16+M16</x:f>
-        <x:v>0.31112224448897796</x:v>
+        <x:v>0.40445891783567134</x:v>
       </x:c>
       <x:c r="P16" s="16" t="n">
         <x:f>N16+I16</x:f>
@@ -2551,15 +2578,15 @@
       </x:c>
       <x:c r="Q16" s="16" t="n">
         <x:f>O16+I16</x:f>
-        <x:v>0.31112224448897796</x:v>
+        <x:v>0.40445891783567134</x:v>
       </x:c>
       <x:c r="R16" s="16" t="n">
         <x:f>ABS(D16)*O16</x:f>
-        <x:v>0.21000751503006013</x:v>
+        <x:v>0.2730097695390782</x:v>
       </x:c>
       <x:c r="S16" s="16" t="n">
         <x:f>E16-O16</x:f>
-        <x:v>2.688877755511022</x:v>
+        <x:v>2.5955410821643286</x:v>
       </x:c>
       <x:c r="T16" s="16"/>
       <x:c r="U16" s="16"/>
@@ -2574,7 +2601,7 @@
       </x:c>
       <x:c r="Y16" s="23" t="n">
         <x:f>ABS(D14)*Q16-R16</x:f>
-        <x:v>0.21000751503006013</x:v>
+        <x:v>0.2730097695390782</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="47" customHeight="1">
@@ -2609,7 +2636,7 @@
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A17)</x:f>
-        <x:v>0.001</x:v>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="L17" s="17" t="n">
         <x:f>0</x:f>
@@ -2625,7 +2652,7 @@
       </x:c>
       <x:c r="O17" s="17" t="n">
         <x:f>K17+M17</x:f>
-        <x:v>0.001</x:v>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="P17" s="17" t="n">
         <x:f>N17+I17</x:f>
@@ -2633,11 +2660,11 @@
       </x:c>
       <x:c r="Q17" s="17" t="n">
         <x:f>O17+I17</x:f>
-        <x:v>0.001</x:v>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="R17" s="17" t="n">
         <x:f>ABS(D17)*O17</x:f>
-        <x:v>0.000675</x:v>
+        <x:v>0.0008775000000000001</x:v>
       </x:c>
       <x:c r="S17" s="17" t="str">
         <x:f>"не определён"</x:f>
@@ -2656,7 +2683,7 @@
       </x:c>
       <x:c r="Y17" s="23" t="n">
         <x:f>ABS(D6)*Q17-R17</x:f>
-        <x:v>0.0026049999999999997</x:v>
+        <x:v>0.0033865</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="47" customHeight="1">
@@ -2701,7 +2728,7 @@
       </x:c>
       <x:c r="M18" s="16" t="n">
         <x:f>Q19</x:f>
-        <x:v>0.21083</x:v>
+        <x:v>0.27143</x:v>
       </x:c>
       <x:c r="N18" s="16" t="n">
         <x:f>J18+L18</x:f>
@@ -2709,7 +2736,7 @@
       </x:c>
       <x:c r="O18" s="16" t="n">
         <x:f>K18+M18</x:f>
-        <x:v>0.21083</x:v>
+        <x:v>0.27143</x:v>
       </x:c>
       <x:c r="P18" s="16" t="n">
         <x:f>ABS(D18)*N18/('Вход'!$C$6*H18)+I18</x:f>
@@ -2717,15 +2744,15 @@
       </x:c>
       <x:c r="Q18" s="16" t="n">
         <x:f>ABS(D18)*O18/('Вход'!$C$6*H18)+I18</x:f>
-        <x:v>0.062033823529411766</x:v>
+        <x:v>0.07985735294117646</x:v>
       </x:c>
       <x:c r="R18" s="16" t="n">
         <x:f>ABS(D18)*O18</x:f>
-        <x:v>1.26498</x:v>
+        <x:v>1.62858</x:v>
       </x:c>
       <x:c r="S18" s="16" t="n">
         <x:f>E18-O18</x:f>
-        <x:v>0.78917</x:v>
+        <x:v>0.7285699999999999</x:v>
       </x:c>
       <x:c r="T18" s="16" t="n">
         <x:v>5.5</x:v>
@@ -2744,7 +2771,7 @@
       </x:c>
       <x:c r="Y18" s="23" t="n">
         <x:f>'Вход'!$C$6*Q18-R18</x:f>
-        <x:v>0.22383176470588229</x:v>
+        <x:v>0.2879964705882352</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="47" customHeight="1">
@@ -2781,7 +2808,7 @@
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A19)</x:f>
-        <x:v>0.15</x:v>
+        <x:v>0.195</x:v>
       </x:c>
       <x:c r="L19" s="17" t="n">
         <x:f>P20</x:f>
@@ -2789,7 +2816,7 @@
       </x:c>
       <x:c r="M19" s="17" t="n">
         <x:f>Q20</x:f>
-        <x:v>0.05643000000000001</x:v>
+        <x:v>0.07203000000000001</x:v>
       </x:c>
       <x:c r="N19" s="17" t="n">
         <x:f>J19+L19</x:f>
@@ -2797,7 +2824,7 @@
       </x:c>
       <x:c r="O19" s="17" t="n">
         <x:f>K19+M19</x:f>
-        <x:v>0.20643</x:v>
+        <x:v>0.26703</x:v>
       </x:c>
       <x:c r="P19" s="17" t="n">
         <x:f>N19+I19</x:f>
@@ -2805,15 +2832,15 @@
       </x:c>
       <x:c r="Q19" s="17" t="n">
         <x:f>O19+I19</x:f>
-        <x:v>0.21083</x:v>
+        <x:v>0.27143</x:v>
       </x:c>
       <x:c r="R19" s="17" t="n">
         <x:f>ABS(D19)*O19</x:f>
-        <x:v>1.0321500000000001</x:v>
+        <x:v>1.33515</x:v>
       </x:c>
       <x:c r="S19" s="17" t="n">
         <x:f>E19-O19</x:f>
-        <x:v>0.79357</x:v>
+        <x:v>0.73297</x:v>
       </x:c>
       <x:c r="T19" s="17" t="n">
         <x:v>4.75</x:v>
@@ -2832,7 +2859,7 @@
       </x:c>
       <x:c r="Y19" s="23" t="n">
         <x:f>ABS(D18)*Q19-R19</x:f>
-        <x:v>0.23282999999999987</x:v>
+        <x:v>0.29342999999999986</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="47" customHeight="1">
@@ -2869,7 +2896,7 @@
       </x:c>
       <x:c r="K20" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A20)</x:f>
-        <x:v>0.002</x:v>
+        <x:v>0.0026000000000000003</x:v>
       </x:c>
       <x:c r="L20" s="16" t="n">
         <x:f>P26</x:f>
@@ -2877,7 +2904,7 @@
       </x:c>
       <x:c r="M20" s="16" t="n">
         <x:f>Q26</x:f>
-        <x:v>0.050030000000000005</x:v>
+        <x:v>0.06503</x:v>
       </x:c>
       <x:c r="N20" s="16" t="n">
         <x:f>J20+L20</x:f>
@@ -2885,7 +2912,7 @@
       </x:c>
       <x:c r="O20" s="16" t="n">
         <x:f>K20+M20</x:f>
-        <x:v>0.05203000000000001</x:v>
+        <x:v>0.06763000000000001</x:v>
       </x:c>
       <x:c r="P20" s="16" t="n">
         <x:f>N20+I20</x:f>
@@ -2893,15 +2920,15 @@
       </x:c>
       <x:c r="Q20" s="16" t="n">
         <x:f>O20+I20</x:f>
-        <x:v>0.05643000000000001</x:v>
+        <x:v>0.07203000000000001</x:v>
       </x:c>
       <x:c r="R20" s="16" t="n">
         <x:f>ABS(D20)*O20</x:f>
-        <x:v>0.17143885000000003</x:v>
+        <x:v>0.22284085000000003</x:v>
       </x:c>
       <x:c r="S20" s="16" t="n">
         <x:f>E20-O20</x:f>
-        <x:v>0.94797</x:v>
+        <x:v>0.93237</x:v>
       </x:c>
       <x:c r="T20" s="16" t="n">
         <x:v>3.135</x:v>
@@ -2920,7 +2947,7 @@
       </x:c>
       <x:c r="Y20" s="23" t="n">
         <x:f>ABS(D19)*Q20-R20</x:f>
-        <x:v>0.11071114999999998</x:v>
+        <x:v>0.13730915000000005</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="47" customHeight="1">
@@ -2957,7 +2984,7 @@
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A21)</x:f>
-        <x:v>0.30000000000000004</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="L21" s="17" t="n">
         <x:f>P23+P27</x:f>
@@ -2965,7 +2992,7 @@
       </x:c>
       <x:c r="M21" s="17" t="n">
         <x:f>Q23+Q27</x:f>
-        <x:v>0.0681</x:v>
+        <x:v>0.0885</x:v>
       </x:c>
       <x:c r="N21" s="17" t="n">
         <x:f>J21+L21</x:f>
@@ -2973,7 +3000,7 @@
       </x:c>
       <x:c r="O21" s="17" t="n">
         <x:f>K21+M21</x:f>
-        <x:v>0.36810000000000004</x:v>
+        <x:v>0.47850000000000004</x:v>
       </x:c>
       <x:c r="P21" s="17" t="n">
         <x:f>ABS(D21)*N21/('Вход'!$C$6*H21)+I21</x:f>
@@ -2981,15 +3008,15 @@
       </x:c>
       <x:c r="Q21" s="17" t="n">
         <x:f>ABS(D21)*O21/('Вход'!$C$6*H21)+I21</x:f>
-        <x:v>0.27050714000532344</x:v>
+        <x:v>0.35162973782273094</x:v>
       </x:c>
       <x:c r="R21" s="17" t="n">
         <x:f>ABS(D21)*O21</x:f>
-        <x:v>5.5178356561085975</x:v>
+        <x:v>7.17273665158371</x:v>
       </x:c>
       <x:c r="S21" s="17" t="n">
         <x:f>E21-O21</x:f>
-        <x:v>0.6318999999999999</x:v>
+        <x:v>0.5215</x:v>
       </x:c>
       <x:c r="T21" s="17" t="n">
         <x:v>14.25</x:v>
@@ -3008,7 +3035,7 @@
       </x:c>
       <x:c r="Y21" s="23" t="n">
         <x:f>'Вход'!$C$6*Q21-R21</x:f>
-        <x:v>0.9743357040191656</x:v>
+        <x:v>1.2663770561618328</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="47" customHeight="1">
@@ -3019,26 +3046,25 @@
         <x:v>BUS24</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>U1102 LMR51610, IBB</x:v>
+        <x:v>U1102 TEN 30-2413WIN</x:v>
       </x:c>
       <x:c r="D22" s="16" t="n">
-        <x:v>-14.990045248868777</x:v>
+        <x:v>-15</x:v>
       </x:c>
       <x:c r="E22" s="16" t="n">
-        <x:f>1-ABS(D22)/(ABS(D22)+'Вход'!$C$7*H22)</x:f>
-        <x:v>0.48996181795787663</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F22" s="16" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="G22" s="16" t="str">
-        <x:v>inverting</x:v>
+        <x:v>isolated_module</x:v>
       </x:c>
       <x:c r="H22" s="15" t="n">
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="I22" s="25" t="n">
-        <x:v>0.000025</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$D$6:$D$37,'Нагрузки'!$A$6:$A$37,A22)</x:f>
@@ -3046,7 +3072,7 @@
       </x:c>
       <x:c r="K22" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A22)</x:f>
-        <x:v>0.30000000000000004</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="L22" s="16" t="n">
         <x:f>P24</x:f>
@@ -3054,7 +3080,7 @@
       </x:c>
       <x:c r="M22" s="16" t="n">
         <x:f>Q24</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="N22" s="16" t="n">
         <x:f>J22+L22</x:f>
@@ -3062,23 +3088,23 @@
       </x:c>
       <x:c r="O22" s="16" t="n">
         <x:f>K22+M22</x:f>
-        <x:v>0.36000000000000004</x:v>
+        <x:v>0.468</x:v>
       </x:c>
       <x:c r="P22" s="16" t="n">
         <x:f>ABS(D22)*N22/('Вход'!$C$6*H22)+I22</x:f>
-        <x:v>0.09761644042232274</x:v>
+        <x:v>0.12765624999999997</x:v>
       </x:c>
       <x:c r="Q22" s="16" t="n">
         <x:f>ABS(D22)*O22/('Вход'!$C$6*H22)+I22</x:f>
-        <x:v>0.28108834841628955</x:v>
+        <x:v>0.395625</x:v>
       </x:c>
       <x:c r="R22" s="16" t="n">
         <x:f>ABS(D22)*O22</x:f>
-        <x:v>5.39641628959276</x:v>
+        <x:v>7.0200000000000005</x:v>
       </x:c>
       <x:c r="S22" s="16" t="n">
         <x:f>E22-O22</x:f>
-        <x:v>0.1299618179578766</x:v>
+        <x:v>1.532</x:v>
       </x:c>
       <x:c r="T22" s="16" t="n">
         <x:v>14.25</x:v>
@@ -3087,17 +3113,17 @@
         <x:v>15.75</x:v>
       </x:c>
       <x:c r="V22" s="12" t="str">
-        <x:v>D11: окно по модулю; IBB ток зависит от Vin</x:v>
+        <x:v>Модуль 15 В / 2 А; OCP платы ограничивает раньше. КПД 0,80 — сценарий, I0=30 мА тип.</x:v>
       </x:c>
       <x:c r="W22" s="12" t="str">
-        <x:v>https://www.ti.com/lit/an/slvafp0/slvafp0.pdf</x:v>
+        <x:v>https://www.tracopower.com/products/ten30win.pdf</x:v>
       </x:c>
       <x:c r="X22" s="12" t="str">
         <x:v>Power</x:v>
       </x:c>
       <x:c r="Y22" s="23" t="n">
         <x:f>'Вход'!$C$6*Q22-R22</x:f>
-        <x:v>1.3497040723981888</x:v>
+        <x:v>2.4750000000000005</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="47" customHeight="1">
@@ -3132,7 +3158,7 @@
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A23)</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="L23" s="17" t="n">
         <x:f>0</x:f>
@@ -3148,7 +3174,7 @@
       </x:c>
       <x:c r="O23" s="17" t="n">
         <x:f>K23+M23</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="P23" s="17" t="n">
         <x:f>N23+I23</x:f>
@@ -3156,11 +3182,11 @@
       </x:c>
       <x:c r="Q23" s="17" t="n">
         <x:f>O23+I23</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="R23" s="17" t="n">
         <x:f>ABS(D23)*O23</x:f>
-        <x:v>0.8994027149321265</x:v>
+        <x:v>1.1692235294117646</x:v>
       </x:c>
       <x:c r="S23" s="17" t="str">
         <x:f>"не определён"</x:f>
@@ -3176,7 +3202,7 @@
         <x:v>D11: по модулю; сопротивление MOSFET ещё не включено</x:v>
       </x:c>
       <x:c r="W23" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
       </x:c>
       <x:c r="X23" s="13" t="str">
         <x:v>Power</x:v>
@@ -3197,7 +3223,7 @@
         <x:v>Ключи листа 2200; N15</x:v>
       </x:c>
       <x:c r="D24" s="16" t="n">
-        <x:v>-14.990045248868777</x:v>
+        <x:v>-15</x:v>
       </x:c>
       <x:c r="E24" s="16"/>
       <x:c r="F24" s="16" t="n">
@@ -3218,7 +3244,7 @@
       </x:c>
       <x:c r="K24" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A24)</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="L24" s="16" t="n">
         <x:f>0</x:f>
@@ -3234,7 +3260,7 @@
       </x:c>
       <x:c r="O24" s="16" t="n">
         <x:f>K24+M24</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="P24" s="16" t="n">
         <x:f>N24+I24</x:f>
@@ -3242,11 +3268,11 @@
       </x:c>
       <x:c r="Q24" s="16" t="n">
         <x:f>O24+I24</x:f>
-        <x:v>0.06</x:v>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="R24" s="16" t="n">
         <x:f>ABS(D24)*O24</x:f>
-        <x:v>0.8994027149321265</x:v>
+        <x:v>1.17</x:v>
       </x:c>
       <x:c r="S24" s="16" t="str">
         <x:f>"не определён"</x:f>
@@ -3262,7 +3288,7 @@
         <x:v>D11: по модулю; сопротивление MOSFET ещё не включено</x:v>
       </x:c>
       <x:c r="W24" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
       </x:c>
       <x:c r="X24" s="12" t="str">
         <x:v>Power</x:v>
@@ -3306,7 +3332,7 @@
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A25)</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="L25" s="17" t="n">
         <x:f>0</x:f>
@@ -3322,7 +3348,7 @@
       </x:c>
       <x:c r="O25" s="17" t="n">
         <x:f>K25+M25</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="P25" s="17" t="n">
         <x:f>N25+I25</x:f>
@@ -3330,15 +3356,15 @@
       </x:c>
       <x:c r="Q25" s="17" t="n">
         <x:f>O25+I25</x:f>
-        <x:v>0.20003</x:v>
+        <x:v>0.26003</x:v>
       </x:c>
       <x:c r="R25" s="17" t="n">
         <x:f>ABS(D25)*O25</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="S25" s="17" t="n">
         <x:f>E25-O25</x:f>
-        <x:v>0.3</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="T25" s="17" t="n">
         <x:v>2.375</x:v>
@@ -3350,14 +3376,14 @@
         <x:v>TI DP83867 VDDA2P5</x:v>
       </x:c>
       <x:c r="W25" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
       </x:c>
       <x:c r="X25" s="13" t="str">
         <x:v>Control</x:v>
       </x:c>
       <x:c r="Y25" s="23" t="n">
         <x:f>ABS(D13)*Q25-R25</x:f>
-        <x:v>0.15909885</x:v>
+        <x:v>0.20679884999999987</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="47" customHeight="1">
@@ -3394,7 +3420,7 @@
       </x:c>
       <x:c r="K26" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A26)</x:f>
-        <x:v>0.05</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="L26" s="16" t="n">
         <x:f>0</x:f>
@@ -3410,7 +3436,7 @@
       </x:c>
       <x:c r="O26" s="16" t="n">
         <x:f>K26+M26</x:f>
-        <x:v>0.05</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="P26" s="16" t="n">
         <x:f>N26+I26</x:f>
@@ -3418,15 +3444,15 @@
       </x:c>
       <x:c r="Q26" s="16" t="n">
         <x:f>O26+I26</x:f>
-        <x:v>0.050030000000000005</x:v>
+        <x:v>0.06503</x:v>
       </x:c>
       <x:c r="R26" s="16" t="n">
         <x:f>ABS(D26)*O26</x:f>
-        <x:v>0.09000000000000001</x:v>
+        <x:v>0.117</x:v>
       </x:c>
       <x:c r="S26" s="16" t="n">
         <x:f>E26-O26</x:f>
-        <x:v>0.45</x:v>
+        <x:v>0.435</x:v>
       </x:c>
       <x:c r="T26" s="16" t="n">
         <x:v>1.71</x:v>
@@ -3438,14 +3464,14 @@
         <x:v>D11: проектное окно, сверить AD4003</x:v>
       </x:c>
       <x:c r="W26" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
       </x:c>
       <x:c r="X26" s="12" t="str">
         <x:v>Control</x:v>
       </x:c>
       <x:c r="Y26" s="23" t="n">
         <x:f>ABS(D20)*Q26-R26</x:f>
-        <x:v>0.07484885000000001</x:v>
+        <x:v>0.09727385000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="47" customHeight="1">
@@ -3482,7 +3508,7 @@
       </x:c>
       <x:c r="K27" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A27)</x:f>
-        <x:v>0.003</x:v>
+        <x:v>0.0039000000000000003</x:v>
       </x:c>
       <x:c r="L27" s="17" t="n">
         <x:f>P28</x:f>
@@ -3490,7 +3516,7 @@
       </x:c>
       <x:c r="M27" s="17" t="n">
         <x:f>Q28</x:f>
-        <x:v>0.005</x:v>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="N27" s="17" t="n">
         <x:f>J27+L27</x:f>
@@ -3498,7 +3524,7 @@
       </x:c>
       <x:c r="O27" s="17" t="n">
         <x:f>K27+M27</x:f>
-        <x:v>0.008</x:v>
+        <x:v>0.010400000000000001</x:v>
       </x:c>
       <x:c r="P27" s="17" t="n">
         <x:f>N27+I27</x:f>
@@ -3506,15 +3532,15 @@
       </x:c>
       <x:c r="Q27" s="17" t="n">
         <x:f>O27+I27</x:f>
-        <x:v>0.0081</x:v>
+        <x:v>0.0105</x:v>
       </x:c>
       <x:c r="R27" s="17" t="n">
         <x:f>ABS(D27)*O27</x:f>
-        <x:v>0.096</x:v>
+        <x:v>0.12480000000000002</x:v>
       </x:c>
       <x:c r="S27" s="17" t="n">
         <x:f>E27-O27</x:f>
-        <x:v>0.092</x:v>
+        <x:v>0.0896</x:v>
       </x:c>
       <x:c r="T27" s="17" t="n">
         <x:v>11.4</x:v>
@@ -3526,14 +3552,14 @@
         <x:v>D11: проектное окно</x:v>
       </x:c>
       <x:c r="W27" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
       </x:c>
       <x:c r="X27" s="13" t="str">
         <x:v>Control</x:v>
       </x:c>
       <x:c r="Y27" s="23" t="n">
         <x:f>ABS(D21)*Q27-R27</x:f>
-        <x:v>0.02541936651583708</x:v>
+        <x:v>0.032595475113122135</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="47" customHeight="1">
@@ -3568,7 +3594,7 @@
       </x:c>
       <x:c r="K28" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A28)</x:f>
-        <x:v>0.005</x:v>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="L28" s="16" t="n">
         <x:f>0</x:f>
@@ -3584,7 +3610,7 @@
       </x:c>
       <x:c r="O28" s="16" t="n">
         <x:f>K28+M28</x:f>
-        <x:v>0.005</x:v>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="P28" s="16" t="n">
         <x:f>N28+I28</x:f>
@@ -3592,11 +3618,11 @@
       </x:c>
       <x:c r="Q28" s="16" t="n">
         <x:f>O28+I28</x:f>
-        <x:v>0.005</x:v>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="R28" s="16" t="n">
         <x:f>ABS(D28)*O28</x:f>
-        <x:v>0.025</x:v>
+        <x:v>0.0325</x:v>
       </x:c>
       <x:c r="S28" s="16" t="str">
         <x:f>"не определён"</x:f>
@@ -3608,14 +3634,14 @@
         <x:v>Точность, шум и динамика опоры рассматриваются отдельно</x:v>
       </x:c>
       <x:c r="W28" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
       </x:c>
       <x:c r="X28" s="12" t="str">
         <x:v>Control</x:v>
       </x:c>
       <x:c r="Y28" s="23" t="n">
         <x:f>ABS(D27)*Q28-R28</x:f>
-        <x:v>0.034999999999999996</x:v>
+        <x:v>0.04550000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3887,7 +3913,7 @@
         <x:v>Запас источника, А</x:v>
       </x:c>
       <x:c r="M5" s="8" t="str">
-        <x:v>Пуск через J400, А</x:v>
+        <x:v>Пуск Control, все вводы, А</x:v>
       </x:c>
       <x:c r="N5" s="8" t="str">
         <x:v>Основание</x:v>
@@ -3901,11 +3927,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="16" t="n">
-        <x:v>108.2</x:v>
+        <x:v>108.4</x:v>
       </x:c>
       <x:c r="D6" s="16" t="n">
         <x:f>B6+C6</x:f>
-        <x:v>108.2</x:v>
+        <x:v>108.4</x:v>
       </x:c>
       <x:c r="E6" s="16" t="n">
         <x:f>'Вход'!$C$9</x:f>
@@ -3924,19 +3950,19 @@
       </x:c>
       <x:c r="I6" s="16" t="n">
         <x:f>D6*E6*ABS('Шины'!D6)/(1000*F6)</x:f>
-        <x:v>0.08517504000000001</x:v>
+        <x:v>0.08533248</x:v>
       </x:c>
       <x:c r="J6" s="16" t="n">
         <x:f>G6+H6+I6</x:f>
-        <x:v>0.16635604</x:v>
+        <x:v>0.16651348</x:v>
       </x:c>
       <x:c r="K6" s="16" t="n">
         <x:f>ABS('Шины'!D6)*J6/('Вход'!$C$6*'Шины'!H6)+'Шины'!I6</x:f>
-        <x:v>0.0267724417254902</x:v>
+        <x:v>0.026797755607843136</x:v>
       </x:c>
       <x:c r="L6" s="16" t="n">
         <x:f>'Шины'!E6-J6</x:f>
-        <x:v>0.83364396</x:v>
+        <x:v>0.83348652</x:v>
       </x:c>
       <x:c r="M6" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A6,'Нагрузки'!$B$6:$B$37,"Control")+0+B6*E6*ABS('Шины'!D6)/(1000*F6)</x:f>
@@ -4079,7 +4105,7 @@
       </x:c>
       <x:c r="H9" s="17" t="n">
         <x:f>K10+K11+K12+K13+K14+K15</x:f>
-        <x:v>1.1227086135362767</x:v>
+        <x:v>1.1394844203251477</x:v>
       </x:c>
       <x:c r="I9" s="17" t="n">
         <x:f>D9*E9*ABS('Шины'!D9)/(1000*F9)</x:f>
@@ -4087,15 +4113,15 @@
       </x:c>
       <x:c r="J9" s="17" t="n">
         <x:f>G9+H9+I9</x:f>
-        <x:v>1.6896946044865029</x:v>
+        <x:v>1.7064704112753741</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:f>ABS('Шины'!D9)*J9/('Вход'!$C$6*'Шины'!H9)+'Шины'!I9</x:f>
-        <x:v>0.4322081272159418</x:v>
+        <x:v>0.43649907327116466</x:v>
       </x:c>
       <x:c r="L9" s="17" t="n">
         <x:f>'Шины'!E9-J9</x:f>
-        <x:v>3.310305395513497</x:v>
+        <x:v>3.293529588724626</x:v>
       </x:c>
       <x:c r="M9" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A9,'Нагрузки'!$B$6:$B$37,"Control")+0+B9*E9*ABS('Шины'!D9)/(1000*F9)</x:f>
@@ -4110,10 +4136,10 @@
         <x:v>CORE1V0</x:v>
       </x:c>
       <x:c r="B10" s="16" t="n">
-        <x:v>844.3900000000008</x:v>
+        <x:v>844.390000000001</x:v>
       </x:c>
       <x:c r="C10" s="16" t="n">
-        <x:v>281.9999999999993</x:v>
+        <x:v>281.9999999999991</x:v>
       </x:c>
       <x:c r="D10" s="16" t="n">
         <x:f>B10+C10</x:f>
@@ -4136,23 +4162,23 @@
       </x:c>
       <x:c r="I10" s="16" t="n">
         <x:f>D10*E10*ABS('Шины'!D10)/(1000*F10)</x:f>
-        <x:v>0.6193097018181818</x:v>
+        <x:v>0.6414752044732813</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
         <x:f>G10+H10+I10</x:f>
-        <x:v>1.6193097018181817</x:v>
+        <x:v>1.6414752044732812</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:f>ABS('Шины'!D10)*J10/(ABS('Шины'!D9)*'Шины'!H10)+'Шины'!I10</x:f>
-        <x:v>0.3363255450586634</x:v>
+        <x:v>0.3531013518475344</x:v>
       </x:c>
       <x:c r="L10" s="16" t="n">
         <x:f>'Шины'!E10-J10</x:f>
-        <x:v>6.380690298181818</x:v>
+        <x:v>6.358524795526719</x:v>
       </x:c>
       <x:c r="M10" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A10,'Нагрузки'!$B$6:$B$37,"Control")+0+B10*E10*ABS('Шины'!D10)/(1000*F10)</x:f>
-        <x:v>1.464260974545455</x:v>
+        <x:v>1.480877180998761</x:v>
       </x:c>
       <x:c r="N10" s="12" t="str">
         <x:v>Схема: C1203=22 нФ, около 2,2 мс; FPGA до конфигурации.</x:v>
@@ -4269,10 +4295,10 @@
         <x:v>IO3V3</x:v>
       </x:c>
       <x:c r="B13" s="17" t="n">
-        <x:v>404.1100000000002</x:v>
+        <x:v>404.11000000000206</x:v>
       </x:c>
       <x:c r="C13" s="17" t="n">
-        <x:v>46.99999999999983</x:v>
+        <x:v>46.999999999997954</x:v>
       </x:c>
       <x:c r="D13" s="17" t="n">
         <x:f>B13+C13</x:f>
@@ -4311,7 +4337,7 @@
       </x:c>
       <x:c r="M13" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A13,'Нагрузки'!$B$6:$B$37,"Control")+K25+B13*E13*ABS('Шины'!D13)/(1000*F13)</x:f>
-        <x:v>0.8757401880000002</x:v>
+        <x:v>0.8757401880000016</x:v>
       </x:c>
       <x:c r="N13" s="13" t="str">
         <x:v>Схема: SS/TR=10 нФ, около 5 мс; подтвердить допуск и нагрузку.</x:v>
@@ -4322,14 +4348,14 @@
         <x:v>DDR1V35</x:v>
       </x:c>
       <x:c r="B14" s="16" t="n">
-        <x:v>140.9199999999999</x:v>
+        <x:v>140.91999999999987</x:v>
       </x:c>
       <x:c r="C14" s="16" t="n">
-        <x:v>57.000000000000085</x:v>
+        <x:v>57.00000000000014</x:v>
       </x:c>
       <x:c r="D14" s="16" t="n">
         <x:f>B14+C14</x:f>
-        <x:v>197.92</x:v>
+        <x:v>197.92000000000002</x:v>
       </x:c>
       <x:c r="E14" s="16" t="n">
         <x:f>'Вход'!$C$9</x:f>
@@ -4348,7 +4374,7 @@
       </x:c>
       <x:c r="I14" s="16" t="n">
         <x:f>D14*E14*ABS('Шины'!D14)/(1000*F14)</x:f>
-        <x:v>0.06412607999999999</x:v>
+        <x:v>0.06412608000000002</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
         <x:f>G14+H14+I14</x:f>
@@ -4715,7 +4741,7 @@
       </x:c>
       <x:c r="H21" s="17" t="n">
         <x:f>K23+K27</x:f>
-        <x:v>0.09954583529411765</x:v>
+        <x:v>0.09954583529411763</x:v>
       </x:c>
       <x:c r="I21" s="17" t="n">
         <x:f>D21*E21*ABS('Шины'!D21)/(1000*F21)</x:f>
@@ -4735,7 +4761,7 @@
       </x:c>
       <x:c r="M21" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A21,'Нагрузки'!$B$6:$B$37,"Control")+K27+B21*E21*ABS('Шины'!D21)/(1000*F21)</x:f>
-        <x:v>0.36438972307692336</x:v>
+        <x:v>0.3643897230769233</x:v>
       </x:c>
       <x:c r="N21" s="13" t="str">
         <x:v>D19: 5 мс условно; действительную рампу и порядок EN подтвердить.</x:v>
@@ -4749,11 +4775,11 @@
         <x:v>57.90000000000008</x:v>
       </x:c>
       <x:c r="C22" s="16" t="n">
-        <x:v>70.99999999999993</x:v>
+        <x:v>66.09999999999992</x:v>
       </x:c>
       <x:c r="D22" s="16" t="n">
         <x:f>B22+C22</x:f>
-        <x:v>128.9</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E22" s="16" t="n">
         <x:f>'Вход'!$C$9</x:f>
@@ -4768,30 +4794,30 @@
       </x:c>
       <x:c r="H22" s="16" t="n">
         <x:f>K24</x:f>
-        <x:v>0.06644583529411763</x:v>
+        <x:v>0.06648</x:v>
       </x:c>
       <x:c r="I22" s="16" t="n">
         <x:f>D22*E22*ABS('Шины'!D22)/(1000*F22)</x:f>
-        <x:v>0.4637320398190045</x:v>
+        <x:v>0.4463999999999999</x:v>
       </x:c>
       <x:c r="J22" s="16" t="n">
         <x:f>G22+H22+I22</x:f>
-        <x:v>0.6351778751131222</x:v>
+        <x:v>0.61788</x:v>
       </x:c>
       <x:c r="K22" s="16" t="n">
         <x:f>ABS('Шины'!D22)*J22/('Вход'!$C$6*'Шины'!H22)+'Шины'!I22</x:f>
-        <x:v>0.4959283900534386</x:v>
+        <x:v>0.5127187499999999</x:v>
       </x:c>
       <x:c r="L22" s="16" t="n">
         <x:f>'Шины'!E22-J22</x:f>
-        <x:v>-0.14521605715524555</x:v>
+        <x:v>1.38212</x:v>
       </x:c>
       <x:c r="M22" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A22,'Нагрузки'!$B$6:$B$37,"Control")+0+B22*E22*ABS('Шины'!D22)/(1000*F22)</x:f>
-        <x:v>0.3133016687782808</x:v>
+        <x:v>0.3134400000000003</x:v>
       </x:c>
       <x:c r="N22" s="12" t="str">
-        <x:v>D19: 5 мс условно; действительную рампу и порядок EN подтвердить.</x:v>
+        <x:v>5 мс — условный сценарий, не характеристика TEN 30WIN. Сравнить с OCP и проверить фактический пуск.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="44" customHeight="1">
@@ -4878,15 +4904,15 @@
       </x:c>
       <x:c r="I24" s="16" t="n">
         <x:f>D24*E24*ABS('Шины'!D24)/(1000*F24)</x:f>
-        <x:v>0.051445835294117635</x:v>
+        <x:v>0.05148</x:v>
       </x:c>
       <x:c r="J24" s="16" t="n">
         <x:f>G24+H24+I24</x:f>
-        <x:v>0.06644583529411763</x:v>
+        <x:v>0.06648</x:v>
       </x:c>
       <x:c r="K24" s="16" t="n">
         <x:f>J24+'Шины'!I24</x:f>
-        <x:v>0.06644583529411763</x:v>
+        <x:v>0.06648</x:v>
       </x:c>
       <x:c r="L24" s="16" t="str">
         <x:f>"не определён"</x:f>
@@ -4894,10 +4920,10 @@
       </x:c>
       <x:c r="M24" s="16" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A24,'Нагрузки'!$B$6:$B$37,"Control")+0+B24*E24*ABS('Шины'!D24)/(1000*F24)</x:f>
-        <x:v>0.04953706425339366</x:v>
+        <x:v>0.04955999999999999</x:v>
       </x:c>
       <x:c r="N24" s="12" t="str">
-        <x:v>D19: 5 мс условно; действительную рампу и порядок EN подтвердить.</x:v>
+        <x:v>Условная рампа и одновременный пуск. Порядок CMD_N15 и PROG_N15 ещё проверить.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="44" customHeight="1">
@@ -5033,7 +5059,7 @@
       </x:c>
       <x:c r="H27" s="17" t="n">
         <x:f>K28</x:f>
-        <x:v>0.025240000000000005</x:v>
+        <x:v>0.02524</x:v>
       </x:c>
       <x:c r="I27" s="17" t="n">
         <x:f>D27*E27*ABS('Шины'!D27)/(1000*F27)</x:f>
@@ -5041,11 +5067,11 @@
       </x:c>
       <x:c r="J27" s="17" t="n">
         <x:f>G27+H27+I27</x:f>
-        <x:v>0.03300000000000001</x:v>
+        <x:v>0.033</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
         <x:f>J27+'Шины'!I27</x:f>
-        <x:v>0.03310000000000001</x:v>
+        <x:v>0.033100000000000004</x:v>
       </x:c>
       <x:c r="L27" s="17" t="n">
         <x:f>'Шины'!E27-J27</x:f>
@@ -5053,7 +5079,7 @@
       </x:c>
       <x:c r="M27" s="17" t="n">
         <x:f>SUMIFS('Нагрузки'!$F$6:$F$37,'Нагрузки'!$A$6:$A$37,A27,'Нагрузки'!$B$6:$B$37,"Control")+K28+B27*E27*ABS('Шины'!D27)/(1000*F27)</x:f>
-        <x:v>0.03300000000000001</x:v>
+        <x:v>0.033</x:v>
       </x:c>
       <x:c r="N27" s="13" t="str">
         <x:v>D19: 5 мс условно; действительную рампу и порядок EN подтвердить.</x:v>
@@ -5067,11 +5093,11 @@
         <x:v>20.200000000000003</x:v>
       </x:c>
       <x:c r="C28" s="16" t="n">
-        <x:v>0</x:v>
+        <x:v>-3.552713678800501e-15</x:v>
       </x:c>
       <x:c r="D28" s="16" t="n">
         <x:f>B28+C28</x:f>
-        <x:v>20.200000000000003</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="E28" s="16" t="n">
         <x:f>'Вход'!$C$9</x:f>
@@ -5090,15 +5116,15 @@
       </x:c>
       <x:c r="I28" s="16" t="n">
         <x:f>D28*E28*ABS('Шины'!D28)/(1000*F28)</x:f>
-        <x:v>0.024240000000000005</x:v>
+        <x:v>0.024239999999999998</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
         <x:f>G28+H28+I28</x:f>
-        <x:v>0.025240000000000005</x:v>
+        <x:v>0.02524</x:v>
       </x:c>
       <x:c r="K28" s="16" t="n">
         <x:f>J28+'Шины'!I28</x:f>
-        <x:v>0.025240000000000005</x:v>
+        <x:v>0.02524</x:v>
       </x:c>
       <x:c r="L28" s="16" t="str">
         <x:f>"не определён"</x:f>
@@ -5209,18 +5235,18 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="21" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="21" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="21" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="63" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="58" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="85" hidden="0" customWidth="1"/>
   </x:cols>
@@ -5238,12 +5264,12 @@
       <x:c r="J1" s="2"/>
       <x:c r="K1" s="2"/>
       <x:c r="L1" s="2"/>
-      <x:c r="M1" s="2"/>
-      <x:c r="N1" s="2"/>
+      <x:c r="M1"/>
+      <x:c r="N1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>Контакты питания и возврата GND</x:v>
+        <x:v>Распределённые вводы: ток контактов</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -5256,12 +5282,12 @@
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
-      <x:c r="M2" s="2"/>
-      <x:c r="N2" s="2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="4" t="str">
-        <x:v>Параметры тока и сопротивления заданы на листе «Вход». Конкретная пара разъёмов и паспортный ток не утверждены.</x:v>
+      <x:c r="A3" s="2" t="str">
+        <x:v>Для общих шин — весь ток Control в каждой зоне по отдельности. Это консервативные оценки; их нельзя суммировать как разные нагрузки.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -5274,8 +5300,8 @@
       <x:c r="J3" s="2"/>
       <x:c r="K3" s="2"/>
       <x:c r="L3" s="2"/>
-      <x:c r="M3" s="2"/>
-      <x:c r="N3" s="2"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -5290,1023 +5316,2547 @@
       <x:c r="J4" s="2"/>
       <x:c r="K4" s="2"/>
       <x:c r="L4" s="2"/>
-      <x:c r="M4" s="2"/>
-      <x:c r="N4" s="2"/>
-    </x:row>
-    <x:row r="5" ht="40" customHeight="1">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
+      <x:c r="A5" s="41" t="str">
+        <x:v>Зона / пара</x:v>
+      </x:c>
+      <x:c r="B5" s="41" t="str">
         <x:v>Шина</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>Контакты J400</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>N питания</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>N GND в модели</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>Пик Control, А</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="str">
-        <x:v>Пуск Control, А</x:v>
-      </x:c>
-      <x:c r="G5" s="8" t="str">
-        <x:v>Расчётный ток, А</x:v>
-      </x:c>
-      <x:c r="H5" s="8" t="str">
-        <x:v>На худший контакт, А</x:v>
-      </x:c>
-      <x:c r="I5" s="8" t="str">
-        <x:v>N по заданному бюджету</x:v>
-      </x:c>
-      <x:c r="J5" s="8" t="str">
-        <x:v>Петля пути, мОм</x:v>
-      </x:c>
-      <x:c r="K5" s="8" t="str">
-        <x:v>Падение пути, мВ</x:v>
-      </x:c>
-      <x:c r="L5" s="8" t="str">
-        <x:v>Доступно на путь, мВ</x:v>
-      </x:c>
-      <x:c r="M5" s="8" t="str">
-        <x:v>Запас по падению, мВ</x:v>
-      </x:c>
-      <x:c r="N5" s="8" t="str">
-        <x:v>Статус / следующий шаг</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="47" customHeight="1">
-      <x:c r="A6" s="9" t="str">
+      <x:c r="C5" s="41" t="str">
+        <x:v>Контакты питания</x:v>
+      </x:c>
+      <x:c r="D5" s="41" t="str">
+        <x:v>Силовых, шт.</x:v>
+      </x:c>
+      <x:c r="E5" s="41" t="str">
+        <x:v>GND пары, шт.</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="str">
+        <x:v>Пик ветви, А</x:v>
+      </x:c>
+      <x:c r="G5" s="41" t="str">
+        <x:v>Пуск ветви, А</x:v>
+      </x:c>
+      <x:c r="H5" s="41" t="str">
+        <x:v>Расчётный, А</x:v>
+      </x:c>
+      <x:c r="I5" s="41" t="str">
+        <x:v>На контакт, А</x:v>
+      </x:c>
+      <x:c r="J5" s="41" t="str">
+        <x:v>Запас к 1 А, А</x:v>
+      </x:c>
+      <x:c r="K5" s="41" t="str">
+        <x:v>Основание</x:v>
+      </x:c>
+      <x:c r="L5" s="41" t="str">
+        <x:v>Что проверить</x:v>
+      </x:c>
+      <x:c r="M5"/>
+      <x:c r="N5"/>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
+      <x:c r="A6" s="13" t="str">
+        <x:v>SUPERVISION: J4901/J400</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
         <x:v>AON</x:v>
       </x:c>
-      <x:c r="B6" s="9" t="str">
+      <x:c r="C6" s="13" t="str">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A6,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.005</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="n">
+      <x:c r="E6" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"AON",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="G6" s="17" t="n">
         <x:f>'Пуск'!M6</x:f>
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="G6" s="16" t="n">
-        <x:f>MAX(E6,F6)</x:f>
-        <x:v>0.005</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="n">
-        <x:f>G6/C6*'Вход'!$C$14</x:f>
-        <x:v>0.00625</x:v>
-      </x:c>
-      <x:c r="I6" s="20" t="n">
-        <x:f>ROUNDUP(G6*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
+      <x:c r="H6" s="17" t="n">
+        <x:f>MAX(F6,G6)</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="n">
+        <x:f>H6/D6*'Вход'!$C$14</x:f>
+        <x:v>0.008125</x:v>
+      </x:c>
+      <x:c r="J6" s="17" t="n">
+        <x:f>'Вход'!$C$15-I6</x:f>
+        <x:v>0.991875</x:v>
+      </x:c>
+      <x:c r="K6" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L6" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M6"/>
+      <x:c r="N6"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="13" t="str">
+        <x:v>FPGA: J4902/J401</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>CORE1V0</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>1, 3, 5, 7, 9, 11, 13, 15</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"CORE1V0",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="n">
+        <x:f>'Пуск'!M10</x:f>
+        <x:v>1.480877180998761</x:v>
+      </x:c>
+      <x:c r="H7" s="17" t="n">
+        <x:f>MAX(F7,G7)</x:f>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="n">
+        <x:f>H7/D7*'Вход'!$C$14</x:f>
+        <x:v>0.8125</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:f>'Вход'!$C$15-I7</x:f>
+        <x:v>0.1875</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="13" t="str">
+        <x:v>FPGA: J4902/J401</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="str">
+        <x:v>AUX1V8</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>19, 21</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F8" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"AUX1V8",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="G8" s="17" t="n">
+        <x:f>'Пуск'!M11</x:f>
+        <x:v>0.1774104</x:v>
+      </x:c>
+      <x:c r="H8" s="17" t="n">
+        <x:f>MAX(F8,G8)</x:f>
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="I8" s="17" t="n">
+        <x:f>H8/D8*'Вход'!$C$14</x:f>
+        <x:v>0.24375000000000002</x:v>
+      </x:c>
+      <x:c r="J8" s="17" t="n">
+        <x:f>'Вход'!$C$15-I8</x:f>
+        <x:v>0.75625</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L8" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M8"/>
+      <x:c r="N8"/>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="13" t="str">
+        <x:v>FPGA: J4902/J401</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>23, 25</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G9" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H9" s="17" t="n">
+        <x:f>MAX(F9,G9)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="n">
+        <x:f>H9/D9*'Вход'!$C$14</x:f>
+        <x:v>0.9668937500000001</x:v>
+      </x:c>
+      <x:c r="J9" s="17" t="n">
+        <x:f>'Вход'!$C$15-I9</x:f>
+        <x:v>0.03310624999999989</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L9" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M9"/>
+      <x:c r="N9"/>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
+      <x:c r="A10" s="13" t="str">
+        <x:v>DDR: J4903/J402</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>DDR1V35</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>1, 3, 5</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"DDR1V35",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>1.04</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="n">
+        <x:f>'Пуск'!M14</x:f>
+        <x:v>0.19565807999999996</x:v>
+      </x:c>
+      <x:c r="H10" s="17" t="n">
+        <x:f>MAX(F10,G10)</x:f>
+        <x:v>1.04</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="n">
+        <x:f>H10/D10*'Вход'!$C$14</x:f>
+        <x:v>0.43333333333333335</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="n">
+        <x:f>'Вход'!$C$15-I10</x:f>
+        <x:v>0.5666666666666667</x:v>
+      </x:c>
+      <x:c r="K10" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L10" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M10"/>
+      <x:c r="N10"/>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
+      <x:c r="A11" s="13" t="str">
+        <x:v>DDR: J4903/J402</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="str">
+        <x:v>VTT</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="str">
+        <x:v>7, 9</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"VTT",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.40445891783567134</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="n">
+        <x:f>'Пуск'!M16</x:f>
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="H11" s="17" t="n">
+        <x:f>MAX(F11,G11)</x:f>
+        <x:v>0.40445891783567134</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="n">
+        <x:f>H11/D11*'Вход'!$C$14</x:f>
+        <x:v>0.2527868236472946</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="n">
+        <x:f>'Вход'!$C$15-I11</x:f>
+        <x:v>0.7472131763527055</x:v>
+      </x:c>
+      <x:c r="K11" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L11" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M11"/>
+      <x:c r="N11"/>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="13" t="str">
+        <x:v>DDR: J4903/J402</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>DDR_VREF</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="16" t="n">
-        <x:f>'Вход'!$C$12/C6+'Вход'!$C$12/D6+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K6" s="16" t="n">
-        <x:f>E6*J6</x:f>
-        <x:v>0.125</x:v>
-      </x:c>
-      <x:c r="L6" s="16" t="n">
-        <x:f>(ABS('Шины'!D6)*(1-'Вход'!$C$10)-'Шины'!T6-'Вход'!$C$11-'Шины'!O6*'Шины'!F6)*1000</x:f>
-        <x:v>33.80000000000001</x:v>
-      </x:c>
-      <x:c r="M6" s="16" t="n">
-        <x:f>L6-K6</x:f>
-        <x:v>33.67500000000001</x:v>
-      </x:c>
-      <x:c r="N6" s="12" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="47" customHeight="1">
-      <x:c r="A7" s="2" t="str">
+      <x:c r="E12" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"DDR_VREF",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.0013000000000000002</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="n">
+        <x:f>'Пуск'!M17</x:f>
+        <x:v>0.0001648</x:v>
+      </x:c>
+      <x:c r="H12" s="17" t="n">
+        <x:f>MAX(F12,G12)</x:f>
+        <x:v>0.0013000000000000002</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="n">
+        <x:f>H12/D12*'Вход'!$C$14</x:f>
+        <x:v>0.0016250000000000001</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:f>'Вход'!$C$15-I12</x:f>
+        <x:v>0.998375</x:v>
+      </x:c>
+      <x:c r="K12" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L12" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M12"/>
+      <x:c r="N12"/>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="13" t="str">
+        <x:v>DDR: J4903/J402</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H13" s="17" t="n">
+        <x:f>MAX(F13,G13)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="n">
+        <x:f>H13/D13*'Вход'!$C$14</x:f>
+        <x:v>1.9337875000000002</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:f>'Вход'!$C$15-I13</x:f>
+        <x:v>-0.9337875000000002</x:v>
+      </x:c>
+      <x:c r="K13" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L13" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M13"/>
+      <x:c r="N13"/>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="13" t="str">
+        <x:v>MCU: J4904/J403</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
         <x:v>SYS3V3</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="str">
-        <x:v>3, 5</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A7,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.8800000000000001</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="n">
+      <x:c r="C14" s="13" t="str">
+        <x:v>1, 3, 5</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"SYS3V3",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>1.1440000000000001</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="n">
         <x:f>'Пуск'!M7</x:f>
         <x:v>0.1733097777777778</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="n">
-        <x:f>MAX(E7,F7)</x:f>
-        <x:v>0.8800000000000001</x:v>
-      </x:c>
-      <x:c r="H7" s="17" t="n">
-        <x:f>G7/C7*'Вход'!$C$14</x:f>
-        <x:v>0.55</x:v>
-      </x:c>
-      <x:c r="I7" s="21" t="n">
-        <x:f>ROUNDUP(G7*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
+      <x:c r="H14" s="17" t="n">
+        <x:f>MAX(F14,G14)</x:f>
+        <x:v>1.1440000000000001</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="n">
+        <x:f>H14/D14*'Вход'!$C$14</x:f>
+        <x:v>0.4766666666666667</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:f>'Вход'!$C$15-I14</x:f>
+        <x:v>0.5233333333333333</x:v>
+      </x:c>
+      <x:c r="K14" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L14" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M14"/>
+      <x:c r="N14"/>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="13" t="str">
+        <x:v>MCU: J4904/J403</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>AON</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"AON",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="n">
+        <x:f>'Пуск'!M6</x:f>
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="n">
+        <x:f>MAX(F15,G15)</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="n">
+        <x:f>H15/D15*'Вход'!$C$14</x:f>
+        <x:v>0.008125</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:f>'Вход'!$C$15-I15</x:f>
+        <x:v>0.991875</x:v>
+      </x:c>
+      <x:c r="K15" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L15" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M15"/>
+      <x:c r="N15"/>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="13" t="str">
+        <x:v>MCU: J4904/J403</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="n">
+        <x:f>MAX(F16,G16)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="n">
+        <x:f>H16/D16*'Вход'!$C$14</x:f>
+        <x:v>1.9337875000000002</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:f>'Вход'!$C$15-I16</x:f>
+        <x:v>-0.9337875000000002</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L16" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M16"/>
+      <x:c r="N16"/>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
+      <x:c r="A17" s="13" t="str">
+        <x:v>USB: J4905/J404</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>1, 3</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:f>'Вход'!$C$12/C7+'Вход'!$C$12/D7+'Вход'!$C$13</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K7" s="17" t="n">
-        <x:f>E7*J7</x:f>
-        <x:v>13.200000000000001</x:v>
-      </x:c>
-      <x:c r="L7" s="17" t="n">
-        <x:f>(ABS('Шины'!D7)*(1-'Вход'!$C$10)-'Шины'!T7-'Вход'!$C$11-'Шины'!O7*'Шины'!F7)*1000</x:f>
-        <x:v>229.51851851851856</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="n">
-        <x:f>L7-K7</x:f>
-        <x:v>216.31851851851857</x:v>
-      </x:c>
-      <x:c r="N7" s="13" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="47" customHeight="1">
-      <x:c r="A8" s="9" t="str">
+      <x:c r="E17" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H17" s="17" t="n">
+        <x:f>MAX(F17,G17)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I17" s="17" t="n">
+        <x:f>H17/D17*'Вход'!$C$14</x:f>
+        <x:v>0.9668937500000001</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:f>'Вход'!$C$15-I17</x:f>
+        <x:v>0.03310624999999989</x:v>
+      </x:c>
+      <x:c r="K17" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L17" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M17"/>
+      <x:c r="N17"/>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="13" t="str">
+        <x:v>USB: J4905/J404</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
         <x:v>USB5</x:v>
       </x:c>
-      <x:c r="B8" s="9" t="str">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A8,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="F8" s="16" t="n">
+      <x:c r="C18" s="13" t="str">
+        <x:v>5, 7</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"USB5",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="n">
         <x:f>'Пуск'!M8</x:f>
         <x:v>0.02012</x:v>
       </x:c>
-      <x:c r="G8" s="16" t="n">
-        <x:f>MAX(E8,F8)</x:f>
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="H8" s="16" t="n">
-        <x:f>G8/C8*'Вход'!$C$14</x:f>
-        <x:v>0.0625</x:v>
-      </x:c>
-      <x:c r="I8" s="20" t="n">
-        <x:f>ROUNDUP(G8*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:f>'Вход'!$C$12/C8+'Вход'!$C$12/D8+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:f>E8*J8</x:f>
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="L8" s="16" t="n">
-        <x:f>(ABS('Шины'!D8)*(1-'Вход'!$C$10)-'Шины'!T8-'Вход'!$C$11-'Шины'!O8*'Шины'!F8)*1000</x:f>
-        <x:v>137.50000000000034</x:v>
-      </x:c>
-      <x:c r="M8" s="16" t="n">
-        <x:f>L8-K8</x:f>
-        <x:v>136.25000000000034</x:v>
-      </x:c>
-      <x:c r="N8" s="12" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="47" customHeight="1">
-      <x:c r="A9" s="2" t="str">
-        <x:v>CORE1V0</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="str">
-        <x:v>13, 15, 17, 19</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="10" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E9" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A9,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F9" s="17" t="n">
-        <x:f>'Пуск'!M10</x:f>
-        <x:v>1.464260974545455</x:v>
-      </x:c>
-      <x:c r="G9" s="17" t="n">
-        <x:f>MAX(E9,F9)</x:f>
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H9" s="17" t="n">
-        <x:f>G9/C9*'Вход'!$C$14</x:f>
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="I9" s="21" t="n">
-        <x:f>ROUNDUP(G9*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
+      <x:c r="H18" s="17" t="n">
+        <x:f>MAX(F18,G18)</x:f>
+        <x:v>0.065</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="n">
+        <x:f>H18/D18*'Вход'!$C$14</x:f>
+        <x:v>0.040625</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:f>'Вход'!$C$15-I18</x:f>
+        <x:v>0.959375</x:v>
+      </x:c>
+      <x:c r="K18" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L18" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M18"/>
+      <x:c r="N18"/>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="13" t="str">
+        <x:v>ETHERNET: J4906/J405</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>PHY1V05</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>1, 3</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J9" s="17" t="n">
-        <x:f>'Вход'!$C$12/C9+'Вход'!$C$12/D9+'Вход'!$C$13</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:f>E9*J9</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L9" s="17" t="n">
-        <x:f>(ABS('Шины'!D10)*(1-'Вход'!$C$10)-'Шины'!T10-'Вход'!$C$11-'Шины'!O10*'Шины'!F10)*1000</x:f>
-        <x:v>19.839999999999982</x:v>
-      </x:c>
-      <x:c r="M9" s="17" t="n">
-        <x:f>L9-K9</x:f>
-        <x:v>-20.160000000000018</x:v>
-      </x:c>
-      <x:c r="N9" s="13" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="47" customHeight="1">
-      <x:c r="A10" s="9" t="str">
-        <x:v>AUX1V8</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="str">
-        <x:v>21, 23</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E10" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A10,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="n">
-        <x:f>'Пуск'!M11</x:f>
-        <x:v>0.1774104</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="n">
-        <x:f>MAX(E10,F10)</x:f>
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="H10" s="16" t="n">
-        <x:f>G10/C10*'Вход'!$C$14</x:f>
-        <x:v>0.1875</x:v>
-      </x:c>
-      <x:c r="I10" s="20" t="n">
-        <x:f>ROUNDUP(G10*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:f>'Вход'!$C$12/C10+'Вход'!$C$12/D10+'Вход'!$C$13</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K10" s="16" t="n">
-        <x:f>E10*J10</x:f>
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="L10" s="16" t="n">
-        <x:f>(ABS('Шины'!D11)*(1-'Вход'!$C$10)-'Шины'!T11-'Вход'!$C$11-'Шины'!O11*'Шины'!F11)*1000</x:f>
-        <x:v>38.00000000000005</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="n">
-        <x:f>L10-K10</x:f>
-        <x:v>33.50000000000005</x:v>
-      </x:c>
-      <x:c r="N10" s="12" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="47" customHeight="1">
-      <x:c r="A11" s="2" t="str">
-        <x:v>IO3V3</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="str">
-        <x:v>7, 9, 11</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="10" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A11,'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
-        <x:v>1.19003</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="n">
-        <x:f>'Пуск'!M13</x:f>
-        <x:v>0.8757401880000002</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="n">
-        <x:f>MAX(E11,F11)</x:f>
-        <x:v>1.19003</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="n">
-        <x:f>G11/C11*'Вход'!$C$14</x:f>
-        <x:v>0.49584583333333326</x:v>
-      </x:c>
-      <x:c r="I11" s="21" t="n">
-        <x:f>ROUNDUP(G11*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:f>'Вход'!$C$12/C11+'Вход'!$C$12/D11+'Вход'!$C$13</x:f>
-        <x:v>11.666666666666668</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:f>E11*J11</x:f>
-        <x:v>13.883683333333334</x:v>
-      </x:c>
-      <x:c r="L11" s="17" t="n">
-        <x:f>(ABS('Шины'!D13)*(1-'Вход'!$C$10)-'Шины'!T13-'Вход'!$C$11-'Шины'!O13*'Шины'!F13)*1000</x:f>
-        <x:v>45.299399999999956</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="n">
-        <x:f>L11-K11</x:f>
-        <x:v>31.415716666666622</x:v>
-      </x:c>
-      <x:c r="N11" s="13" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="47" customHeight="1">
-      <x:c r="A12" s="9" t="str">
-        <x:v>DDR1V35</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="str">
-        <x:v>25, 27, 29</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="10" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A12,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="n">
-        <x:f>'Пуск'!M14</x:f>
-        <x:v>0.19565807999999996</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="n">
-        <x:f>MAX(E12,F12)</x:f>
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="H12" s="16" t="n">
-        <x:f>G12/C12*'Вход'!$C$14</x:f>
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="I12" s="20" t="n">
-        <x:f>ROUNDUP(G12*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:f>'Вход'!$C$12/C12+'Вход'!$C$12/D12+'Вход'!$C$13</x:f>
-        <x:v>11.666666666666668</x:v>
-      </x:c>
-      <x:c r="K12" s="16" t="n">
-        <x:f>E12*J12</x:f>
-        <x:v>9.333333333333334</x:v>
-      </x:c>
-      <x:c r="L12" s="16" t="n">
-        <x:f>(ABS('Шины'!D14)*(1-'Вход'!$C$10)-'Шины'!T14-'Вход'!$C$11-'Шины'!O14*'Шины'!F14)*1000</x:f>
-        <x:v>19.388777555110195</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="n">
-        <x:f>L12-K12</x:f>
-        <x:v>10.055444221776861</x:v>
-      </x:c>
-      <x:c r="N12" s="12" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="47" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>PHY1V05</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="str">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A13,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="n">
+      <x:c r="F19" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"PHY1V05",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="n">
         <x:f>'Пуск'!M15</x:f>
         <x:v>0.110292108</x:v>
       </x:c>
-      <x:c r="G13" s="17" t="n">
-        <x:f>MAX(E13,F13)</x:f>
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="H13" s="17" t="n">
-        <x:f>G13/C13*'Вход'!$C$14</x:f>
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="I13" s="21" t="n">
-        <x:f>ROUNDUP(G13*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
+      <x:c r="H19" s="17" t="n">
+        <x:f>MAX(F19,G19)</x:f>
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="I19" s="17" t="n">
+        <x:f>H19/D19*'Вход'!$C$14</x:f>
+        <x:v>0.1625</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:f>'Вход'!$C$15-I19</x:f>
+        <x:v>0.8375</x:v>
+      </x:c>
+      <x:c r="K19" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L19" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M19"/>
+      <x:c r="N19"/>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="13" t="str">
+        <x:v>ETHERNET: J4906/J405</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>5, 7, 9</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H20" s="17" t="n">
+        <x:f>MAX(F20,G20)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="n">
+        <x:f>H20/D20*'Вход'!$C$14</x:f>
+        <x:v>0.6445958333333334</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:f>'Вход'!$C$15-I20</x:f>
+        <x:v>0.35540416666666663</x:v>
+      </x:c>
+      <x:c r="K20" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L20" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M20"/>
+      <x:c r="N20"/>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="13" t="str">
+        <x:v>DAC_MATRIX: J4907/J406</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>1, 3</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"P15",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q27</x:f>
+        <x:v>0.4005</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="n">
+        <x:f>'Пуск'!M21</x:f>
+        <x:v>0.3643897230769233</x:v>
+      </x:c>
+      <x:c r="H21" s="17" t="n">
+        <x:f>MAX(F21,G21)</x:f>
+        <x:v>0.4005</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="n">
+        <x:f>H21/D21*'Вход'!$C$14</x:f>
+        <x:v>0.2503125</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:f>'Вход'!$C$15-I21</x:f>
+        <x:v>0.7496875000000001</x:v>
+      </x:c>
+      <x:c r="K21" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L21" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M21"/>
+      <x:c r="N21"/>
+    </x:row>
+    <x:row r="22" ht="48" customHeight="1">
+      <x:c r="A22" s="13" t="str">
+        <x:v>DAC_MATRIX: J4907/J406</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="str">
+        <x:v>N15</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="str">
+        <x:v>5, 7</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E22" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"N15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="n">
+        <x:f>'Пуск'!M22</x:f>
+        <x:v>0.3134400000000003</x:v>
+      </x:c>
+      <x:c r="H22" s="17" t="n">
+        <x:f>MAX(F22,G22)</x:f>
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="n">
+        <x:f>H22/D22*'Вход'!$C$14</x:f>
+        <x:v>0.24375000000000002</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="n">
+        <x:f>'Вход'!$C$15-I22</x:f>
+        <x:v>0.75625</x:v>
+      </x:c>
+      <x:c r="K22" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L22" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M22"/>
+      <x:c r="N22"/>
+    </x:row>
+    <x:row r="23" ht="48" customHeight="1">
+      <x:c r="A23" s="13" t="str">
+        <x:v>DAC_MATRIX: J4907/J406</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>ANA5</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:f>'Вход'!$C$12/C13+'Вход'!$C$12/D13+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:f>E13*J13</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L13" s="17" t="n">
-        <x:f>(ABS('Шины'!D15)*(1-'Вход'!$C$10)-'Шины'!T15-'Вход'!$C$11-'Шины'!O15*'Шины'!F15)*1000</x:f>
-        <x:v>64.51000000000008</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="n">
-        <x:f>L13-K13</x:f>
-        <x:v>59.510000000000076</x:v>
-      </x:c>
-      <x:c r="N13" s="13" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="47" customHeight="1">
-      <x:c r="A14" s="9" t="str">
-        <x:v>VTT</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="str">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C14" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A14,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.31112224448897796</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="n">
-        <x:f>'Пуск'!M16</x:f>
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="n">
-        <x:f>MAX(E14,F14)</x:f>
-        <x:v>0.31112224448897796</x:v>
-      </x:c>
-      <x:c r="H14" s="16" t="n">
-        <x:f>G14/C14*'Вход'!$C$14</x:f>
-        <x:v>0.3889028056112225</x:v>
-      </x:c>
-      <x:c r="I14" s="20" t="n">
-        <x:f>ROUNDUP(G14*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:f>'Вход'!$C$12/C14+'Вход'!$C$12/D14+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K14" s="16" t="n">
-        <x:f>E14*J14</x:f>
-        <x:v>7.778056112224449</x:v>
-      </x:c>
-      <x:c r="L14" s="16" t="str">
-        <x:v>tracking</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="str">
-        <x:v>проверить отдельно</x:v>
-      </x:c>
-      <x:c r="N14" s="12" t="str">
-        <x:v>Проверить source/sink, sense на нагрузке и tracking относительно DDR_VREF.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="47" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>DDR_VREF</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="str">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A15,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="n">
-        <x:f>'Пуск'!M17</x:f>
-        <x:v>0.0001648</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="n">
-        <x:f>MAX(E15,F15)</x:f>
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="H15" s="17" t="n">
-        <x:f>G15/C15*'Вход'!$C$14</x:f>
-        <x:v>0.00125</x:v>
-      </x:c>
-      <x:c r="I15" s="21" t="n">
-        <x:f>ROUNDUP(G15*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:f>'Вход'!$C$12/C15+'Вход'!$C$12/D15+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:f>E15*J15</x:f>
-        <x:v>0.025</x:v>
-      </x:c>
-      <x:c r="L15" s="17" t="str">
-        <x:v>tracking</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="str">
-        <x:v>проверить отдельно</x:v>
-      </x:c>
-      <x:c r="N15" s="13" t="str">
-        <x:v>Опорная цепь: проверить tracking и шум; ток контакта не определяет качество.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="47" customHeight="1">
-      <x:c r="A16" s="9" t="str">
-        <x:v>ANA5</x:v>
-      </x:c>
-      <x:c r="B16" s="9" t="str">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A16,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="n">
+      <x:c r="E23" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"ANA5",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.195</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="n">
         <x:f>'Пуск'!M19</x:f>
         <x:v>0.06386153846153847</x:v>
       </x:c>
-      <x:c r="G16" s="16" t="n">
-        <x:f>MAX(E16,F16)</x:f>
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="H16" s="16" t="n">
-        <x:f>G16/C16*'Вход'!$C$14</x:f>
-        <x:v>0.1875</x:v>
-      </x:c>
-      <x:c r="I16" s="20" t="n">
-        <x:f>ROUNDUP(G16*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
+      <x:c r="H23" s="17" t="n">
+        <x:f>MAX(F23,G23)</x:f>
+        <x:v>0.195</x:v>
+      </x:c>
+      <x:c r="I23" s="17" t="n">
+        <x:f>H23/D23*'Вход'!$C$14</x:f>
+        <x:v>0.24375000000000002</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="n">
+        <x:f>'Вход'!$C$15-I23</x:f>
+        <x:v>0.75625</x:v>
+      </x:c>
+      <x:c r="K23" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L23" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M23"/>
+      <x:c r="N23"/>
+    </x:row>
+    <x:row r="24" ht="48" customHeight="1">
+      <x:c r="A24" s="13" t="str">
+        <x:v>DAC_MATRIX: J4907/J406</x:v>
+      </x:c>
+      <x:c r="B24" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C24" s="13" t="str">
+        <x:v>11, 17</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H24" s="17" t="n">
+        <x:f>MAX(F24,G24)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="n">
+        <x:f>H24/D24*'Вход'!$C$14</x:f>
+        <x:v>0.9668937500000001</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="n">
+        <x:f>'Вход'!$C$15-I24</x:f>
+        <x:v>0.03310624999999989</x:v>
+      </x:c>
+      <x:c r="K24" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L24" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M24"/>
+      <x:c r="N24"/>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="13" t="str">
+        <x:v>DAC_MATRIX: J4907/J406</x:v>
+      </x:c>
+      <x:c r="B25" s="13" t="str">
+        <x:v>PROG_P15</x:v>
+      </x:c>
+      <x:c r="C25" s="13" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:f>'Вход'!$C$12/C16+'Вход'!$C$12/D16+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K16" s="16" t="n">
-        <x:f>E16*J16</x:f>
-        <x:v>3.75</x:v>
-      </x:c>
-      <x:c r="L16" s="16" t="n">
-        <x:f>(ABS('Шины'!D19)*(1-'Вход'!$C$10)-'Шины'!T19-'Вход'!$C$11-'Шины'!O19*'Шины'!F19)*1000</x:f>
-        <x:v>129.67850000000033</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="n">
-        <x:f>L16-K16</x:f>
-        <x:v>125.92850000000033</x:v>
-      </x:c>
-      <x:c r="N16" s="12" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="47" customHeight="1">
-      <x:c r="A17" s="2" t="str">
+      <x:c r="E25" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"PROG_P15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.078</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="n">
+        <x:f>'Пуск'!M23</x:f>
+        <x:v>0.04953706425339366</x:v>
+      </x:c>
+      <x:c r="H25" s="17" t="n">
+        <x:f>MAX(F25,G25)</x:f>
+        <x:v>0.078</x:v>
+      </x:c>
+      <x:c r="I25" s="17" t="n">
+        <x:f>H25/D25*'Вход'!$C$14</x:f>
+        <x:v>0.0975</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="n">
+        <x:f>'Вход'!$C$15-I25</x:f>
+        <x:v>0.9025</x:v>
+      </x:c>
+      <x:c r="K25" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L25" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M25"/>
+      <x:c r="N25"/>
+    </x:row>
+    <x:row r="26" ht="48" customHeight="1">
+      <x:c r="A26" s="13" t="str">
+        <x:v>DAC_MATRIX: J4907/J406</x:v>
+      </x:c>
+      <x:c r="B26" s="13" t="str">
+        <x:v>PROG_N15</x:v>
+      </x:c>
+      <x:c r="C26" s="13" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"PROG_N15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.078</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="n">
+        <x:f>'Пуск'!M24</x:f>
+        <x:v>0.04955999999999999</x:v>
+      </x:c>
+      <x:c r="H26" s="17" t="n">
+        <x:f>MAX(F26,G26)</x:f>
+        <x:v>0.078</x:v>
+      </x:c>
+      <x:c r="I26" s="17" t="n">
+        <x:f>H26/D26*'Вход'!$C$14</x:f>
+        <x:v>0.0975</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="n">
+        <x:f>'Вход'!$C$15-I26</x:f>
+        <x:v>0.9025</x:v>
+      </x:c>
+      <x:c r="K26" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L26" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M26"/>
+      <x:c r="N26"/>
+    </x:row>
+    <x:row r="27" ht="48" customHeight="1">
+      <x:c r="A27" s="13" t="str">
+        <x:v>ADC_AFE: J4908/J407</x:v>
+      </x:c>
+      <x:c r="B27" s="13" t="str">
+        <x:v>P15</x:v>
+      </x:c>
+      <x:c r="C27" s="13" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"P15",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q27</x:f>
+        <x:v>0.4005</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="n">
+        <x:f>'Пуск'!M21</x:f>
+        <x:v>0.3643897230769233</x:v>
+      </x:c>
+      <x:c r="H27" s="17" t="n">
+        <x:f>MAX(F27,G27)</x:f>
+        <x:v>0.4005</x:v>
+      </x:c>
+      <x:c r="I27" s="17" t="n">
+        <x:f>H27/D27*'Вход'!$C$14</x:f>
+        <x:v>0.500625</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="n">
+        <x:f>'Вход'!$C$15-I27</x:f>
+        <x:v>0.499375</x:v>
+      </x:c>
+      <x:c r="K27" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L27" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+      <x:c r="M27"/>
+      <x:c r="N27"/>
+    </x:row>
+    <x:row r="28" ht="48" customHeight="1">
+      <x:c r="A28" s="13" t="str">
+        <x:v>ADC_AFE: J4908/J407</x:v>
+      </x:c>
+      <x:c r="B28" s="13" t="str">
+        <x:v>N15</x:v>
+      </x:c>
+      <x:c r="C28" s="13" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"N15",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="n">
+        <x:f>'Пуск'!M22</x:f>
+        <x:v>0.3134400000000003</x:v>
+      </x:c>
+      <x:c r="H28" s="17" t="n">
+        <x:f>MAX(F28,G28)</x:f>
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="I28" s="17" t="n">
+        <x:f>H28/D28*'Вход'!$C$14</x:f>
+        <x:v>0.48750000000000004</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="n">
+        <x:f>'Вход'!$C$15-I28</x:f>
+        <x:v>0.5125</x:v>
+      </x:c>
+      <x:c r="K28" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L28" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="48" customHeight="1">
+      <x:c r="A29" s="13" t="str">
+        <x:v>ADC_AFE: J4908/J407</x:v>
+      </x:c>
+      <x:c r="B29" s="13" t="str">
+        <x:v>ANA5</x:v>
+      </x:c>
+      <x:c r="C29" s="13" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"ANA5",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.195</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="n">
+        <x:f>'Пуск'!M19</x:f>
+        <x:v>0.06386153846153847</x:v>
+      </x:c>
+      <x:c r="H29" s="17" t="n">
+        <x:f>MAX(F29,G29)</x:f>
+        <x:v>0.195</x:v>
+      </x:c>
+      <x:c r="I29" s="17" t="n">
+        <x:f>H29/D29*'Вход'!$C$14</x:f>
+        <x:v>0.24375000000000002</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="n">
+        <x:f>'Вход'!$C$15-I29</x:f>
+        <x:v>0.75625</x:v>
+      </x:c>
+      <x:c r="K29" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L29" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="48" customHeight="1">
+      <x:c r="A30" s="13" t="str">
+        <x:v>ADC_AFE: J4908/J407</x:v>
+      </x:c>
+      <x:c r="B30" s="13" t="str">
         <x:v>ANA3V3</x:v>
       </x:c>
-      <x:c r="B17" s="2" t="str">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C17" s="2" t="n">
+      <x:c r="C30" s="13" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A17,'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q26</x:f>
-        <x:v>0.050030000000000005</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="n">
+      <x:c r="E30" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"ANA3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q26</x:f>
+        <x:v>0.06503</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="n">
         <x:f>'Пуск'!M20</x:f>
         <x:v>0.010809353846153847</x:v>
       </x:c>
-      <x:c r="G17" s="17" t="n">
-        <x:f>MAX(E17,F17)</x:f>
-        <x:v>0.050030000000000005</x:v>
-      </x:c>
-      <x:c r="H17" s="17" t="n">
-        <x:f>G17/C17*'Вход'!$C$14</x:f>
-        <x:v>0.06253750000000001</x:v>
-      </x:c>
-      <x:c r="I17" s="21" t="n">
-        <x:f>ROUNDUP(G17*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
+      <x:c r="H30" s="17" t="n">
+        <x:f>MAX(F30,G30)</x:f>
+        <x:v>0.06503</x:v>
+      </x:c>
+      <x:c r="I30" s="17" t="n">
+        <x:f>H30/D30*'Вход'!$C$14</x:f>
+        <x:v>0.08128750000000001</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="n">
+        <x:f>'Вход'!$C$15-I30</x:f>
+        <x:v>0.9187125</x:v>
+      </x:c>
+      <x:c r="K30" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L30" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="48" customHeight="1">
+      <x:c r="A31" s="13" t="str">
+        <x:v>ADC_AFE: J4908/J407</x:v>
+      </x:c>
+      <x:c r="B31" s="13" t="str">
+        <x:v>IO3V3</x:v>
+      </x:c>
+      <x:c r="C31" s="13" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:f>'Вход'!$C$12/C17+'Вход'!$C$12/D17+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:f>E17*J17</x:f>
-        <x:v>1.25075</x:v>
-      </x:c>
-      <x:c r="L17" s="17" t="n">
-        <x:f>(ABS('Шины'!D20)*(1-'Вход'!$C$10)-'Шины'!T20-'Вход'!$C$11-'Шины'!O20*'Шины'!F20)*1000</x:f>
-        <x:v>81.49850000000006</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="n">
-        <x:f>L17-K17</x:f>
-        <x:v>80.24775000000007</x:v>
-      </x:c>
-      <x:c r="N17" s="13" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="47" customHeight="1">
-      <x:c r="A18" s="9" t="str">
-        <x:v>P15</x:v>
-      </x:c>
-      <x:c r="B18" s="9" t="str">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C18" s="9" t="n">
+      <x:c r="E31" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"IO3V3",'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q25</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="n">
+        <x:f>'Пуск'!M13</x:f>
+        <x:v>0.8757401880000016</x:v>
+      </x:c>
+      <x:c r="H31" s="17" t="n">
+        <x:f>MAX(F31,G31)</x:f>
+        <x:v>1.5470300000000001</x:v>
+      </x:c>
+      <x:c r="I31" s="17" t="n">
+        <x:f>H31/D31*'Вход'!$C$14</x:f>
+        <x:v>1.9337875000000002</x:v>
+      </x:c>
+      <x:c r="J31" s="17" t="n">
+        <x:f>'Вход'!$C$15-I31</x:f>
+        <x:v>-0.9337875000000002</x:v>
+      </x:c>
+      <x:c r="K31" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L31" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="48" customHeight="1">
+      <x:c r="A32" s="13" t="str">
+        <x:v>ADC_AFE: J4908/J407</x:v>
+      </x:c>
+      <x:c r="B32" s="13" t="str">
+        <x:v>AON</x:v>
+      </x:c>
+      <x:c r="C32" s="13" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D18" s="10" t="n">
+      <x:c r="E32" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="n">
+        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,"AON",'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="n">
+        <x:f>'Пуск'!M6</x:f>
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="H32" s="17" t="n">
+        <x:f>MAX(F32,G32)</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="I32" s="17" t="n">
+        <x:f>H32/D32*'Вход'!$C$14</x:f>
+        <x:v>0.008125</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="n">
+        <x:f>'Вход'!$C$15-I32</x:f>
+        <x:v>0.991875</x:v>
+      </x:c>
+      <x:c r="K32" s="13" t="str">
+        <x:v>Весь ток данной шины Control; общий GND — в таблице ниже</x:v>
+      </x:c>
+      <x:c r="L32" s="13" t="str">
+        <x:v>PCB, токораспределение и нагрев; токовой оценки недостаточно</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+      <x:c r="I33" s="2"/>
+      <x:c r="J33" s="2"/>
+      <x:c r="K33" s="2"/>
+      <x:c r="L33" s="2"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+      <x:c r="I34" s="2"/>
+      <x:c r="J34" s="2"/>
+      <x:c r="K34" s="2"/>
+      <x:c r="L34" s="2"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+      <x:c r="I35" s="2"/>
+      <x:c r="J35" s="2"/>
+      <x:c r="K35" s="2"/>
+      <x:c r="L35" s="2"/>
+    </x:row>
+    <x:row r="36" ht="44" customHeight="1">
+      <x:c r="A36" s="41" t="str">
+        <x:v>Общий возврат пары</x:v>
+      </x:c>
+      <x:c r="B36" s="41" t="str">
+        <x:v>GND, шт.</x:v>
+      </x:c>
+      <x:c r="C36" s="41" t="str">
+        <x:v>Сумма модулей, А</x:v>
+      </x:c>
+      <x:c r="D36" s="41" t="str">
+        <x:v>Средний, А</x:v>
+      </x:c>
+      <x:c r="E36" s="41" t="str">
+        <x:v>С неравномерностью, А</x:v>
+      </x:c>
+      <x:c r="F36" s="41" t="str">
+        <x:v>Запас, А</x:v>
+      </x:c>
+      <x:c r="G36" s="41" t="str">
+        <x:v>Основание</x:v>
+      </x:c>
+      <x:c r="H36" s="2"/>
+      <x:c r="I36" s="2"/>
+      <x:c r="J36" s="2"/>
+      <x:c r="K36" s="2"/>
+      <x:c r="L36" s="2"/>
+    </x:row>
+    <x:row r="37" ht="30" customHeight="1">
+      <x:c r="A37" s="2" t="str">
+        <x:v>SUPERVISION</x:v>
+      </x:c>
+      <x:c r="B37" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="n">
+        <x:f>H6</x:f>
+        <x:v>0.006500000000000001</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="n">
+        <x:f>C37/B37</x:f>
+        <x:v>0.0006500000000000001</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="n">
+        <x:f>D37*'Вход'!$C$14</x:f>
+        <x:v>0.0008125000000000001</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="n">
+        <x:f>'Вход'!$C$15-E37</x:f>
+        <x:v>0.9991875</x:v>
+      </x:c>
+      <x:c r="G37" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H37" s="2"/>
+      <x:c r="I37" s="2"/>
+      <x:c r="J37" s="2"/>
+      <x:c r="K37" s="2"/>
+      <x:c r="L37" s="2"/>
+    </x:row>
+    <x:row r="38" ht="30" customHeight="1">
+      <x:c r="A38" s="2" t="str">
+        <x:v>FPGA</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="n">
+        <x:f>H7+H8+H9</x:f>
+        <x:v>7.13703</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="n">
+        <x:f>C38/B38</x:f>
+        <x:v>0.5490023076923077</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="n">
+        <x:f>D38*'Вход'!$C$14</x:f>
+        <x:v>0.6862528846153847</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="n">
+        <x:f>'Вход'!$C$15-E38</x:f>
+        <x:v>0.3137471153846153</x:v>
+      </x:c>
+      <x:c r="G38" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H38" s="2"/>
+      <x:c r="I38" s="2"/>
+      <x:c r="J38" s="2"/>
+      <x:c r="K38" s="2"/>
+      <x:c r="L38" s="2"/>
+    </x:row>
+    <x:row r="39" ht="30" customHeight="1">
+      <x:c r="A39" s="2" t="str">
+        <x:v>DDR</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="n">
+        <x:f>H10+H11+H12+H13</x:f>
+        <x:v>2.9927889178356715</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="n">
+        <x:f>C39/B39</x:f>
+        <x:v>0.42754127397652447</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="n">
+        <x:f>D39*'Вход'!$C$14</x:f>
+        <x:v>0.5344265924706556</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="n">
+        <x:f>'Вход'!$C$15-E39</x:f>
+        <x:v>0.4655734075293444</x:v>
+      </x:c>
+      <x:c r="G39" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H39" s="2"/>
+      <x:c r="I39" s="2"/>
+      <x:c r="J39" s="2"/>
+      <x:c r="K39" s="2"/>
+      <x:c r="L39" s="2"/>
+    </x:row>
+    <x:row r="40" ht="30" customHeight="1">
+      <x:c r="A40" s="2" t="str">
+        <x:v>MCU</x:v>
+      </x:c>
+      <x:c r="B40" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="n">
+        <x:f>H14+H15+H16</x:f>
+        <x:v>2.6975300000000004</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="n">
+        <x:f>C40/B40</x:f>
+        <x:v>0.539506</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="n">
+        <x:f>D40*'Вход'!$C$14</x:f>
+        <x:v>0.6743825000000001</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="n">
+        <x:f>'Вход'!$C$15-E40</x:f>
+        <x:v>0.3256174999999999</x:v>
+      </x:c>
+      <x:c r="G40" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H40" s="2"/>
+      <x:c r="I40" s="2"/>
+      <x:c r="J40" s="2"/>
+      <x:c r="K40" s="2"/>
+      <x:c r="L40" s="2"/>
+    </x:row>
+    <x:row r="41" ht="30" customHeight="1">
+      <x:c r="A41" s="2" t="str">
+        <x:v>USB</x:v>
+      </x:c>
+      <x:c r="B41" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="n">
+        <x:f>H17+H18</x:f>
+        <x:v>1.61203</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="n">
+        <x:f>C41/B41</x:f>
+        <x:v>0.4030075</x:v>
+      </x:c>
+      <x:c r="E41" s="17" t="n">
+        <x:f>D41*'Вход'!$C$14</x:f>
+        <x:v>0.503759375</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="n">
+        <x:f>'Вход'!$C$15-E41</x:f>
+        <x:v>0.496240625</x:v>
+      </x:c>
+      <x:c r="G41" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H41" s="2"/>
+      <x:c r="I41" s="2"/>
+      <x:c r="J41" s="2"/>
+      <x:c r="K41" s="2"/>
+      <x:c r="L41" s="2"/>
+    </x:row>
+    <x:row r="42" ht="30" customHeight="1">
+      <x:c r="A42" s="2" t="str">
+        <x:v>ETHERNET</x:v>
+      </x:c>
+      <x:c r="B42" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="n">
+        <x:f>H19+H20</x:f>
+        <x:v>1.8070300000000001</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="n">
+        <x:f>C42/B42</x:f>
+        <x:v>0.361406</x:v>
+      </x:c>
+      <x:c r="E42" s="17" t="n">
+        <x:f>D42*'Вход'!$C$14</x:f>
+        <x:v>0.45175750000000003</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="n">
+        <x:f>'Вход'!$C$15-E42</x:f>
+        <x:v>0.5482425</x:v>
+      </x:c>
+      <x:c r="G42" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H42" s="2"/>
+      <x:c r="I42" s="2"/>
+      <x:c r="J42" s="2"/>
+      <x:c r="K42" s="2"/>
+      <x:c r="L42" s="2"/>
+    </x:row>
+    <x:row r="43" ht="30" customHeight="1">
+      <x:c r="A43" s="2" t="str">
+        <x:v>DAC_MATRIX</x:v>
+      </x:c>
+      <x:c r="B43" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C43" s="17" t="n">
+        <x:f>H21+H22+H23+H24+H25+H26</x:f>
+        <x:v>2.68853</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="n">
+        <x:f>C43/B43</x:f>
+        <x:v>0.2987255555555556</x:v>
+      </x:c>
+      <x:c r="E43" s="17" t="n">
+        <x:f>D43*'Вход'!$C$14</x:f>
+        <x:v>0.37340694444444444</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="n">
+        <x:f>'Вход'!$C$15-E43</x:f>
+        <x:v>0.6265930555555556</x:v>
+      </x:c>
+      <x:c r="G43" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H43" s="2"/>
+      <x:c r="I43" s="2"/>
+      <x:c r="J43" s="2"/>
+      <x:c r="K43" s="2"/>
+      <x:c r="L43" s="2"/>
+    </x:row>
+    <x:row r="44" ht="30" customHeight="1">
+      <x:c r="A44" s="2" t="str">
+        <x:v>ADC_AFE</x:v>
+      </x:c>
+      <x:c r="B44" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C44" s="17" t="n">
+        <x:f>H27+H28+H29+H30+H31+H32</x:f>
+        <x:v>2.60406</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="n">
+        <x:f>C44/B44</x:f>
+        <x:v>0.43401</x:v>
+      </x:c>
+      <x:c r="E44" s="17" t="n">
+        <x:f>D44*'Вход'!$C$14</x:f>
+        <x:v>0.5425125</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="n">
+        <x:f>'Вход'!$C$15-E44</x:f>
+        <x:v>0.45748750000000005</x:v>
+      </x:c>
+      <x:c r="G44" s="2" t="str">
+        <x:v>Модули токов; без вычитания N15. Сигнальные токи не включены.</x:v>
+      </x:c>
+      <x:c r="H44" s="2"/>
+      <x:c r="I44" s="2"/>
+      <x:c r="J44" s="2"/>
+      <x:c r="K44" s="2"/>
+      <x:c r="L44" s="2"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="2"/>
+      <x:c r="B45" s="2"/>
+      <x:c r="C45" s="2"/>
+      <x:c r="D45" s="2"/>
+      <x:c r="E45" s="2"/>
+      <x:c r="F45" s="2"/>
+      <x:c r="G45" s="2"/>
+      <x:c r="H45" s="2"/>
+      <x:c r="I45" s="2"/>
+      <x:c r="J45" s="2"/>
+      <x:c r="K45" s="2"/>
+      <x:c r="L45" s="2"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="2"/>
+      <x:c r="B46" s="2"/>
+      <x:c r="C46" s="2"/>
+      <x:c r="D46" s="2"/>
+      <x:c r="E46" s="2"/>
+      <x:c r="F46" s="2"/>
+      <x:c r="G46" s="2"/>
+      <x:c r="H46" s="2"/>
+      <x:c r="I46" s="2"/>
+      <x:c r="J46" s="2"/>
+      <x:c r="K46" s="2"/>
+      <x:c r="L46" s="2"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="2"/>
+      <x:c r="B47" s="2"/>
+      <x:c r="C47" s="2"/>
+      <x:c r="D47" s="2"/>
+      <x:c r="E47" s="2"/>
+      <x:c r="F47" s="2"/>
+      <x:c r="G47" s="2"/>
+      <x:c r="H47" s="2"/>
+      <x:c r="I47" s="2"/>
+      <x:c r="J47" s="2"/>
+      <x:c r="K47" s="2"/>
+      <x:c r="L47" s="2"/>
+    </x:row>
+    <x:row r="48" ht="26" customHeight="1">
+      <x:c r="A48" s="2" t="str">
+        <x:v>CORE: условная DC-модель</x:v>
+      </x:c>
+      <x:c r="B48" s="2"/>
+      <x:c r="C48" s="2"/>
+      <x:c r="D48" s="2"/>
+      <x:c r="E48" s="2"/>
+      <x:c r="F48" s="2"/>
+      <x:c r="G48" s="2"/>
+      <x:c r="H48" s="2"/>
+      <x:c r="I48" s="2"/>
+      <x:c r="J48" s="2"/>
+      <x:c r="K48" s="2"/>
+      <x:c r="L48" s="2"/>
+    </x:row>
+    <x:row r="49" ht="26" customHeight="1">
+      <x:c r="A49" s="2" t="str">
+        <x:v>Положительный тракт со шунтом, Ом</x:v>
+      </x:c>
+      <x:c r="B49" s="2"/>
+      <x:c r="C49" s="2"/>
+      <x:c r="D49" s="43" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="E49" s="2"/>
+      <x:c r="F49" s="13" t="str">
+        <x:v>7 мОм включают шунт 2 мОм. 3 мОм — общий GND. Для этой локальной модели взят только FPGA IO; токи других зон через данный возврат не предполагаются. Требуются геометрия PCB и проверка устойчивости.</x:v>
+      </x:c>
+      <x:c r="G49" s="13"/>
+      <x:c r="H49" s="13"/>
+      <x:c r="I49" s="13"/>
+      <x:c r="J49" s="13"/>
+      <x:c r="K49" s="13"/>
+      <x:c r="L49" s="13"/>
+    </x:row>
+    <x:row r="50" ht="26" customHeight="1">
+      <x:c r="A50" s="2" t="str">
+        <x:v>Общий возврат, Ом</x:v>
+      </x:c>
+      <x:c r="B50" s="2"/>
+      <x:c r="C50" s="2"/>
+      <x:c r="D50" s="43" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="E50" s="2"/>
+      <x:c r="F50" s="13"/>
+      <x:c r="G50" s="13"/>
+      <x:c r="H50" s="13"/>
+      <x:c r="I50" s="13"/>
+      <x:c r="J50" s="13"/>
+      <x:c r="K50" s="13"/>
+      <x:c r="L50" s="13"/>
+    </x:row>
+    <x:row r="51" ht="26" customHeight="1">
+      <x:c r="A51" s="2" t="str">
+        <x:v>Линия sense, Ом</x:v>
+      </x:c>
+      <x:c r="B51" s="2"/>
+      <x:c r="C51" s="2"/>
+      <x:c r="D51" s="43" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E18" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A18,'Нагрузки'!$B$6:$B$37,"Control")+'Шины'!Q27</x:f>
-        <x:v>0.30810000000000004</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="n">
-        <x:f>'Пуск'!M21</x:f>
-        <x:v>0.36438972307692336</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="n">
-        <x:f>MAX(E18,F18)</x:f>
-        <x:v>0.36438972307692336</x:v>
-      </x:c>
-      <x:c r="H18" s="16" t="n">
-        <x:f>G18/C18*'Вход'!$C$14</x:f>
-        <x:v>0.4554871538461542</x:v>
-      </x:c>
-      <x:c r="I18" s="20" t="n">
-        <x:f>ROUNDUP(G18*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:f>'Вход'!$C$12/C18+'Вход'!$C$12/D18+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K18" s="16" t="n">
-        <x:f>E18*J18</x:f>
-        <x:v>7.702500000000001</x:v>
-      </x:c>
-      <x:c r="L18" s="16" t="n">
-        <x:f>(ABS('Шины'!D21)*(1-'Вход'!$C$10)-'Шины'!T21-'Вход'!$C$11-'Шины'!O21*'Шины'!F21)*1000</x:f>
-        <x:v>393.43434389140054</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="n">
-        <x:f>L18-K18</x:f>
-        <x:v>385.73184389140056</x:v>
-      </x:c>
-      <x:c r="N18" s="12" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="47" customHeight="1">
-      <x:c r="A19" s="2" t="str">
-        <x:v>N15</x:v>
-      </x:c>
-      <x:c r="B19" s="2" t="str">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C19" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A19,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.30000000000000004</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="n">
-        <x:f>'Пуск'!M22</x:f>
-        <x:v>0.3133016687782808</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="n">
-        <x:f>MAX(E19,F19)</x:f>
-        <x:v>0.3133016687782808</x:v>
-      </x:c>
-      <x:c r="H19" s="17" t="n">
-        <x:f>G19/C19*'Вход'!$C$14</x:f>
-        <x:v>0.391627085972851</x:v>
-      </x:c>
-      <x:c r="I19" s="21" t="n">
-        <x:f>ROUNDUP(G19*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:f>'Вход'!$C$12/C19+'Вход'!$C$12/D19+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:f>E19*J19</x:f>
-        <x:v>7.500000000000001</x:v>
-      </x:c>
-      <x:c r="L19" s="17" t="n">
-        <x:f>(ABS('Шины'!D22)*(1-'Вход'!$C$10)-'Шины'!T22-'Вход'!$C$11-'Шины'!O22*'Шины'!F22)*1000</x:f>
-        <x:v>394.2443438914005</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="n">
-        <x:f>L19-K19</x:f>
-        <x:v>386.7443438914005</x:v>
-      </x:c>
-      <x:c r="N19" s="13" t="str">
-        <x:v>MPN пары, многоконтактная токовая характеристика и реальные сопротивления пока не заданы.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="47" customHeight="1">
-      <x:c r="A20" s="9" t="str">
-        <x:v>PROG_P15</x:v>
-      </x:c>
-      <x:c r="B20" s="9" t="str">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C20" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A20,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="n">
-        <x:f>'Пуск'!M23</x:f>
-        <x:v>0.04953706425339366</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="n">
-        <x:f>MAX(E20,F20)</x:f>
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="H20" s="16" t="n">
-        <x:f>G20/C20*'Вход'!$C$14</x:f>
-        <x:v>0.075</x:v>
-      </x:c>
-      <x:c r="I20" s="20" t="n">
-        <x:f>ROUNDUP(G20*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:f>'Вход'!$C$12/C20+'Вход'!$C$12/D20+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K20" s="16" t="n">
-        <x:f>E20*J20</x:f>
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="L20" s="16" t="n">
-        <x:f>(ABS('Шины'!D21)*(1-'Вход'!$C$10)-'Шины'!T23-'Вход'!$C$11-'Шины'!O21*'Шины'!F21)*1000</x:f>
-        <x:v>393.43434389140054</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="n">
-        <x:f>L20-K20</x:f>
-        <x:v>391.93434389140054</x:v>
-      </x:c>
-      <x:c r="N20" s="12" t="str">
-        <x:v>Не включены потери ключей ±15 В; уточнить RDS(on), включение и нагрузку.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="47" customHeight="1">
-      <x:c r="A21" s="2" t="str">
-        <x:v>PROG_N15</x:v>
-      </x:c>
-      <x:c r="B21" s="2" t="str">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C21" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="n">
-        <x:f>SUMIFS('Нагрузки'!$E$6:$E$37,'Нагрузки'!$A$6:$A$37,A21,'Нагрузки'!$B$6:$B$37,"Control")+0</x:f>
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="n">
-        <x:f>'Пуск'!M24</x:f>
-        <x:v>0.04953706425339366</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="n">
-        <x:f>MAX(E21,F21)</x:f>
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="H21" s="17" t="n">
-        <x:f>G21/C21*'Вход'!$C$14</x:f>
-        <x:v>0.075</x:v>
-      </x:c>
-      <x:c r="I21" s="21" t="n">
-        <x:f>ROUNDUP(G21*'Вход'!$C$14/'Вход'!$C$15,0)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:f>'Вход'!$C$12/C21+'Вход'!$C$12/D21+'Вход'!$C$13</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:f>E21*J21</x:f>
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="L21" s="17" t="n">
-        <x:f>(ABS('Шины'!D22)*(1-'Вход'!$C$10)-'Шины'!T24-'Вход'!$C$11-'Шины'!O22*'Шины'!F22)*1000</x:f>
-        <x:v>394.2443438914005</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="n">
-        <x:f>L21-K21</x:f>
-        <x:v>392.7443438914005</x:v>
-      </x:c>
-      <x:c r="N21" s="13" t="str">
-        <x:v>Не включены потери ключей ±15 В; уточнить RDS(on), включение и нагрузку.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="2"/>
-      <x:c r="B22" s="2"/>
-      <x:c r="C22" s="2"/>
-      <x:c r="D22" s="2"/>
-      <x:c r="E22" s="2"/>
-      <x:c r="F22" s="2"/>
-      <x:c r="G22" s="2"/>
-      <x:c r="H22" s="2"/>
-      <x:c r="I22" s="2"/>
-      <x:c r="J22" s="2"/>
-      <x:c r="K22" s="2"/>
-      <x:c r="L22" s="2"/>
-      <x:c r="M22" s="2"/>
-      <x:c r="N22" s="2"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="2"/>
-      <x:c r="B23" s="2"/>
-      <x:c r="C23" s="2"/>
-      <x:c r="D23" s="2"/>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="2"/>
-      <x:c r="G23" s="2"/>
-      <x:c r="H23" s="2"/>
-      <x:c r="I23" s="2"/>
-      <x:c r="J23" s="2"/>
-      <x:c r="K23" s="2"/>
-      <x:c r="L23" s="2"/>
-      <x:c r="M23" s="2"/>
-      <x:c r="N23" s="2"/>
-    </x:row>
-    <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="13" t="str">
-        <x:v>Контактов GND по схеме</x:v>
-      </x:c>
-      <x:c r="B24" s="13"/>
-      <x:c r="C24" s="13"/>
-      <x:c r="D24" s="2" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="13" t="str">
-        <x:v>Токи положительных и отрицательных шин здесь не взаимно вычитаются. Усреднение по всем GND не подтверждает ток ближайшего возвратного контакта: требуются геометрия пары, распределение тока и тепловая характеристика при полной нагрузке. Принятые N GND — модель, не новая распиновка.</x:v>
-      </x:c>
-      <x:c r="G24" s="13"/>
-      <x:c r="H24" s="13"/>
-      <x:c r="I24" s="13"/>
-      <x:c r="J24" s="13"/>
-      <x:c r="K24" s="13"/>
-      <x:c r="L24" s="13"/>
-      <x:c r="M24" s="13"/>
-      <x:c r="N24" s="13"/>
-    </x:row>
-    <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="13" t="str">
-        <x:v>Распределено GND в модели</x:v>
-      </x:c>
-      <x:c r="B25" s="13"/>
-      <x:c r="C25" s="13"/>
-      <x:c r="D25" s="2" t="n">
-        <x:f>SUM(D6:D21)</x:f>
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E25" s="2"/>
-      <x:c r="F25" s="13"/>
-      <x:c r="G25" s="13"/>
-      <x:c r="H25" s="13"/>
-      <x:c r="I25" s="13"/>
-      <x:c r="J25" s="13"/>
-      <x:c r="K25" s="13"/>
-      <x:c r="L25" s="13"/>
-      <x:c r="M25" s="13"/>
-      <x:c r="N25" s="13"/>
-    </x:row>
-    <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="13" t="str">
-        <x:v>Сумма модулей пиков, А</x:v>
-      </x:c>
-      <x:c r="B26" s="13"/>
-      <x:c r="C26" s="13"/>
-      <x:c r="D26" s="17" t="n">
-        <x:f>SUM(E6:E21)</x:f>
-        <x:v>8.66528224448898</x:v>
-      </x:c>
-      <x:c r="E26" s="2"/>
-      <x:c r="F26" s="13"/>
-      <x:c r="G26" s="13"/>
-      <x:c r="H26" s="13"/>
-      <x:c r="I26" s="13"/>
-      <x:c r="J26" s="13"/>
-      <x:c r="K26" s="13"/>
-      <x:c r="L26" s="13"/>
-      <x:c r="M26" s="13"/>
-      <x:c r="N26" s="13"/>
-    </x:row>
-    <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="22" t="str">
-        <x:v>Средний по 30 GND × неравномерность, А</x:v>
-      </x:c>
-      <x:c r="B27" s="22"/>
-      <x:c r="C27" s="22"/>
-      <x:c r="D27" s="23" t="n">
-        <x:f>D26/D24*'Вход'!$C$14</x:f>
-        <x:v>0.3610534268537075</x:v>
-      </x:c>
-      <x:c r="F27" s="22"/>
-      <x:c r="G27" s="22"/>
-      <x:c r="H27" s="22"/>
-      <x:c r="I27" s="22"/>
-      <x:c r="J27" s="22"/>
-      <x:c r="K27" s="22"/>
-      <x:c r="L27" s="22"/>
-      <x:c r="M27" s="22"/>
-      <x:c r="N27" s="22"/>
+      <x:c r="E51" s="2"/>
+      <x:c r="F51" s="13"/>
+      <x:c r="G51" s="13"/>
+      <x:c r="H51" s="13"/>
+      <x:c r="I51" s="13"/>
+      <x:c r="J51" s="13"/>
+      <x:c r="K51" s="13"/>
+      <x:c r="L51" s="13"/>
+    </x:row>
+    <x:row r="52" ht="26" customHeight="1">
+      <x:c r="A52" s="2" t="str">
+        <x:v>R1210 fallback, Ом</x:v>
+      </x:c>
+      <x:c r="B52" s="2"/>
+      <x:c r="C52" s="2"/>
+      <x:c r="D52" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E52" s="2"/>
+      <x:c r="F52" s="13"/>
+      <x:c r="G52" s="13"/>
+      <x:c r="H52" s="13"/>
+      <x:c r="I52" s="13"/>
+      <x:c r="J52" s="13"/>
+      <x:c r="K52" s="13"/>
+      <x:c r="L52" s="13"/>
+    </x:row>
+    <x:row r="53" ht="26" customHeight="1">
+      <x:c r="A53" s="2" t="str">
+        <x:v>Vref преобразователя, В</x:v>
+      </x:c>
+      <x:c r="B53" s="2"/>
+      <x:c r="C53" s="2"/>
+      <x:c r="D53" s="43" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="E53" s="2"/>
+      <x:c r="F53" s="13"/>
+      <x:c r="G53" s="13"/>
+      <x:c r="H53" s="13"/>
+      <x:c r="I53" s="13"/>
+      <x:c r="J53" s="13"/>
+      <x:c r="K53" s="13"/>
+      <x:c r="L53" s="13"/>
+    </x:row>
+    <x:row r="54" ht="26" customHeight="1">
+      <x:c r="A54" s="2" t="str">
+        <x:v>Нижний резистор, Ом</x:v>
+      </x:c>
+      <x:c r="B54" s="2"/>
+      <x:c r="C54" s="2"/>
+      <x:c r="D54" s="43" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="E54" s="2"/>
+      <x:c r="F54" s="2"/>
+      <x:c r="G54" s="2"/>
+      <x:c r="H54" s="2"/>
+      <x:c r="I54" s="2"/>
+      <x:c r="J54" s="2"/>
+      <x:c r="K54" s="2"/>
+      <x:c r="L54" s="2"/>
+    </x:row>
+    <x:row r="55" ht="26" customHeight="1">
+      <x:c r="A55" s="2" t="str">
+        <x:v>Верхний резистор, Ом</x:v>
+      </x:c>
+      <x:c r="B55" s="2"/>
+      <x:c r="C55" s="2"/>
+      <x:c r="D55" s="43" t="n">
+        <x:v>10200</x:v>
+      </x:c>
+      <x:c r="E55" s="2"/>
+      <x:c r="F55" s="2"/>
+      <x:c r="G55" s="2"/>
+      <x:c r="H55" s="2"/>
+      <x:c r="I55" s="2"/>
+      <x:c r="J55" s="2"/>
+      <x:c r="K55" s="2"/>
+      <x:c r="L55" s="2"/>
+    </x:row>
+    <x:row r="56" ht="26" customHeight="1">
+      <x:c r="A56" s="2" t="str">
+        <x:v>CORE ток, А</x:v>
+      </x:c>
+      <x:c r="B56" s="2"/>
+      <x:c r="C56" s="2"/>
+      <x:c r="D56" s="42" t="n">
+        <x:f>'Шины'!O10</x:f>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="E56" s="2"/>
+      <x:c r="F56" s="2"/>
+      <x:c r="G56" s="2"/>
+      <x:c r="H56" s="2"/>
+      <x:c r="I56" s="2"/>
+      <x:c r="J56" s="2"/>
+      <x:c r="K56" s="2"/>
+      <x:c r="L56" s="2"/>
+    </x:row>
+    <x:row r="57" ht="26" customHeight="1">
+      <x:c r="A57" s="2" t="str">
+        <x:v>AUX + FPGA IO возврат, А</x:v>
+      </x:c>
+      <x:c r="B57" s="2"/>
+      <x:c r="C57" s="2"/>
+      <x:c r="D57" s="42" t="n">
+        <x:f>'Нагрузки'!E14+'Нагрузки'!E16</x:f>
+        <x:v>0.91</x:v>
+      </x:c>
+      <x:c r="E57" s="2"/>
+      <x:c r="F57" s="2"/>
+      <x:c r="G57" s="2"/>
+      <x:c r="H57" s="2"/>
+      <x:c r="I57" s="2"/>
+      <x:c r="J57" s="2"/>
+      <x:c r="K57" s="2"/>
+      <x:c r="L57" s="2"/>
+    </x:row>
+    <x:row r="58" ht="26" customHeight="1">
+      <x:c r="A58" s="2" t="str">
+        <x:v>Выставленный номинал, В</x:v>
+      </x:c>
+      <x:c r="B58" s="2"/>
+      <x:c r="C58" s="2"/>
+      <x:c r="D58" s="42" t="n">
+        <x:f>D53*(1+D55/D54)</x:f>
+        <x:v>1.008</x:v>
+      </x:c>
+      <x:c r="E58" s="2"/>
+      <x:c r="F58" s="2"/>
+      <x:c r="G58" s="2"/>
+      <x:c r="H58" s="2"/>
+      <x:c r="I58" s="2"/>
+      <x:c r="J58" s="2"/>
+      <x:c r="K58" s="2"/>
+      <x:c r="L58" s="2"/>
+    </x:row>
+    <x:row r="59" ht="26" customHeight="1">
+      <x:c r="A59" s="2" t="str">
+        <x:v>Ток линии sense, А</x:v>
+      </x:c>
+      <x:c r="B59" s="2"/>
+      <x:c r="C59" s="2"/>
+      <x:c r="D59" s="42" t="n">
+        <x:f>(D53/D54*D52-D49*D56)/(D52+D51+D49)</x:f>
+        <x:v>-0.0003207698476343223</x:v>
+      </x:c>
+      <x:c r="E59" s="2"/>
+      <x:c r="F59" s="2"/>
+      <x:c r="G59" s="2"/>
+      <x:c r="H59" s="2"/>
+      <x:c r="I59" s="2"/>
+      <x:c r="J59" s="2"/>
+      <x:c r="K59" s="2"/>
+      <x:c r="L59" s="2"/>
+    </x:row>
+    <x:row r="60" ht="26" customHeight="1">
+      <x:c r="A60" s="2" t="str">
+        <x:v>Положительный потенциал нагрузки, В</x:v>
+      </x:c>
+      <x:c r="B60" s="2"/>
+      <x:c r="C60" s="2"/>
+      <x:c r="D60" s="42" t="n">
+        <x:f>D58+D51*D59</x:f>
+        <x:v>1.0076792301523656</x:v>
+      </x:c>
+      <x:c r="E60" s="2"/>
+      <x:c r="F60" s="2"/>
+      <x:c r="G60" s="2"/>
+      <x:c r="H60" s="2"/>
+      <x:c r="I60" s="2"/>
+      <x:c r="J60" s="2"/>
+      <x:c r="K60" s="2"/>
+      <x:c r="L60" s="2"/>
+    </x:row>
+    <x:row r="61" ht="26" customHeight="1">
+      <x:c r="A61" s="2" t="str">
+        <x:v>Vraw с учётом sense, В</x:v>
+      </x:c>
+      <x:c r="B61" s="2"/>
+      <x:c r="C61" s="2"/>
+      <x:c r="D61" s="42" t="n">
+        <x:f>D60+D49*(D56+D59)</x:f>
+        <x:v>1.0440769847634321</x:v>
+      </x:c>
+      <x:c r="E61" s="2"/>
+      <x:c r="F61" s="2"/>
+      <x:c r="G61" s="2"/>
+      <x:c r="H61" s="2"/>
+      <x:c r="I61" s="2"/>
+      <x:c r="J61" s="2"/>
+      <x:c r="K61" s="2"/>
+      <x:c r="L61" s="2"/>
+    </x:row>
+    <x:row r="62" ht="26" customHeight="1">
+      <x:c r="A62" s="2" t="str">
+        <x:v>Напряжение нагрузки, В</x:v>
+      </x:c>
+      <x:c r="B62" s="2"/>
+      <x:c r="C62" s="2"/>
+      <x:c r="D62" s="42" t="n">
+        <x:f>D60-D50*(D56+D57)</x:f>
+        <x:v>0.9893492301523656</x:v>
+      </x:c>
+      <x:c r="E62" s="2"/>
+      <x:c r="F62" s="2"/>
+      <x:c r="G62" s="2"/>
+      <x:c r="H62" s="2"/>
+      <x:c r="I62" s="2"/>
+      <x:c r="J62" s="2"/>
+      <x:c r="K62" s="2"/>
+      <x:c r="L62" s="2"/>
+    </x:row>
+    <x:row r="63" ht="26" customHeight="1">
+      <x:c r="A63" s="2" t="str">
+        <x:v>Нижняя оценка с допусками, В</x:v>
+      </x:c>
+      <x:c r="B63" s="2"/>
+      <x:c r="C63" s="2"/>
+      <x:c r="D63" s="42" t="n">
+        <x:f>D62-'Вход'!C10*D58-'Вход'!C11</x:f>
+        <x:v>0.9591892301523657</x:v>
+      </x:c>
+      <x:c r="E63" s="2"/>
+      <x:c r="F63" s="2"/>
+      <x:c r="G63" s="2"/>
+      <x:c r="H63" s="2"/>
+      <x:c r="I63" s="2"/>
+      <x:c r="J63" s="2"/>
+      <x:c r="K63" s="2"/>
+      <x:c r="L63" s="2"/>
+    </x:row>
+    <x:row r="64" ht="26" customHeight="1">
+      <x:c r="A64" s="2" t="str">
+        <x:v>Запас над Vmin FPGA, мВ</x:v>
+      </x:c>
+      <x:c r="B64" s="2"/>
+      <x:c r="C64" s="2"/>
+      <x:c r="D64" s="42" t="n">
+        <x:f>(D63-'Шины'!T10)*1000</x:f>
+        <x:v>9.189230152365724</x:v>
+      </x:c>
+      <x:c r="E64" s="2"/>
+      <x:c r="F64" s="2"/>
+      <x:c r="G64" s="2"/>
+      <x:c r="H64" s="2"/>
+      <x:c r="I64" s="2"/>
+      <x:c r="J64" s="2"/>
+      <x:c r="K64" s="2"/>
+      <x:c r="L64" s="2"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="2"/>
+      <x:c r="B65" s="2"/>
+      <x:c r="C65" s="2"/>
+      <x:c r="D65" s="2"/>
+      <x:c r="E65" s="2"/>
+      <x:c r="F65" s="2"/>
+      <x:c r="G65" s="2"/>
+      <x:c r="H65" s="2"/>
+      <x:c r="I65" s="2"/>
+      <x:c r="J65" s="2"/>
+      <x:c r="K65" s="2"/>
+      <x:c r="L65" s="2"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="2"/>
+      <x:c r="B66" s="2"/>
+      <x:c r="C66" s="2"/>
+      <x:c r="D66" s="2"/>
+      <x:c r="E66" s="2"/>
+      <x:c r="F66" s="2"/>
+      <x:c r="G66" s="2"/>
+      <x:c r="H66" s="2"/>
+      <x:c r="I66" s="2"/>
+      <x:c r="J66" s="2"/>
+      <x:c r="K66" s="2"/>
+      <x:c r="L66" s="2"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="2"/>
+      <x:c r="B67" s="2"/>
+      <x:c r="C67" s="2"/>
+      <x:c r="D67" s="2"/>
+      <x:c r="E67" s="2"/>
+      <x:c r="F67" s="2"/>
+      <x:c r="G67" s="2"/>
+      <x:c r="H67" s="2"/>
+      <x:c r="I67" s="2"/>
+      <x:c r="J67" s="2"/>
+      <x:c r="K67" s="2"/>
+      <x:c r="L67" s="2"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="2"/>
+      <x:c r="B68" s="2"/>
+      <x:c r="C68" s="2"/>
+      <x:c r="D68" s="2"/>
+      <x:c r="E68" s="2"/>
+      <x:c r="F68" s="2"/>
+      <x:c r="G68" s="2"/>
+      <x:c r="H68" s="2"/>
+      <x:c r="I68" s="2"/>
+      <x:c r="J68" s="2"/>
+      <x:c r="K68" s="2"/>
+      <x:c r="L68" s="2"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="2"/>
+      <x:c r="B69" s="2"/>
+      <x:c r="C69" s="2"/>
+      <x:c r="D69" s="2"/>
+      <x:c r="E69" s="2"/>
+      <x:c r="F69" s="2"/>
+      <x:c r="G69" s="2"/>
+      <x:c r="H69" s="2"/>
+      <x:c r="I69" s="2"/>
+      <x:c r="J69" s="2"/>
+      <x:c r="K69" s="2"/>
+      <x:c r="L69" s="2"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="2"/>
+      <x:c r="B70" s="2"/>
+      <x:c r="C70" s="2"/>
+      <x:c r="D70" s="2"/>
+      <x:c r="E70" s="2"/>
+      <x:c r="F70" s="2"/>
+      <x:c r="G70" s="2"/>
+      <x:c r="H70" s="2"/>
+      <x:c r="I70" s="2"/>
+      <x:c r="J70" s="2"/>
+      <x:c r="K70" s="2"/>
+      <x:c r="L70" s="2"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="2"/>
+      <x:c r="B71" s="2"/>
+      <x:c r="C71" s="2"/>
+      <x:c r="D71" s="2"/>
+      <x:c r="E71" s="2"/>
+      <x:c r="F71" s="2"/>
+      <x:c r="G71" s="2"/>
+      <x:c r="H71" s="2"/>
+      <x:c r="I71" s="2"/>
+      <x:c r="J71" s="2"/>
+      <x:c r="K71" s="2"/>
+      <x:c r="L71" s="2"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="2"/>
+      <x:c r="B72" s="2"/>
+      <x:c r="C72" s="2"/>
+      <x:c r="D72" s="2"/>
+      <x:c r="E72" s="2"/>
+      <x:c r="F72" s="2"/>
+      <x:c r="G72" s="2"/>
+      <x:c r="H72" s="2"/>
+      <x:c r="I72" s="2"/>
+      <x:c r="J72" s="2"/>
+      <x:c r="K72" s="2"/>
+      <x:c r="L72" s="2"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="2"/>
+      <x:c r="B73" s="2"/>
+      <x:c r="C73" s="2"/>
+      <x:c r="D73" s="2"/>
+      <x:c r="E73" s="2"/>
+      <x:c r="F73" s="2"/>
+      <x:c r="G73" s="2"/>
+      <x:c r="H73" s="2"/>
+      <x:c r="I73" s="2"/>
+      <x:c r="J73" s="2"/>
+      <x:c r="K73" s="2"/>
+      <x:c r="L73" s="2"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="2"/>
+      <x:c r="B74" s="2"/>
+      <x:c r="C74" s="2"/>
+      <x:c r="D74" s="2"/>
+      <x:c r="E74" s="2"/>
+      <x:c r="F74" s="2"/>
+      <x:c r="G74" s="2"/>
+      <x:c r="H74" s="2"/>
+      <x:c r="I74" s="2"/>
+      <x:c r="J74" s="2"/>
+      <x:c r="K74" s="2"/>
+      <x:c r="L74" s="2"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="2"/>
+      <x:c r="B75" s="2"/>
+      <x:c r="C75" s="2"/>
+      <x:c r="D75" s="2"/>
+      <x:c r="E75" s="2"/>
+      <x:c r="F75" s="2"/>
+      <x:c r="G75" s="2"/>
+      <x:c r="H75" s="2"/>
+      <x:c r="I75" s="2"/>
+      <x:c r="J75" s="2"/>
+      <x:c r="K75" s="2"/>
+      <x:c r="L75" s="2"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="2"/>
+      <x:c r="B76" s="2"/>
+      <x:c r="C76" s="2"/>
+      <x:c r="D76" s="2"/>
+      <x:c r="E76" s="2"/>
+      <x:c r="F76" s="2"/>
+      <x:c r="G76" s="2"/>
+      <x:c r="H76" s="2"/>
+      <x:c r="I76" s="2"/>
+      <x:c r="J76" s="2"/>
+      <x:c r="K76" s="2"/>
+      <x:c r="L76" s="2"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="2"/>
+      <x:c r="B77" s="2"/>
+      <x:c r="C77" s="2"/>
+      <x:c r="D77" s="2"/>
+      <x:c r="E77" s="2"/>
+      <x:c r="F77" s="2"/>
+      <x:c r="G77" s="2"/>
+      <x:c r="H77" s="2"/>
+      <x:c r="I77" s="2"/>
+      <x:c r="J77" s="2"/>
+      <x:c r="K77" s="2"/>
+      <x:c r="L77" s="2"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="2"/>
+      <x:c r="B78" s="2"/>
+      <x:c r="C78" s="2"/>
+      <x:c r="D78" s="2"/>
+      <x:c r="E78" s="2"/>
+      <x:c r="F78" s="2"/>
+      <x:c r="G78" s="2"/>
+      <x:c r="H78" s="2"/>
+      <x:c r="I78" s="2"/>
+      <x:c r="J78" s="2"/>
+      <x:c r="K78" s="2"/>
+      <x:c r="L78" s="2"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="2"/>
+      <x:c r="B79" s="2"/>
+      <x:c r="C79" s="2"/>
+      <x:c r="D79" s="2"/>
+      <x:c r="E79" s="2"/>
+      <x:c r="F79" s="2"/>
+      <x:c r="G79" s="2"/>
+      <x:c r="H79" s="2"/>
+      <x:c r="I79" s="2"/>
+      <x:c r="J79" s="2"/>
+      <x:c r="K79" s="2"/>
+      <x:c r="L79" s="2"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="2"/>
+      <x:c r="B80" s="2"/>
+      <x:c r="C80" s="2"/>
+      <x:c r="D80" s="2"/>
+      <x:c r="E80" s="2"/>
+      <x:c r="F80" s="2"/>
+      <x:c r="G80" s="2"/>
+      <x:c r="H80" s="2"/>
+      <x:c r="I80" s="2"/>
+      <x:c r="J80" s="2"/>
+      <x:c r="K80" s="2"/>
+      <x:c r="L80" s="2"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="2"/>
+      <x:c r="B81" s="2"/>
+      <x:c r="C81" s="2"/>
+      <x:c r="D81" s="2"/>
+      <x:c r="E81" s="2"/>
+      <x:c r="F81" s="2"/>
+      <x:c r="G81" s="2"/>
+      <x:c r="H81" s="2"/>
+      <x:c r="I81" s="2"/>
+      <x:c r="J81" s="2"/>
+      <x:c r="K81" s="2"/>
+      <x:c r="L81" s="2"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="2"/>
+      <x:c r="B82" s="2"/>
+      <x:c r="C82" s="2"/>
+      <x:c r="D82" s="2"/>
+      <x:c r="E82" s="2"/>
+      <x:c r="F82" s="2"/>
+      <x:c r="G82" s="2"/>
+      <x:c r="H82" s="2"/>
+      <x:c r="I82" s="2"/>
+      <x:c r="J82" s="2"/>
+      <x:c r="K82" s="2"/>
+      <x:c r="L82" s="2"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="2"/>
+      <x:c r="B83" s="2"/>
+      <x:c r="C83" s="2"/>
+      <x:c r="D83" s="2"/>
+      <x:c r="E83" s="2"/>
+      <x:c r="F83" s="2"/>
+      <x:c r="G83" s="2"/>
+      <x:c r="H83" s="2"/>
+      <x:c r="I83" s="2"/>
+      <x:c r="J83" s="2"/>
+      <x:c r="K83" s="2"/>
+      <x:c r="L83" s="2"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="2"/>
+      <x:c r="B84" s="2"/>
+      <x:c r="C84" s="2"/>
+      <x:c r="D84" s="2"/>
+      <x:c r="E84" s="2"/>
+      <x:c r="F84" s="2"/>
+      <x:c r="G84" s="2"/>
+      <x:c r="H84" s="2"/>
+      <x:c r="I84" s="2"/>
+      <x:c r="J84" s="2"/>
+      <x:c r="K84" s="2"/>
+      <x:c r="L84" s="2"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="2"/>
+      <x:c r="B85" s="2"/>
+      <x:c r="C85" s="2"/>
+      <x:c r="D85" s="2"/>
+      <x:c r="E85" s="2"/>
+      <x:c r="F85" s="2"/>
+      <x:c r="G85" s="2"/>
+      <x:c r="H85" s="2"/>
+      <x:c r="I85" s="2"/>
+      <x:c r="J85" s="2"/>
+      <x:c r="K85" s="2"/>
+      <x:c r="L85" s="2"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="2"/>
+      <x:c r="B86" s="2"/>
+      <x:c r="C86" s="2"/>
+      <x:c r="D86" s="2"/>
+      <x:c r="E86" s="2"/>
+      <x:c r="F86" s="2"/>
+      <x:c r="G86" s="2"/>
+      <x:c r="H86" s="2"/>
+      <x:c r="I86" s="2"/>
+      <x:c r="J86" s="2"/>
+      <x:c r="K86" s="2"/>
+      <x:c r="L86" s="2"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="2"/>
+      <x:c r="B87" s="2"/>
+      <x:c r="C87" s="2"/>
+      <x:c r="D87" s="2"/>
+      <x:c r="E87" s="2"/>
+      <x:c r="F87" s="2"/>
+      <x:c r="G87" s="2"/>
+      <x:c r="H87" s="2"/>
+      <x:c r="I87" s="2"/>
+      <x:c r="J87" s="2"/>
+      <x:c r="K87" s="2"/>
+      <x:c r="L87" s="2"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="2"/>
+      <x:c r="B88" s="2"/>
+      <x:c r="C88" s="2"/>
+      <x:c r="D88" s="2"/>
+      <x:c r="E88" s="2"/>
+      <x:c r="F88" s="2"/>
+      <x:c r="G88" s="2"/>
+      <x:c r="H88" s="2"/>
+      <x:c r="I88" s="2"/>
+      <x:c r="J88" s="2"/>
+      <x:c r="K88" s="2"/>
+      <x:c r="L88" s="2"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="2"/>
+      <x:c r="B89" s="2"/>
+      <x:c r="C89" s="2"/>
+      <x:c r="D89" s="2"/>
+      <x:c r="E89" s="2"/>
+      <x:c r="F89" s="2"/>
+      <x:c r="G89" s="2"/>
+      <x:c r="H89" s="2"/>
+      <x:c r="I89" s="2"/>
+      <x:c r="J89" s="2"/>
+      <x:c r="K89" s="2"/>
+      <x:c r="L89" s="2"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="2"/>
+      <x:c r="B90" s="2"/>
+      <x:c r="C90" s="2"/>
+      <x:c r="D90" s="2"/>
+      <x:c r="E90" s="2"/>
+      <x:c r="F90" s="2"/>
+      <x:c r="G90" s="2"/>
+      <x:c r="H90" s="2"/>
+      <x:c r="I90" s="2"/>
+      <x:c r="J90" s="2"/>
+      <x:c r="K90" s="2"/>
+      <x:c r="L90" s="2"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="2"/>
+      <x:c r="B91" s="2"/>
+      <x:c r="C91" s="2"/>
+      <x:c r="D91" s="2"/>
+      <x:c r="E91" s="2"/>
+      <x:c r="F91" s="2"/>
+      <x:c r="G91" s="2"/>
+      <x:c r="H91" s="2"/>
+      <x:c r="I91" s="2"/>
+      <x:c r="J91" s="2"/>
+      <x:c r="K91" s="2"/>
+      <x:c r="L91" s="2"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="2"/>
+      <x:c r="B92" s="2"/>
+      <x:c r="C92" s="2"/>
+      <x:c r="D92" s="2"/>
+      <x:c r="E92" s="2"/>
+      <x:c r="F92" s="2"/>
+      <x:c r="G92" s="2"/>
+      <x:c r="H92" s="2"/>
+      <x:c r="I92" s="2"/>
+      <x:c r="J92" s="2"/>
+      <x:c r="K92" s="2"/>
+      <x:c r="L92" s="2"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="2"/>
+      <x:c r="B93" s="2"/>
+      <x:c r="C93" s="2"/>
+      <x:c r="D93" s="2"/>
+      <x:c r="E93" s="2"/>
+      <x:c r="F93" s="2"/>
+      <x:c r="G93" s="2"/>
+      <x:c r="H93" s="2"/>
+      <x:c r="I93" s="2"/>
+      <x:c r="J93" s="2"/>
+      <x:c r="K93" s="2"/>
+      <x:c r="L93" s="2"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="2"/>
+      <x:c r="B94" s="2"/>
+      <x:c r="C94" s="2"/>
+      <x:c r="D94" s="2"/>
+      <x:c r="E94" s="2"/>
+      <x:c r="F94" s="2"/>
+      <x:c r="G94" s="2"/>
+      <x:c r="H94" s="2"/>
+      <x:c r="I94" s="2"/>
+      <x:c r="J94" s="2"/>
+      <x:c r="K94" s="2"/>
+      <x:c r="L94" s="2"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="2"/>
+      <x:c r="B95" s="2"/>
+      <x:c r="C95" s="2"/>
+      <x:c r="D95" s="2"/>
+      <x:c r="E95" s="2"/>
+      <x:c r="F95" s="2"/>
+      <x:c r="G95" s="2"/>
+      <x:c r="H95" s="2"/>
+      <x:c r="I95" s="2"/>
+      <x:c r="J95" s="2"/>
+      <x:c r="K95" s="2"/>
+      <x:c r="L95" s="2"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="2"/>
+      <x:c r="B96" s="2"/>
+      <x:c r="C96" s="2"/>
+      <x:c r="D96" s="2"/>
+      <x:c r="E96" s="2"/>
+      <x:c r="F96" s="2"/>
+      <x:c r="G96" s="2"/>
+      <x:c r="H96" s="2"/>
+      <x:c r="I96" s="2"/>
+      <x:c r="J96" s="2"/>
+      <x:c r="K96" s="2"/>
+      <x:c r="L96" s="2"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="2"/>
+      <x:c r="B97" s="2"/>
+      <x:c r="C97" s="2"/>
+      <x:c r="D97" s="2"/>
+      <x:c r="E97" s="2"/>
+      <x:c r="F97" s="2"/>
+      <x:c r="G97" s="2"/>
+      <x:c r="H97" s="2"/>
+      <x:c r="I97" s="2"/>
+      <x:c r="J97" s="2"/>
+      <x:c r="K97" s="2"/>
+      <x:c r="L97" s="2"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="2"/>
+      <x:c r="B98" s="2"/>
+      <x:c r="C98" s="2"/>
+      <x:c r="D98" s="2"/>
+      <x:c r="E98" s="2"/>
+      <x:c r="F98" s="2"/>
+      <x:c r="G98" s="2"/>
+      <x:c r="H98" s="2"/>
+      <x:c r="I98" s="2"/>
+      <x:c r="J98" s="2"/>
+      <x:c r="K98" s="2"/>
+      <x:c r="L98" s="2"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="2"/>
+      <x:c r="B99" s="2"/>
+      <x:c r="C99" s="2"/>
+      <x:c r="D99" s="2"/>
+      <x:c r="E99" s="2"/>
+      <x:c r="F99" s="2"/>
+      <x:c r="G99" s="2"/>
+      <x:c r="H99" s="2"/>
+      <x:c r="I99" s="2"/>
+      <x:c r="J99" s="2"/>
+      <x:c r="K99" s="2"/>
+      <x:c r="L99" s="2"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="2"/>
+      <x:c r="B100" s="2"/>
+      <x:c r="C100" s="2"/>
+      <x:c r="D100" s="2"/>
+      <x:c r="E100" s="2"/>
+      <x:c r="F100" s="2"/>
+      <x:c r="G100" s="2"/>
+      <x:c r="H100" s="2"/>
+      <x:c r="I100" s="2"/>
+      <x:c r="J100" s="2"/>
+      <x:c r="K100" s="2"/>
+      <x:c r="L100" s="2"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="2"/>
+      <x:c r="B101" s="2"/>
+      <x:c r="C101" s="2"/>
+      <x:c r="D101" s="2"/>
+      <x:c r="E101" s="2"/>
+      <x:c r="F101" s="2"/>
+      <x:c r="G101" s="2"/>
+      <x:c r="H101" s="2"/>
+      <x:c r="I101" s="2"/>
+      <x:c r="J101" s="2"/>
+      <x:c r="K101" s="2"/>
+      <x:c r="L101" s="2"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="2"/>
+      <x:c r="B102" s="2"/>
+      <x:c r="C102" s="2"/>
+      <x:c r="D102" s="2"/>
+      <x:c r="E102" s="2"/>
+      <x:c r="F102" s="2"/>
+      <x:c r="G102" s="2"/>
+      <x:c r="H102" s="2"/>
+      <x:c r="I102" s="2"/>
+      <x:c r="J102" s="2"/>
+      <x:c r="K102" s="2"/>
+      <x:c r="L102" s="2"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="2"/>
+      <x:c r="B103" s="2"/>
+      <x:c r="C103" s="2"/>
+      <x:c r="D103" s="2"/>
+      <x:c r="E103" s="2"/>
+      <x:c r="F103" s="2"/>
+      <x:c r="G103" s="2"/>
+      <x:c r="H103" s="2"/>
+      <x:c r="I103" s="2"/>
+      <x:c r="J103" s="2"/>
+      <x:c r="K103" s="2"/>
+      <x:c r="L103" s="2"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="2"/>
+      <x:c r="B104" s="2"/>
+      <x:c r="C104" s="2"/>
+      <x:c r="D104" s="2"/>
+      <x:c r="E104" s="2"/>
+      <x:c r="F104" s="2"/>
+      <x:c r="G104" s="2"/>
+      <x:c r="H104" s="2"/>
+      <x:c r="I104" s="2"/>
+      <x:c r="J104" s="2"/>
+      <x:c r="K104" s="2"/>
+      <x:c r="L104" s="2"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="2"/>
+      <x:c r="B105" s="2"/>
+      <x:c r="C105" s="2"/>
+      <x:c r="D105" s="2"/>
+      <x:c r="E105" s="2"/>
+      <x:c r="F105" s="2"/>
+      <x:c r="G105" s="2"/>
+      <x:c r="H105" s="2"/>
+      <x:c r="I105" s="2"/>
+      <x:c r="J105" s="2"/>
+      <x:c r="K105" s="2"/>
+      <x:c r="L105" s="2"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A24:C24"/>
-    <x:mergeCell ref="A25:C25"/>
-    <x:mergeCell ref="A26:C26"/>
-    <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="F24:N27"/>
+    <x:mergeCell ref="G37:K37"/>
+    <x:mergeCell ref="G38:K38"/>
+    <x:mergeCell ref="G39:K39"/>
+    <x:mergeCell ref="G40:K40"/>
+    <x:mergeCell ref="G41:K41"/>
+    <x:mergeCell ref="G42:K42"/>
+    <x:mergeCell ref="G43:K43"/>
+    <x:mergeCell ref="G44:K44"/>
+    <x:mergeCell ref="A48:C48"/>
+    <x:mergeCell ref="A49:C49"/>
+    <x:mergeCell ref="A50:C50"/>
+    <x:mergeCell ref="A51:C51"/>
+    <x:mergeCell ref="A52:C52"/>
+    <x:mergeCell ref="A53:C53"/>
+    <x:mergeCell ref="A54:C54"/>
+    <x:mergeCell ref="A55:C55"/>
+    <x:mergeCell ref="A56:C56"/>
+    <x:mergeCell ref="A57:C57"/>
+    <x:mergeCell ref="A58:C58"/>
+    <x:mergeCell ref="A59:C59"/>
+    <x:mergeCell ref="A60:C60"/>
+    <x:mergeCell ref="A61:C61"/>
+    <x:mergeCell ref="A62:C62"/>
+    <x:mergeCell ref="A63:C63"/>
+    <x:mergeCell ref="A64:C64"/>
+    <x:mergeCell ref="F49:L53"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="M6:M21">
     <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J6:J32">
+    <x:cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -6329,6 +7879,7 @@
     <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="85" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="65" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -6355,7 +7906,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="4" t="str">
-        <x:v>Жёлтые значения — рабочие допущения. Токи в амперах. Пуск указан без заряда конденсаторов.</x:v>
+        <x:v>Пик = базовое допущение × запас на листе «Вход». Средний и пусковой режимы заданы отдельно.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -6389,7 +7940,7 @@
         <x:v>Средний, А</x:v>
       </x:c>
       <x:c r="E5" s="8" t="str">
-        <x:v>Пик, А</x:v>
+        <x:v>Пик с запасом, А</x:v>
       </x:c>
       <x:c r="F5" s="8" t="str">
         <x:v>Пуск без C, А</x:v>
@@ -6399,6 +7950,9 @@
       </x:c>
       <x:c r="H5" s="8" t="str">
         <x:v>Источник</x:v>
+      </x:c>
+      <x:c r="I5" s="35" t="str">
+        <x:v>Базовый пик, А</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="47" customHeight="1">
@@ -6409,22 +7963,26 @@
         <x:v>Power</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>PM MCU, 14 INA301, INA293, логика, оптопары, мониторы</x:v>
+        <x:v>PM MCU, 14 INA301, INA293, логика, оптопары, мониторы; U4901 HOST_ALIVE</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="n">
-        <x:v>0.2</x:v>
+      <x:c r="E6" s="38" t="n">
+        <x:f>I6*'Вход'!$C$22</x:f>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>D01: суммарный резерв, включая VIN/Iq TPS51200; уточнить режим MCU и оптопар</x:v>
+        <x:v>D01: суммарный резерв, включая VIN/Iq TPS51200; уточнить режим MCU и оптопар; U4901 включён в тот же агрегированный резерв, отдельно максимум не подтверждён</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I6" s="37" t="n">
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="47" customHeight="1">
@@ -6440,8 +7998,9 @@
       <x:c r="D7" s="11" t="n">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="n">
-        <x:v>0.005</x:v>
+      <x:c r="E7" s="38" t="n">
+        <x:f>I7*'Вход'!$C$22</x:f>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
         <x:v>0.001</x:v>
@@ -6450,7 +8009,10 @@
         <x:v>D01: предварительный резерв</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I7" s="37" t="n">
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="47" customHeight="1">
@@ -6466,8 +8028,9 @@
       <x:c r="D8" s="11" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="n">
-        <x:v>0.4</x:v>
+      <x:c r="E8" s="38" t="n">
+        <x:f>I8*'Вход'!$C$22</x:f>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
         <x:v>0.08</x:v>
@@ -6476,7 +8039,10 @@
         <x:v>D02: допущение; частоты, периферия и активность не заданы</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I8" s="37" t="n">
+        <x:v>0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="47" customHeight="1">
@@ -6492,8 +8058,9 @@
       <x:c r="D9" s="11" t="n">
         <x:v>0.09</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="n">
-        <x:v>0.15</x:v>
+      <x:c r="E9" s="38" t="n">
+        <x:f>I9*'Вход'!$C$22</x:f>
+        <x:v>0.195</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:v>0.03</x:v>
@@ -6502,7 +8069,10 @@
         <x:v>D02: допущение; заменить расчётом по режимам памяти</x:v>
       </x:c>
       <x:c r="H9" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="n">
+        <x:v>0.15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="47" customHeight="1">
@@ -6518,8 +8088,9 @@
       <x:c r="D10" s="11" t="n">
         <x:v>0.115</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="n">
-        <x:v>0.28</x:v>
+      <x:c r="E10" s="38" t="n">
+        <x:f>I10*'Вход'!$C$22</x:f>
+        <x:v>0.36400000000000005</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:v>0.03</x:v>
@@ -6528,7 +8099,10 @@
         <x:v>D02: 15/30 мА Flash и 100/250 мА microSD; карта не выбрана</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I10" s="37" t="n">
+        <x:v>0.28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="47" customHeight="1">
@@ -6544,8 +8118,9 @@
       <x:c r="D11" s="11" t="n">
         <x:v>0.02</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="n">
-        <x:v>0.05</x:v>
+      <x:c r="E11" s="38" t="n">
+        <x:f>I11*'Вход'!$C$22</x:f>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:v>0.01</x:v>
@@ -6554,7 +8129,10 @@
         <x:v>D02: суммарный резерв</x:v>
       </x:c>
       <x:c r="H11" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I11" s="37" t="n">
+        <x:v>0.05</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="47" customHeight="1">
@@ -6570,8 +8148,9 @@
       <x:c r="D12" s="11" t="n">
         <x:v>0.01</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="n">
-        <x:v>0.02</x:v>
+      <x:c r="E12" s="38" t="n">
+        <x:f>I12*'Вход'!$C$22</x:f>
+        <x:v>0.026000000000000002</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:v>0.005</x:v>
@@ -6580,7 +8159,10 @@
         <x:v>D02: суммарный резерв</x:v>
       </x:c>
       <x:c r="H12" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I12" s="37" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="47" customHeight="1">
@@ -6596,8 +8178,9 @@
       <x:c r="D13" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="n">
-        <x:v>4</x:v>
+      <x:c r="E13" s="38" t="n">
+        <x:f>I13*'Вход'!$C$22</x:f>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:v>1</x:v>
@@ -6607,6 +8190,9 @@
       </x:c>
       <x:c r="H13" s="13" t="str">
         <x:v>https://docs.amd.com/v/u/en-US/ds181_Artix_7_Data_Sheet</x:v>
+      </x:c>
+      <x:c r="I13" s="37" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="47" customHeight="1">
@@ -6622,8 +8208,9 @@
       <x:c r="D14" s="11" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="n">
-        <x:v>0.3</x:v>
+      <x:c r="E14" s="38" t="n">
+        <x:f>I14*'Вход'!$C$22</x:f>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:v>0.15</x:v>
@@ -6633,6 +8220,9 @@
       </x:c>
       <x:c r="H14" s="12" t="str">
         <x:v>https://docs.amd.com/v/u/en-US/ds181_Artix_7_Data_Sheet</x:v>
+      </x:c>
+      <x:c r="I14" s="37" t="n">
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="47" customHeight="1">
@@ -6648,7 +8238,8 @@
       <x:c r="D15" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="n">
+      <x:c r="E15" s="38" t="n">
+        <x:f>I15*'Вход'!$C$22</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
@@ -6658,7 +8249,10 @@
         <x:v>D04: потребитель в текущей схеме не найден; 0 относится к этому сценарию, не к разрешению удалить шину</x:v>
       </x:c>
       <x:c r="H15" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I15" s="37" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="47" customHeight="1">
@@ -6674,8 +8268,9 @@
       <x:c r="D16" s="11" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="n">
-        <x:v>0.4</x:v>
+      <x:c r="E16" s="38" t="n">
+        <x:f>I16*'Вход'!$C$22</x:f>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:v>0.225</x:v>
@@ -6685,6 +8280,9 @@
       </x:c>
       <x:c r="H16" s="12" t="str">
         <x:v>https://docs.amd.com/v/u/en-US/ds181_Artix_7_Data_Sheet</x:v>
+      </x:c>
+      <x:c r="I16" s="37" t="n">
+        <x:v>0.4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="47" customHeight="1">
@@ -6700,8 +8298,9 @@
       <x:c r="D17" s="11" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="n">
-        <x:v>0.3</x:v>
+      <x:c r="E17" s="38" t="n">
+        <x:f>I17*'Вход'!$C$22</x:f>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
         <x:v>0.08</x:v>
@@ -6710,7 +8309,10 @@
         <x:v>D05: общий ток на входе 3,3 В; FT1V0 отдельно повторно не суммируется</x:v>
       </x:c>
       <x:c r="H17" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I17" s="37" t="n">
+        <x:v>0.3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="47" customHeight="1">
@@ -6726,8 +8328,9 @@
       <x:c r="D18" s="11" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="n">
-        <x:v>0.12</x:v>
+      <x:c r="E18" s="38" t="n">
+        <x:f>I18*'Вход'!$C$22</x:f>
+        <x:v>0.156</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:v>0.025</x:v>
@@ -6736,7 +8339,10 @@
         <x:v>D05: резерв; зависит от частот и ёмкостной нагрузки</x:v>
       </x:c>
       <x:c r="H18" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I18" s="37" t="n">
+        <x:v>0.12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="47" customHeight="1">
@@ -6752,8 +8358,9 @@
       <x:c r="D19" s="11" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
-        <x:v>0.09</x:v>
+      <x:c r="E19" s="38" t="n">
+        <x:f>I19*'Вход'!$C$22</x:f>
+        <x:v>0.11699999999999999</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:v>0.06</x:v>
@@ -6762,7 +8369,10 @@
         <x:v>D05: допущение до проверки исполнения генератора</x:v>
       </x:c>
       <x:c r="H19" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I19" s="37" t="n">
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="47" customHeight="1">
@@ -6778,8 +8388,9 @@
       <x:c r="D20" s="11" t="n">
         <x:v>0.04</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="n">
-        <x:v>0.08</x:v>
+      <x:c r="E20" s="38" t="n">
+        <x:f>I20*'Вход'!$C$22</x:f>
+        <x:v>0.10400000000000001</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:v>0.025</x:v>
@@ -6789,6 +8400,9 @@
       </x:c>
       <x:c r="H20" s="12" t="str">
         <x:v>https://www.ti.com/lit/ds/symlink/dp83867ir.pdf</x:v>
+      </x:c>
+      <x:c r="I20" s="37" t="n">
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="47" customHeight="1">
@@ -6804,8 +8418,9 @@
       <x:c r="D21" s="11" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="n">
-        <x:v>0.8</x:v>
+      <x:c r="E21" s="38" t="n">
+        <x:f>I21*'Вход'!$C$22</x:f>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:v>0.15</x:v>
@@ -6814,7 +8429,10 @@
         <x:v>D06: бюджет памяти и I/O; средний включает верхние драйверы SSTL. Пиковая огибающая рассчитана для source VTT</x:v>
       </x:c>
       <x:c r="H21" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I21" s="37" t="n">
+        <x:v>0.8</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="47" customHeight="1">
@@ -6828,21 +8446,25 @@
         <x:v>23 терминирующих резистора по 49,9 Ом</x:v>
       </x:c>
       <x:c r="D22" s="24" t="n">
-        <x:f>E22*0.5</x:f>
+        <x:f>I22*0.5</x:f>
         <x:v>0.15556112224448898</x:v>
       </x:c>
-      <x:c r="E22" s="24" t="n">
+      <x:c r="E22" s="38" t="n">
+        <x:f>I22*'Вход'!$C$22</x:f>
+        <x:v>0.40445891783567134</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="G22" s="12" t="str">
+        <x:v>CALC: |Imax|=23×0,675/49,9; средний source принят 50%. Возможен равный по модулю sink; он не вычитается из входной мощности</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="str">
+        <x:v>https://www.ti.com/product/TPS51200</x:v>
+      </x:c>
+      <x:c r="I22" s="37" t="n">
         <x:f>'Вход'!C52</x:f>
         <x:v>0.31112224448897796</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="n">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="G22" s="12" t="str">
-        <x:v>CALC: |Imax|=23×0,675/49,9; средний source принят 50%. Возможен равный по модулю sink; он не вычитается из входной мощности</x:v>
-      </x:c>
-      <x:c r="H22" s="12" t="str">
-        <x:v>https://www.ti.com/product/TPS51200</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="47" customHeight="1">
@@ -6858,8 +8480,9 @@
       <x:c r="D23" s="11" t="n">
         <x:v>0.0001</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="n">
-        <x:v>0.001</x:v>
+      <x:c r="E23" s="38" t="n">
+        <x:f>I23*'Вход'!$C$22</x:f>
+        <x:v>0.0013000000000000002</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:v>0.0001</x:v>
@@ -6868,7 +8491,10 @@
         <x:v>D06: предварительный ток опор; критерий — tracking/noise, не нагрев контакта</x:v>
       </x:c>
       <x:c r="H23" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I23" s="37" t="n">
+        <x:v>0.001</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="47" customHeight="1">
@@ -6884,8 +8510,9 @@
       <x:c r="D24" s="11" t="n">
         <x:v>0.108</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="n">
-        <x:v>0.2</x:v>
+      <x:c r="E24" s="38" t="n">
+        <x:f>I24*'Вход'!$C$22</x:f>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:v>0.108</x:v>
@@ -6895,6 +8522,9 @@
       </x:c>
       <x:c r="H24" s="12" t="str">
         <x:v>https://www.ti.com/lit/ds/symlink/dp83867ir.pdf</x:v>
+      </x:c>
+      <x:c r="I24" s="37" t="n">
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="47" customHeight="1">
@@ -6910,8 +8540,9 @@
       <x:c r="D25" s="11" t="n">
         <x:v>0.137</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="n">
-        <x:v>0.2</x:v>
+      <x:c r="E25" s="38" t="n">
+        <x:f>I25*'Вход'!$C$22</x:f>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:v>0.137</x:v>
@@ -6921,6 +8552,9 @@
       </x:c>
       <x:c r="H25" s="13" t="str">
         <x:v>https://www.ti.com/lit/ds/symlink/dp83867ir.pdf</x:v>
+      </x:c>
+      <x:c r="I25" s="37" t="n">
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="47" customHeight="1">
@@ -6936,8 +8570,9 @@
       <x:c r="D26" s="11" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="n">
-        <x:v>0.15</x:v>
+      <x:c r="E26" s="38" t="n">
+        <x:f>I26*'Вход'!$C$22</x:f>
+        <x:v>0.195</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:v>0.04</x:v>
@@ -6947,6 +8582,9 @@
       </x:c>
       <x:c r="H26" s="12" t="str">
         <x:v>https://www.analog.com/en/products/ad5676r.html</x:v>
+      </x:c>
+      <x:c r="I26" s="37" t="n">
+        <x:v>0.15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="47" customHeight="1">
@@ -6962,8 +8600,9 @@
       <x:c r="D27" s="11" t="n">
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="n">
-        <x:v>0.002</x:v>
+      <x:c r="E27" s="38" t="n">
+        <x:f>I27*'Вход'!$C$22</x:f>
+        <x:v>0.0026000000000000003</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:v>0.001</x:v>
@@ -6972,7 +8611,10 @@
         <x:v>D07: резерв; основной потребитель — локальный LDO ADC на Control</x:v>
       </x:c>
       <x:c r="H27" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I27" s="37" t="n">
+        <x:v>0.002</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="47" customHeight="1">
@@ -6988,8 +8630,9 @@
       <x:c r="D28" s="11" t="n">
         <x:v>0.02</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="n">
-        <x:v>0.05</x:v>
+      <x:c r="E28" s="38" t="n">
+        <x:f>I28*'Вход'!$C$22</x:f>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:v>0.01</x:v>
@@ -6998,7 +8641,10 @@
         <x:v>D07: допущение до задания частоты выборок</x:v>
       </x:c>
       <x:c r="H28" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I28" s="37" t="n">
+        <x:v>0.05</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="47" customHeight="1">
@@ -7014,8 +8660,9 @@
       <x:c r="D29" s="11" t="n">
         <x:v>0.075</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="n">
-        <x:v>0.1</x:v>
+      <x:c r="E29" s="38" t="n">
+        <x:f>I29*'Вход'!$C$22</x:f>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:v>0.1</x:v>
@@ -7025,6 +8672,9 @@
       </x:c>
       <x:c r="H29" s="13" t="str">
         <x:v>https://www.ti.com/product/OPA4192</x:v>
+      </x:c>
+      <x:c r="I29" s="37" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="47" customHeight="1">
@@ -7040,8 +8690,9 @@
       <x:c r="D30" s="11" t="n">
         <x:v>0.03</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>0.2</x:v>
+      <x:c r="E30" s="38" t="n">
+        <x:f>I30*'Вход'!$C$22</x:f>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:v>0.005</x:v>
@@ -7050,7 +8701,10 @@
         <x:v>D08: допущение. 32 одновременных BL, проводимость DUT и заряд линий требуют отдельного расчёта</x:v>
       </x:c>
       <x:c r="H30" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I30" s="37" t="n">
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="47" customHeight="1">
@@ -7066,8 +8720,9 @@
       <x:c r="D31" s="11" t="n">
         <x:v>0.075</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="n">
-        <x:v>0.1</x:v>
+      <x:c r="E31" s="38" t="n">
+        <x:f>I31*'Вход'!$C$22</x:f>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
         <x:v>0.1</x:v>
@@ -7077,6 +8732,9 @@
       </x:c>
       <x:c r="H31" s="13" t="str">
         <x:v>https://www.ti.com/product/OPA4192</x:v>
+      </x:c>
+      <x:c r="I31" s="37" t="n">
+        <x:v>0.1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="47" customHeight="1">
@@ -7092,8 +8750,9 @@
       <x:c r="D32" s="11" t="n">
         <x:v>0.03</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="n">
-        <x:v>0.2</x:v>
+      <x:c r="E32" s="38" t="n">
+        <x:f>I32*'Вход'!$C$22</x:f>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:v>0.005</x:v>
@@ -7102,7 +8761,10 @@
         <x:v>D08: допущение. 32 одновременных BL, проводимость DUT и заряд линий требуют отдельного расчёта</x:v>
       </x:c>
       <x:c r="H32" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I32" s="37" t="n">
+        <x:v>0.2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="47" customHeight="1">
@@ -7118,8 +8780,9 @@
       <x:c r="D33" s="11" t="n">
         <x:v>0.02</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="n">
-        <x:v>0.06</x:v>
+      <x:c r="E33" s="38" t="n">
+        <x:f>I33*'Вход'!$C$22</x:f>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>0.015</x:v>
@@ -7128,7 +8791,10 @@
         <x:v>D09: резерв до определения импульсов, нагрузки и скважности; учитывается также в родительской ±15 В</x:v>
       </x:c>
       <x:c r="H33" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I33" s="37" t="n">
+        <x:v>0.06</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="47" customHeight="1">
@@ -7144,8 +8810,9 @@
       <x:c r="D34" s="11" t="n">
         <x:v>0.02</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="n">
-        <x:v>0.06</x:v>
+      <x:c r="E34" s="38" t="n">
+        <x:f>I34*'Вход'!$C$22</x:f>
+        <x:v>0.078</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
         <x:v>0.015</x:v>
@@ -7154,7 +8821,10 @@
         <x:v>D09: резерв до определения импульсов, нагрузки и скважности; учитывается также в родительской ±15 В</x:v>
       </x:c>
       <x:c r="H34" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I34" s="37" t="n">
+        <x:v>0.06</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="47" customHeight="1">
@@ -7170,8 +8840,9 @@
       <x:c r="D35" s="11" t="n">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="n">
-        <x:v>0.003</x:v>
+      <x:c r="E35" s="38" t="n">
+        <x:f>I35*'Вход'!$C$22</x:f>
+        <x:v>0.0039000000000000003</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:v>0.002</x:v>
@@ -7180,7 +8851,10 @@
         <x:v>D07: собственный ток опоры предварительно; выходная нагрузка MAT_ADC_REF учитывается отдельно</x:v>
       </x:c>
       <x:c r="H35" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I35" s="37" t="n">
+        <x:v>0.003</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="47" customHeight="1">
@@ -7196,8 +8870,9 @@
       <x:c r="D36" s="11" t="n">
         <x:v>0.001</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="n">
-        <x:v>0.005</x:v>
+      <x:c r="E36" s="38" t="n">
+        <x:f>I36*'Вход'!$C$22</x:f>
+        <x:v>0.006500000000000001</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:v>0.001</x:v>
@@ -7206,7 +8881,10 @@
         <x:v>D07: допущение; динамический ток зарядки входа ADC и буфер ещё проверить</x:v>
       </x:c>
       <x:c r="H36" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I36" s="37" t="n">
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="47" customHeight="1">
@@ -7222,8 +8900,9 @@
       <x:c r="D37" s="11" t="n">
         <x:v>0.02</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="n">
-        <x:v>0.05</x:v>
+      <x:c r="E37" s="38" t="n">
+        <x:f>I37*'Вход'!$C$22</x:f>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
         <x:v>0.02</x:v>
@@ -7232,7 +8911,10 @@
         <x:v>D10: резерв только контроллеру Type-C; внешняя нагрузка USB VBUS не разрешена и не учтена</x:v>
       </x:c>
       <x:c r="H37" s="13" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware</x:v>
+      </x:c>
+      <x:c r="I37" s="37" t="n">
+        <x:v>0.05</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -7395,13 +9077,13 @@
         <x:v>Вход максимальный</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
         <x:v>В</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>D12: 36 В; проверить пределы и выбросы</x:v>
+        <x:v>Рабочий вход кандидата 18–30 В. Уставка OVP около 34 В; выбросы проверить отдельно.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -7463,13 +9145,13 @@
         <x:v>Сопротивление одной контактной пары</x:v>
       </x:c>
       <x:c r="C12" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>мОм</x:v>
       </x:c>
       <x:c r="E12" s="12" t="str">
-        <x:v>D15: 10 мОм условно. Δ15 мОм Samtec не является абсолютным сопротивлением</x:v>
+        <x:v>20 мОм — проектный приёмочный бюджет контактной пары, не гарантированный максимум Samtec.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -7477,7 +9159,7 @@
         <x:v>pcb_loop_mohm</x:v>
       </x:c>
       <x:c r="B13" s="2" t="str">
-        <x:v>Сопротивление дорожек прямого и обратного пути</x:v>
+        <x:v>PCB петля: прежний общий ориентир</x:v>
       </x:c>
       <x:c r="C13" s="14" t="n">
         <x:v>5</x:v>
@@ -7486,7 +9168,7 @@
         <x:v>мОм</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>D15: 5 мОм условно, без шунта и контактов</x:v>
+        <x:v>Не используется для подтверждения распределённых вводов. Для CORE отдельный расчёт на листе «Контакты».</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -7582,13 +9264,13 @@
         <x:v>Ёмкость при первом подъёме BUS24</x:v>
       </x:c>
       <x:c r="C19" s="14" t="n">
-        <x:v>149</x:v>
+        <x:v>144.2</x:v>
       </x:c>
       <x:c r="D19" s="2" t="str">
         <x:v>мкФ</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>Схема: 144,2 мкФ к GND + 4,8 мкФ BUS24–N15_RAW; нижние преобразователи выключены</x:v>
+        <x:v>Сумма номиналов к GND на BUS24, BUS24_PRE_SHUNT и EFUSE_OUT по текущему netlist.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
@@ -7630,16 +9312,16 @@
         <x:v>reserve_factor</x:v>
       </x:c>
       <x:c r="B22" s="9" t="str">
-        <x:v>Резерв внешнего БП по мощности</x:v>
+        <x:v>Множитель базового пика нагрузок</x:v>
       </x:c>
       <x:c r="C22" s="14" t="n">
-        <x:v>1.25</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
         <x:v>×</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
-        <x:v>D18: 25% для предварительного выбора мощности, не заказ БП</x:v>
+        <x:v>+30% к каждому исходному пику нагрузки. Во входной мощности повторно не умножается.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
@@ -7663,7 +9345,7 @@
       </x:c>
       <x:c r="C25" s="17" t="n">
         <x:f>('Шины'!P6+'Шины'!P7+'Шины'!P8+'Шины'!P9+'Шины'!P18+'Шины'!P21+'Шины'!P22)*C6+C6*C21</x:f>
-        <x:v>14.54900977618701</x:v>
+        <x:v>15.361068702928616</x:v>
       </x:c>
       <x:c r="D25" s="2"/>
       <x:c r="E25" s="13"/>
@@ -7675,7 +9357,7 @@
       </x:c>
       <x:c r="C26" s="16" t="n">
         <x:f>('Шины'!Q6+'Шины'!Q7+'Шины'!Q8+'Шины'!Q9+'Шины'!Q18+'Шины'!Q21+'Шины'!Q22)*C6+C6*C21</x:f>
-        <x:v>32.279067883702865</x:v>
+        <x:v>42.79523885920843</x:v>
       </x:c>
       <x:c r="D26" s="9"/>
       <x:c r="E26" s="12"/>
@@ -7687,7 +9369,7 @@
       </x:c>
       <x:c r="C27" s="17" t="n">
         <x:f>('Пуск'!K6+'Пуск'!K7+'Пуск'!K8+'Пуск'!K9+'Пуск'!K18+'Пуск'!K21+'Пуск'!K22)*C6+C6*C21</x:f>
-        <x:v>38.380913476802405</x:v>
+        <x:v>38.887472354021696</x:v>
       </x:c>
       <x:c r="D27" s="2"/>
       <x:c r="E27" s="13"/>
@@ -7706,7 +9388,7 @@
       </x:c>
       <x:c r="C29" s="17" t="n">
         <x:f>IF(C18=0,C25/C6,(C6-SQRT(C6^2-4*C18*C25))/(2*C18))</x:f>
-        <x:v>0.6080574097421761</x:v>
+        <x:v>0.6421060300578763</x:v>
       </x:c>
       <x:c r="D29" s="2"/>
       <x:c r="E29" s="13"/>
@@ -7718,7 +9400,7 @@
       </x:c>
       <x:c r="C30" s="16" t="n">
         <x:f>IF(C18=0,C26/C6,(C6-SQRT(C6^2-4*C18*C26))/(2*C18))</x:f>
-        <x:v>1.3541294952707617</x:v>
+        <x:v>1.7993227645216456</x:v>
       </x:c>
       <x:c r="D30" s="9"/>
       <x:c r="E30" s="12"/>
@@ -7730,7 +9412,7 @@
       </x:c>
       <x:c r="C31" s="17" t="n">
         <x:f>IF(C18=0,C26/C7,(C7-SQRT(C7^2-4*C18*C26))/(2*C18))</x:f>
-        <x:v>1.8152490771758512</x:v>
+        <x:v>2.416441190124911</x:v>
       </x:c>
       <x:c r="D31" s="2"/>
       <x:c r="E31" s="13"/>
@@ -7742,7 +9424,7 @@
       </x:c>
       <x:c r="C32" s="16" t="n">
         <x:f>IF(C18=0,C27/C7,(C7-SQRT(C7^2-4*C18*C27))/(2*C18))</x:f>
-        <x:v>2.1634771947481055</x:v>
+        <x:v>2.1924610333301215</x:v>
       </x:c>
       <x:c r="D32" s="9"/>
       <x:c r="E32" s="12"/>
@@ -7785,7 +9467,7 @@
       </x:c>
       <x:c r="C36" s="16" t="n">
         <x:f>C35-C31</x:f>
-        <x:v>1.3297713072155295</x:v>
+        <x:v>0.7285791942664694</x:v>
       </x:c>
       <x:c r="D36" s="9"/>
       <x:c r="E36" s="12"/>
@@ -7793,11 +9475,11 @@
     <x:row r="37" ht="34" customHeight="1">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2" t="str">
-        <x:v>Пиковая входная мощность с резервом БП, Вт</x:v>
+        <x:v>Входная мощность при расчётном пике, Вт</x:v>
       </x:c>
       <x:c r="C37" s="17" t="n">
-        <x:f>C30*C6*C22</x:f>
-        <x:v>40.62388485812285</x:v>
+        <x:f>C30*C6</x:f>
+        <x:v>43.18374634851949</x:v>
       </x:c>
       <x:c r="D37" s="2"/>
       <x:c r="E37" s="13"/>
@@ -7816,7 +9498,7 @@
       </x:c>
       <x:c r="C39" s="17" t="n">
         <x:f>C19*C9*C20/1000</x:f>
-        <x:v>0.0894</x:v>
+        <x:v>0.08652</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
       <x:c r="E39" s="13"/>
@@ -7862,7 +9544,7 @@
       </x:c>
       <x:c r="C43" s="17" t="n">
         <x:f>C31^2*C42</x:f>
-        <x:v>0.06590258424375559</x:v>
+        <x:v>0.11678376050664595</x:v>
       </x:c>
       <x:c r="D43" s="2"/>
       <x:c r="E43" s="13"/>
@@ -7874,7 +9556,7 @@
       </x:c>
       <x:c r="C44" s="16" t="n">
         <x:f>C31^2*C18</x:f>
-        <x:v>0.39541550546253346</x:v>
+        <x:v>0.7007025630398757</x:v>
       </x:c>
       <x:c r="D44" s="9"/>
       <x:c r="E44" s="12"/>
@@ -7889,11 +9571,11 @@
     <x:row r="46" ht="34" customHeight="1">
       <x:c r="A46" s="9"/>
       <x:c r="B46" s="9" t="str">
-        <x:v>N15, оценка тока при 24 В, А</x:v>
+        <x:v>N15: паспортный ток модуля, А</x:v>
       </x:c>
       <x:c r="C46" s="16" t="n">
-        <x:f>1-ABS('Шины'!D22)/(ABS('Шины'!D22)+C6*'Шины'!H22)</x:f>
-        <x:v>0.5615669666490206</x:v>
+        <x:f>'Шины'!E22</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D46" s="9"/>
       <x:c r="E46" s="12"/>
@@ -7901,26 +9583,29 @@
     <x:row r="47" ht="34" customHeight="1">
       <x:c r="A47" s="2"/>
       <x:c r="B47" s="2" t="str">
-        <x:v>N15, оценка тока при Vin min, А</x:v>
+        <x:v>N15: нижняя статическая оценка OCP, А</x:v>
       </x:c>
       <x:c r="C47" s="17" t="n">
-        <x:f>'Шины'!E22</x:f>
-        <x:v>0.48996181795787663</x:v>
+        <x:v>0.5125921326601899</x:v>
       </x:c>
       <x:c r="D47" s="2"/>
-      <x:c r="E47" s="13"/>
+      <x:c r="E47" s="13" t="str">
+        <x:v>Снимок расчёта допусков n15-ocp-corners.json; уставки схемы здесь не редактируются.</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
       <x:c r="A48" s="9"/>
       <x:c r="B48" s="9" t="str">
-        <x:v>N15: требуемая рампа, дочерние пуски в огибающей, мс</x:v>
+        <x:v>N15: запас OCP к пику, А</x:v>
       </x:c>
       <x:c r="C48" s="16" t="n">
-        <x:f>IF('Шины'!E22&lt;='Пуск'!G22+'Пуск'!H22,"нет запаса",'Пуск'!D22*C9*ABS('Шины'!D22)/(1000*('Шины'!E22-'Пуск'!G22-'Пуск'!H22)))</x:f>
-        <x:v>7.279572534175508</x:v>
+        <x:f>C47-'Шины'!O22</x:f>
+        <x:v>0.044592132660189854</x:v>
       </x:c>
       <x:c r="D48" s="9"/>
-      <x:c r="E48" s="12"/>
+      <x:c r="E48" s="12" t="str">
+        <x:v>Пуск 5 мс — условный сценарий; он может пересекать OCP даже при запасе модуля по току.</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
       <x:c r="A49" s="2"/>
@@ -8043,7 +9728,7 @@
       <x:c r="C60" s="9"/>
       <x:c r="D60" s="9"/>
       <x:c r="E60" s="12" t="str">
-        <x:v>https://github.com/max-talanov/mira/tree/24b4428877257387bc5a686abd9e830a37f58770/hardware; https://www.ti.com/lit/ds/symlink/tps2663.pdf</x:v>
+        <x:v>https://github.com/max-talanov/mira/tree/52f43869b6ed5019490eb40afbc84a4d607fd61e/hardware; https://www.ti.com/lit/ds/symlink/tps2663.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="34" customHeight="1">
@@ -8054,7 +9739,7 @@
       <x:c r="C61" s="2"/>
       <x:c r="D61" s="2"/>
       <x:c r="E61" s="13" t="str">
-        <x:v>https://www.ti.com/lit/an/slvafp0/slvafp0.pdf</x:v>
+        <x:v>https://www.tracopower.com/products/ten30win.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="34" customHeight="1">
@@ -8076,19 +9761,19 @@
       <x:c r="C63" s="2"/>
       <x:c r="D63" s="2"/>
       <x:c r="E63" s="13" t="str">
-        <x:v>https://suddendocs.samtec.com/productspecs/tsw-sxx.pdf</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="34" customHeight="1">
+        <x:v>../distributed-power/connector-bom.csv; https://www.samtec.com/products/ssw-113-01-s-d</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="55" customHeight="1">
       <x:c r="A64" s="9"/>
       <x:c r="B64" s="9"/>
       <x:c r="C64" s="9"/>
       <x:c r="D64" s="9"/>
       <x:c r="E64" s="12" t="str">
-        <x:v>Samtec SSW/TSW: 4,7 А при одном нагруженном контакте в каждом ряду. Этот рейтинг не перенесён на все 64 контакта J400.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="42" customHeight="1">
+        <x:v>Выбраны восемь пар SSW/HTSW. 1 А/контакт — проектное ограничение; требуется температурная проверка при совместной нагрузке.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="55" customHeight="1">
       <x:c r="A65" s="2"/>
       <x:c r="B65" s="2" t="str">
         <x:v>D20: КПД и собственное потребление</x:v>
@@ -8096,10 +9781,10 @@
       <x:c r="C65" s="2"/>
       <x:c r="D65" s="2"/>
       <x:c r="E65" s="13" t="str">
-        <x:v>КПД и Iq на листе «Шины» — предварительные значения. Они не заменяют кривые КПД, Iq в рабочем режиме, тепловой расчёт и потери дросселей. При 18 В мощность нагрузки считается постоянной.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="42" customHeight="1">
+        <x:v>Для N15: η=0,80 как сценарий потерь плюс 30 мА типового холостого тока. Паспортные 89% полной нагрузки не переносятся на этот режим. Для остальных источников сохранены прежние допущения η/Iq.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="55" customHeight="1">
       <x:c r="A66" s="9"/>
       <x:c r="B66" s="9" t="str">
         <x:v>Границы модели</x:v>
@@ -8107,7 +9792,7 @@
       <x:c r="C66" s="9"/>
       <x:c r="D66" s="9"/>
       <x:c r="E66" s="12" t="str">
-        <x:v>Предполагается штатная работа узлов после устранения открытых электрических вопросов I01–I08 и E01–E07. Это не расчёт аварийного потребления и не подтверждение фактической связности схем.</x:v>
+        <x:v>ERC: 0/0/0 на обеих схемах. Модель не подтверждает PCB, переходные процессы, обрыв связи и тепловой режим.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="27" customHeight="1">
